--- a/gui/rebalance_localizations.xlsx
+++ b/gui/rebalance_localizations.xlsx
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">rebalance_localizations!$A$1:$K$517</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">rebalance_localizations!$A$1:$K$647</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="1246">
   <si>
     <t>ENGLISH</t>
   </si>
@@ -151,9 +151,6 @@
     <t>gui/hud/building_description/bio_cobalt_refinery</t>
   </si>
   <si>
-    <t>Refines cobalt from bio-compounds and solvent</t>
-  </si>
-  <si>
     <t>gui/hud/building_description/bio_palladium_refinery</t>
   </si>
   <si>
@@ -163,15 +160,9 @@
     <t>gui/hud/building_description/bio_titanium_refinery</t>
   </si>
   <si>
-    <t>Refines titanium from bio-compounds and solvent</t>
-  </si>
-  <si>
     <t>gui/hud/building_description/bio_uranium_ore_refinery</t>
   </si>
   <si>
-    <t>Refines uranium ore from bio-compounds and solvent</t>
-  </si>
-  <si>
     <t>gui/hud/building_description/biomass_water_press</t>
   </si>
   <si>
@@ -712,60 +703,6 @@
     <t>Infused Super Coolant</t>
   </si>
   <si>
-    <t>resource_name/ammo_mech_energy_cell_lvl2</t>
-  </si>
-  <si>
-    <t>resource_name/ammo_mech_energy_cell_lvl3</t>
-  </si>
-  <si>
-    <t>resource_name/ammo_mech_explosive_lvl2</t>
-  </si>
-  <si>
-    <t>resource_name/ammo_mech_explosive_lvl3</t>
-  </si>
-  <si>
-    <t>resource_name/ammo_mech_high_caliber_lvl2</t>
-  </si>
-  <si>
-    <t>resource_name/ammo_mech_high_caliber_lvl3</t>
-  </si>
-  <si>
-    <t>resource_name/ammo_mech_liquid_lvl2</t>
-  </si>
-  <si>
-    <t>resource_name/ammo_mech_liquid_lvl3</t>
-  </si>
-  <si>
-    <t>resource_name/ammo_mech_low_caliber_lvl2</t>
-  </si>
-  <si>
-    <t>resource_name/ammo_mech_low_caliber_lvl3</t>
-  </si>
-  <si>
-    <t>resource_name/ammo_tower_explosive_lvl2</t>
-  </si>
-  <si>
-    <t>resource_name/ammo_tower_explosive_lvl3</t>
-  </si>
-  <si>
-    <t>resource_name/ammo_tower_high_caliber_lvl2</t>
-  </si>
-  <si>
-    <t>resource_name/ammo_tower_high_caliber_lvl3</t>
-  </si>
-  <si>
-    <t>resource_name/ammo_tower_liquid_lvl2</t>
-  </si>
-  <si>
-    <t>resource_name/ammo_tower_liquid_lvl3</t>
-  </si>
-  <si>
-    <t>resource_name/ammo_tower_low_caliber_lvl2</t>
-  </si>
-  <si>
-    <t>resource_name/ammo_tower_low_caliber_lvl3</t>
-  </si>
-  <si>
     <t>resource_name/ammonium</t>
   </si>
   <si>
@@ -997,9 +934,6 @@
     <t>gui/hud/building_name/fluorine_trap</t>
   </si>
   <si>
-    <t>Atmospheric Fluorine Trap</t>
-  </si>
-  <si>
     <t>gui/hud/building_description/solvent_condenser</t>
   </si>
   <si>
@@ -1009,9 +943,6 @@
     <t>gui/hud/building_name/fluorine_trap_lvl_3</t>
   </si>
   <si>
-    <t>Captures fluorine compounds from atmosphere</t>
-  </si>
-  <si>
     <t>Condenses hyrdo-fluorines into solvent liquid</t>
   </si>
   <si>
@@ -1573,9 +1504,6 @@
     <t>Allows Riftbreakers to collect and utilized morphed biomass from plants and creatues in the metallic biome and utilize it to produce morphium.</t>
   </si>
   <si>
-    <t>gui/menu/research/name/biomass_morpherd_processing</t>
-  </si>
-  <si>
     <t>Morphed Biomass Handling</t>
   </si>
   <si>
@@ -1705,27 +1633,12 @@
     <t>Advanced Low Caliber Production</t>
   </si>
   <si>
-    <t>Top End Energy Cell Production</t>
-  </si>
-  <si>
-    <t>Top End High Caliber Production</t>
-  </si>
-  <si>
-    <t>Top End Low Caliber Production</t>
-  </si>
-  <si>
     <t>Advanced Explosives Production</t>
   </si>
   <si>
     <t>Advanced Liquid Ammunitions Production</t>
   </si>
   <si>
-    <t>Top End Explosives Production</t>
-  </si>
-  <si>
-    <t>Top End Liquid Ammunitions Production</t>
-  </si>
-  <si>
     <t>gui/hud/building_description/ammo_factory_liquid_adv_gas</t>
   </si>
   <si>
@@ -2269,9 +2182,6 @@
     <t>Canon using cryo rounds</t>
   </si>
   <si>
-    <t>gui/menu/research/description/tower_artillery_acid</t>
-  </si>
-  <si>
     <t>gui/menu/research/description/tower_artillery_napalm</t>
   </si>
   <si>
@@ -2284,9 +2194,6 @@
     <t>gui/menu/research/description/tower_cannon_incindiary</t>
   </si>
   <si>
-    <t>gui/menu/research/name/tower_artillery_acid</t>
-  </si>
-  <si>
     <t>gui/menu/research/name/tower_artillery_napalm</t>
   </si>
   <si>
@@ -2686,60 +2593,6 @@
     <t>gui/menu/planetary_scanner/base_info_buildings_ammo</t>
   </si>
   <si>
-    <t>High caliber &lt;img="gui/hud/building_info_mech"&gt; top end</t>
-  </si>
-  <si>
-    <t>High caliber &lt;img="gui/hud/building_info_mech"&gt; advanced</t>
-  </si>
-  <si>
-    <t>Explosive &lt;img="gui/hud/building_info_mech"&gt; top end</t>
-  </si>
-  <si>
-    <t>Explosive &lt;img="gui/hud/building_info_mech"&gt; advanced</t>
-  </si>
-  <si>
-    <t>Energy cell &lt;img="gui/hud/building_info_mech"&gt; top end</t>
-  </si>
-  <si>
-    <t>Energy cell &lt;img="gui/hud/building_info_mech"&gt; advanced</t>
-  </si>
-  <si>
-    <t>Liquid &lt;img="gui/hud/building_info_mech"&gt; advanced</t>
-  </si>
-  <si>
-    <t>Liquid &lt;img="gui/hud/building_info_mech"&gt; top end</t>
-  </si>
-  <si>
-    <t>Low caliber &lt;img="gui/hud/building_info_mech"&gt; advanced</t>
-  </si>
-  <si>
-    <t>Low caliber &lt;img="gui/hud/building_info_mech"&gt; top end</t>
-  </si>
-  <si>
-    <t>Explosive &lt;img="gui/hud/building_info_tower"&gt; top end</t>
-  </si>
-  <si>
-    <t>High caliber &lt;img="gui/hud/building_info_tower"&gt; advanced</t>
-  </si>
-  <si>
-    <t>High caliber &lt;img="gui/hud/building_info_tower"&gt; top end</t>
-  </si>
-  <si>
-    <t>Liquid &lt;img="gui/hud/building_info_tower"&gt; top end</t>
-  </si>
-  <si>
-    <t>Low caliber &lt;img="gui/hud/building_info_tower"&gt; advanced</t>
-  </si>
-  <si>
-    <t>Low caliber &lt;img="gui/hud/building_info_tower"&gt; top end</t>
-  </si>
-  <si>
-    <t>Liquid &lt;img="gui/hud/building_info_tower"&gt; advanced</t>
-  </si>
-  <si>
-    <t>Explosive &lt;img="gui/hud/building_info_tower"&gt; advanced</t>
-  </si>
-  <si>
     <t>Resist - Solar Flare</t>
   </si>
   <si>
@@ -2860,12 +2713,6 @@
     <t>gui/hud/building_description/crystalizer_tanzanite</t>
   </si>
   <si>
-    <t>Crystalizes Tanzanite from Ironium and Plasma</t>
-  </si>
-  <si>
-    <t>Crystalizes Ferdonite from Ironium and Supercoolant</t>
-  </si>
-  <si>
     <t>gui/menu/research/description/crystalizer_rhodonite</t>
   </si>
   <si>
@@ -2941,12 +2788,6 @@
     <t>gui/menu/research/description/crystalizer_tanzanite_lvl3</t>
   </si>
   <si>
-    <t>Crystalizes Hazenite from Ironium and Reagent</t>
-  </si>
-  <si>
-    <t>Crystalizes Rhodonite from Ironium and Nitric Acid</t>
-  </si>
-  <si>
     <t>gui/menu/research/name/crystalizer_rhodonite</t>
   </si>
   <si>
@@ -2966,6 +2807,960 @@
   </si>
   <si>
     <t>gui/menu/inventory/upgrade/stat_name/resistance_sunburn</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/towers_artillery_acid</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/towers_artillery_acid</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/comm_hub_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/comm_hub_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/comm_hub_lvl_4</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/comm_hub_lvl_5</t>
+  </si>
+  <si>
+    <t>Communications Hub 2</t>
+  </si>
+  <si>
+    <t>Communications Hub 4</t>
+  </si>
+  <si>
+    <t>Communications Hub 3</t>
+  </si>
+  <si>
+    <t>Communications Hub 5</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/outposts_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/outposts_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/outposts_lvl_4</t>
+  </si>
+  <si>
+    <t>Outpost Expansion</t>
+  </si>
+  <si>
+    <t>Outpost Expansion 2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/outposts_lvl_1</t>
+  </si>
+  <si>
+    <t>Outpost Expansion 3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/comm_hub_expansion_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/comm_hub_expansion_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/comm_hub_expansion_lvl_4</t>
+  </si>
+  <si>
+    <t>Communications Hub Expansion 2</t>
+  </si>
+  <si>
+    <t>Communications Hub Expansion 3</t>
+  </si>
+  <si>
+    <t>Communications Hub Expansion 4</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/comm_hub_lvl_4</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/comm_hub_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/comm_hub_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/comm_hub_lvl_5</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/outposts_lvl_1</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/outposts_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/outposts_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/comm_hub_expansion_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/comm_hub_expansion_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/comm_hub_expansion_lvl_4</t>
+  </si>
+  <si>
+    <t>Outpost Expansion 4</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/outposts_lvl_5</t>
+  </si>
+  <si>
+    <t>Outpost Expansion 5</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/outposts_lvl_4</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/outposts_lvl_5</t>
+  </si>
+  <si>
+    <t>Technical infrastructure needed to support a larget amount of remote outpost</t>
+  </si>
+  <si>
+    <t>Technical infrastructure to support a larger amount of communication hubs</t>
+  </si>
+  <si>
+    <t>Optimizing the Communications Hub to maintain a stronger connection and allow more data bandwith</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/comm_hub_expansion_lvl_1</t>
+  </si>
+  <si>
+    <t>Communications Hub Expansion</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/comm_hub_expansion_lvl_1</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/ai_hub</t>
+  </si>
+  <si>
+    <t>AI Hubs enable maintain and control of defenses and advanced production facilities</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/resource_converter_cobalt</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/resource_converter_cobalt</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/resource_converter_palladium</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/resource_converter_titanium</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/resource_converter_palladium</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/resource_converter_titanium</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/resource_converter_cobalt</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/resource_converter_palladium</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/resource_converter_titanium</t>
+  </si>
+  <si>
+    <t>Metallic Morphing - Cobalt</t>
+  </si>
+  <si>
+    <t>Metallic Morphing - Palladium</t>
+  </si>
+  <si>
+    <t>Metallic Morphing - Titanium</t>
+  </si>
+  <si>
+    <t>Cobalt Morphing Plant</t>
+  </si>
+  <si>
+    <t>Palladium Morphing Plant</t>
+  </si>
+  <si>
+    <t>Titanium Morphing Plant</t>
+  </si>
+  <si>
+    <t>Uses morphium to convert cobalt into palladium</t>
+  </si>
+  <si>
+    <t>Uses morphium to convert cobalt into titanium</t>
+  </si>
+  <si>
+    <t>Uses morphium to convert iron into cobalt</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/fire_control_station_artillery</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/fire_control_station_artillery</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/fire_control_station_artillery</t>
+  </si>
+  <si>
+    <t>Powers up/down long range artillery towers depending on if enemies are in vicinity or not. Much wieder detection range then regular fire control stations</t>
+  </si>
+  <si>
+    <t>Long Range Fire Control Station</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/uranium_enrichment_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/uranium_enrichment_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/uranium_enrichment_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/uranium_enrichment_lvl_3</t>
+  </si>
+  <si>
+    <t>Enhanced Uranium Enrichtment</t>
+  </si>
+  <si>
+    <t>Morphing Uranium Enrichment</t>
+  </si>
+  <si>
+    <t>Application of morphium to adjust isotope ratio of raw uranium allows to maximize centrifuge yield</t>
+  </si>
+  <si>
+    <t>Advanced techniques applying tanzanite allows for a more efficient mass seperation of isotopes</t>
+  </si>
+  <si>
+    <t>resource_name/reagent_compressed</t>
+  </si>
+  <si>
+    <t>resource_name/solvent_compressed</t>
+  </si>
+  <si>
+    <t>resource_name/nitric_acid_compressed</t>
+  </si>
+  <si>
+    <t>resource_name/fluorine_compressed</t>
+  </si>
+  <si>
+    <t>resource_name/deuterium_compressed</t>
+  </si>
+  <si>
+    <t>resource_name/magma_metal_compressed</t>
+  </si>
+  <si>
+    <t>resource_name/petroleum_compressed</t>
+  </si>
+  <si>
+    <t>Packaged Reagent</t>
+  </si>
+  <si>
+    <t>Packaged Solvent</t>
+  </si>
+  <si>
+    <t>Packaged Petroleum</t>
+  </si>
+  <si>
+    <t>Packaged N.Acid</t>
+  </si>
+  <si>
+    <t>Liquid Fluorine</t>
+  </si>
+  <si>
+    <t>Liquid Deuterium</t>
+  </si>
+  <si>
+    <t>You don't want to know</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/fire_control_station_artillery</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/resource_converter_cobalt</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/resource_converter_palladium</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/resource_converter_titanium</t>
+  </si>
+  <si>
+    <t>Uses morphiums ability to transition between elements to convert iron into cobalt</t>
+  </si>
+  <si>
+    <t>Uses morphium ability to transition between elements to convert cobalt into palladium</t>
+  </si>
+  <si>
+    <t>Uses morphium ability to transition between elements to convert cobalt into titanium</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/ammonium_synthesis</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/ammonium_synthesis_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/ammonium_synthesis</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/ammonium_synthesis_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/ammonium_synthesizer</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/ammonium_synthesizer</t>
+  </si>
+  <si>
+    <t>Ammonium Synthesizer</t>
+  </si>
+  <si>
+    <t>Synthesizes ammonium from atmospheric nitrogen via the Haber-process. Flammable gas serves serves as hydrogen source.</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/ammonium_synthesizer_lvl_2</t>
+  </si>
+  <si>
+    <t>Improves the Haber process by cleaning the gas from sulfur residuals using water</t>
+  </si>
+  <si>
+    <t>Ammonium synthesis from atmospheric nitrogen via the Haber-process. Flammable gas or pertoleum serves serves as hydrogen source.</t>
+  </si>
+  <si>
+    <t>Atmospheric Nitrogen Utilization</t>
+  </si>
+  <si>
+    <t>Improved Haber Process</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/ammonium_extraction_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/ammonium_extraction</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/ammonium_extraction_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/ammonium_extraction</t>
+  </si>
+  <si>
+    <t>Ammonium Extraction</t>
+  </si>
+  <si>
+    <t>Advanced Ammonium Extraction</t>
+  </si>
+  <si>
+    <t>Extracts Ammonium from nitrate rich natural sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extracts Ammonium from nitrate rich natural sources. </t>
+  </si>
+  <si>
+    <t>gui/menu/inventory/upgrade/stat_name/ammo_homing</t>
+  </si>
+  <si>
+    <t>Projectile homing</t>
+  </si>
+  <si>
+    <t>gui/menu/inventory/stat_name/ammo_homing</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/carbonization</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/carbonization_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/carbonization</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/carbonization_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/carbonizer</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/carbonizer</t>
+  </si>
+  <si>
+    <t>Synthethise carbon from carbon rich gases or liquids</t>
+  </si>
+  <si>
+    <t>Carbonizer</t>
+  </si>
+  <si>
+    <t>Carbon Synthesis</t>
+  </si>
+  <si>
+    <t>Advanced Carbon Synthesis</t>
+  </si>
+  <si>
+    <t>Synthethise carbon from carbon rich gases or liquids. Uses reagent as catalyst increase the yield</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/bioreactor</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/bioreactor</t>
+  </si>
+  <si>
+    <t>Bioreactor</t>
+  </si>
+  <si>
+    <t>Uses biological processes to decompose mud into sludge</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/energy_connector_armored</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/energy_connector_armored</t>
+  </si>
+  <si>
+    <t>Armored Energy Connector</t>
+  </si>
+  <si>
+    <t>An armored but more expensive variant of the energy connector</t>
+  </si>
+  <si>
+    <t>resource_name/uranium_depleted</t>
+  </si>
+  <si>
+    <t>Mycelium</t>
+  </si>
+  <si>
+    <t>Mycel</t>
+  </si>
+  <si>
+    <t>Depleted Uranium</t>
+  </si>
+  <si>
+    <t>resource_name/alloys</t>
+  </si>
+  <si>
+    <t>Alloys</t>
+  </si>
+  <si>
+    <t>Legierungen</t>
+  </si>
+  <si>
+    <t>Abgereichertes Uran</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/fluorine_trap_lvl_2</t>
+  </si>
+  <si>
+    <t>resource_name/biomass_mycelium</t>
+  </si>
+  <si>
+    <t>Mycelium Press</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/mycelium_processing</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/mycelium_processing_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/mycelium_processing</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/mycelium_processing_lvl_2</t>
+  </si>
+  <si>
+    <t>Mycelim Processing</t>
+  </si>
+  <si>
+    <t>Advanced Mycelium Processing</t>
+  </si>
+  <si>
+    <t>Extracts fluorine from fluor rich mycelium</t>
+  </si>
+  <si>
+    <t>Advanced Morphed Biomass Handling</t>
+  </si>
+  <si>
+    <t>Extraction of fluorine from fluor rich mycelium</t>
+  </si>
+  <si>
+    <t>Fluorine Capture</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/fluorine_capture</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/fluorine_capture_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/fluorine_capture</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/fluorine_capture_lvl_2</t>
+  </si>
+  <si>
+    <t>Biome Adjusted Fluorine Capture</t>
+  </si>
+  <si>
+    <t>Technology to capture atmospheric fluorine</t>
+  </si>
+  <si>
+    <t>Adapted fluorine capture method for fluorine rich biomes</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/biomass_morphed_processing_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/biomass_mycelium_press</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/biomass_mycelium_press</t>
+  </si>
+  <si>
+    <t>Fluorine Capture Plant</t>
+  </si>
+  <si>
+    <t>Special Fluorine Capture Plant</t>
+  </si>
+  <si>
+    <t>Captures atmospheric fluorine compounds from atmosphere. Improved for fluorine rich enviorments</t>
+  </si>
+  <si>
+    <t>Captures atmospheric fluorine compounds from atmosphere</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/biomass_morphed_processing</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/biomass_morphed_processing_lvl_2</t>
+  </si>
+  <si>
+    <t>Stores large quantities of liquid materials</t>
+  </si>
+  <si>
+    <t>Small Storage Silo</t>
+  </si>
+  <si>
+    <t>Large Storage Silo</t>
+  </si>
+  <si>
+    <t>Stores liquid materials in a minimal space</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/liquid_material_storage_large</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/liquid_material_storage_small</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/liquid_material_storage_large</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/liquid_material_storage_small</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/steel_seperator</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/steel_seperator</t>
+  </si>
+  <si>
+    <t>Metal Seperator</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/steel_seperator_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/steel_seperator_lvl_3</t>
+  </si>
+  <si>
+    <t>Seperates metals of out lava including trace amounts of titanium</t>
+  </si>
+  <si>
+    <t>Seperates simple metals of out lava</t>
+  </si>
+  <si>
+    <t>Seperates metals of out lava including low amounts of titanium</t>
+  </si>
+  <si>
+    <t>An advanced form of a wall. Instead of relying on a solid structure this version utilizes high-power laser beams to form a barrier. Coming into contact with this structure may be harmful.</t>
+  </si>
+  <si>
+    <t>Provides basic protection for the base. Can be built in multiple layers. Cheap, reliable and sturdy.</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/wall_small_lvl_1</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/wall_small_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/wall_small_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/wall_energy_lvl_1</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/wall_energy_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/wall_energy_lvl_3</t>
+  </si>
+  <si>
+    <t>Reinforced conrete wall. Increased physical resistence but fragile to acid and area damage</t>
+  </si>
+  <si>
+    <t>Tought reinforced conrete wall. High physical resistence but fragile to acid and area damage</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/wall_crystal_lvl_1</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/wall_crystal_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/wall_crystal_lvl_3</t>
+  </si>
+  <si>
+    <t>Reistant to fire and acid damage but sensible to area damage. Shatters on destruction dealing damage to nearby enemies.</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/wall_vine_lvl_1</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/wall_vine_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/wall_vine_lvl_3</t>
+  </si>
+  <si>
+    <t>These walls automatically recede into the ground when the Mech is close to them. This allows the user to shoot over them with ease and negates the need for building gates. Resistant to area and acid damage but very fragile to fire damage. The walls also regenerate missing hit points over time, but do not reconstruct from ruins by themselves.</t>
+  </si>
+  <si>
+    <t>A defensive wall made from synthesized crystals found in the depths of the Galatean cavern network. When destroyed the wall will shatter and its shards will damage the nearby creatures.</t>
+  </si>
+  <si>
+    <t>Advanced powered regenerating energy barrier. Highly resistant to energy and cryo damage but very fragile to physical and sensitve to fire and acid damage. Deals damage on contact.</t>
+  </si>
+  <si>
+    <t>Tought powered regenerating energy barrier. Highly resistant to energy and cryo damage but very fragile to physical and sensitve to fire and acid damage. Deals damage on contact.</t>
+  </si>
+  <si>
+    <t>Resistant to area and acid damage but very  fragile to fire damage. Regenerates health and recedes when Mech passes by.</t>
+  </si>
+  <si>
+    <t>gui/menu/planetary_scanner/base_info_buildings_liquids</t>
+  </si>
+  <si>
+    <t>Liquids and gas builings:</t>
+  </si>
+  <si>
+    <t>Crystalizes Ferdonite from Carbonium and Water. Requires carbonium deposit as crystal seed but does not consume the deposit.</t>
+  </si>
+  <si>
+    <t>Crystalizes Tanzanite from Ammonium and Flammable Gas. Requires ammonium deposit as crystal seed but does not consume the deposit.</t>
+  </si>
+  <si>
+    <t>Crystalizes Hazenite from Ironium and Fluorine. Requires ironium deposit as crystal seed but does not consume the deposit.</t>
+  </si>
+  <si>
+    <t>Crystalizes Rhodonite from Ironium and Fluorine. Requires carbonium deposit as crystal seed but does not consume the deposit.</t>
+  </si>
+  <si>
+    <t>Crystalizes Ferdonite from Carbonium Water and Supercoolant. Requires carbonium deposit as crystal seed but does not consume the deposit.</t>
+  </si>
+  <si>
+    <t>Crystalizes Hazenite from Ironium Fluorine and Reagent. Requires ironium deposit as crystal seed but does not consume the deposit.</t>
+  </si>
+  <si>
+    <t>Crystalizes Rhodonite from Ironium Fluorine and Nitric Acid. Requires carbonium deposit as crystal seed but does not consume the deposit.</t>
+  </si>
+  <si>
+    <t>Crystalizes Tanzanite from Ammonium Flammable Gas and Plasma. Requires ammonium deposit as crystal seed but does not consume the deposit.</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/crystalizer_ferdonite_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/crystalizer_hazenite_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/crystalizer_rhodonite_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/crystalizer_tanzanite_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/crystalizer_ferdonite_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/crystalizer_hazenite_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/crystalizer_rhodonite_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/crystalizer_tanzanite_lvl_3</t>
+  </si>
+  <si>
+    <t>Advanced Energy Cell Optimization</t>
+  </si>
+  <si>
+    <t>Advanced High Caliber Optimization</t>
+  </si>
+  <si>
+    <t>Advanced Low Caliber Optimization</t>
+  </si>
+  <si>
+    <t>High-Tech Energy Cell Optimization</t>
+  </si>
+  <si>
+    <t>High-Tech High Caliber Optimization</t>
+  </si>
+  <si>
+    <t>High-Tech Low Caliber Optimization</t>
+  </si>
+  <si>
+    <t>Advanced Explosives Optimization</t>
+  </si>
+  <si>
+    <t>High-Tech Explosives Optimization</t>
+  </si>
+  <si>
+    <t>Advanced Liquid Ammunitions Optimization</t>
+  </si>
+  <si>
+    <t>High-Tech Liquid Ammunitions Optimization</t>
+  </si>
+  <si>
+    <t>Production of high capacity energy cells build from locally available resources</t>
+  </si>
+  <si>
+    <t>Adaptation of high capacity energy cells production to optimize yield</t>
+  </si>
+  <si>
+    <t>Adaptation of advanced high caliber rounds production to optimize yield</t>
+  </si>
+  <si>
+    <t>Adaptation of high explosive warheads production to optimize yield</t>
+  </si>
+  <si>
+    <t>Production of high explosive warheads from locally available resources for weapons like granade and missile launchers</t>
+  </si>
+  <si>
+    <t>Production of advanced high caliber rounds assembled from locally available resources for weapons like cannons</t>
+  </si>
+  <si>
+    <t>Production of highly reactive liquid munitions from locally available resources for weapons like flame throwers</t>
+  </si>
+  <si>
+    <t>Production of advanced low caliber rounds assembled from locally available resources for weapons like machine guns</t>
+  </si>
+  <si>
+    <t>Production of high-tech overcharged energy cell for top end energy weapons</t>
+  </si>
+  <si>
+    <t>Adaptation of high-tech overcharged energy cell production to optimize yield</t>
+  </si>
+  <si>
+    <t>Adaptation of high-tech explosives warhead production to optimize yield</t>
+  </si>
+  <si>
+    <t>Production of high-tech explosives warheads for top end weapons like granade and missile launchers</t>
+  </si>
+  <si>
+    <t>Production of high-tech high caliber rounds for top end weapons like cannons</t>
+  </si>
+  <si>
+    <t>Adaptation of high-tech high caliber round production to optimize yield</t>
+  </si>
+  <si>
+    <t>Production of high-tech liquid ammunitions for top end liquid based weapons like flame throwers</t>
+  </si>
+  <si>
+    <t>Adaptation of high-tech liquid ammunition production to optimize yield</t>
+  </si>
+  <si>
+    <t>Production of high-tech low caliber rounds for top end weapons like machine guns</t>
+  </si>
+  <si>
+    <t>Adaptation of high-tech low caliber round production to optimize yield</t>
+  </si>
+  <si>
+    <t>Adaptation of advanced low caliber round production to optimize yield</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/ammo_energy_cell_lvl2b</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/ammo_explosive_lvl2b</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/ammo_high_caliber_lvl2b</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/ammo_liquid_lvl2b</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/ammo_low_caliber_lvl2b</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/ammo_energy_cell_lvl2b</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/ammo_explosive_lvl2b</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/ammo_high_caliber_lvl2b</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/ammo_liquid_lvl2b</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/ammo_low_caliber_lvl2b</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/bio_cobalt_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/bio_titanium_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/bio_palladium_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/bio_uranium_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/bio_cobalt_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/bio_titanium_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/bio_palladium_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/bio_uranium_lvl_2</t>
+  </si>
+  <si>
+    <t>Improved Bio-Cobalt Extraction</t>
+  </si>
+  <si>
+    <t>Improved Bio-Titanium Extraction</t>
+  </si>
+  <si>
+    <t>Improved Bio-Palladium Extraction</t>
+  </si>
+  <si>
+    <t>Improved Bio-Uranium Extraction</t>
+  </si>
+  <si>
+    <t>Improving the method of trace cobalt from Galateas bio-matter.</t>
+  </si>
+  <si>
+    <t>Improving the method of trace uranium from Galateas bio-matter.</t>
+  </si>
+  <si>
+    <t>Improving the method of trace palladium from Galateas bio-matter.</t>
+  </si>
+  <si>
+    <t>Improving the method of trace titanium from Galateas bio-matter.</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/bio_cobalt_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/bio_titanium_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/bio_palladium_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/bio_uranium_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/bio_cobalt_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/bio_titanium_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/bio_palladium_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/bio_uranium_lvl_3</t>
+  </si>
+  <si>
+    <t>Perfected Bio-Cobalt Extraction</t>
+  </si>
+  <si>
+    <t>Perfected Bio-Titanium Extraction</t>
+  </si>
+  <si>
+    <t>Perfected Bio-Palladium Extraction</t>
+  </si>
+  <si>
+    <t>Perfected Bio-Uranium Extraction</t>
+  </si>
+  <si>
+    <t>Refines cobalt from bio-compounds and reagent fluid</t>
+  </si>
+  <si>
+    <t>Refines titanium from bio-compounds and reagent fluid</t>
+  </si>
+  <si>
+    <t>Refines uranium ore from bio-compounds and nitric acid</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/carbonium_powerplant_renewable</t>
+  </si>
+  <si>
+    <t>Must be built on top of Carbonium ore deposit. Reagent renders the deposit renewable and does not consume it. Can use only unrefined Carbonium straight from the ground.</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/deep_ionization</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/deep_ionization_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/deep_ionization_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/deep_ionization</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/deep_ionization_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/deep_ionization_lvl_3</t>
+  </si>
+  <si>
+    <t>Deep ionization</t>
+  </si>
+  <si>
+    <t>Advanced deep ionization</t>
+  </si>
+  <si>
+    <t>Extreme ionization</t>
+  </si>
+  <si>
+    <t>High energy physics allows the production of deeply ionized plasmas with strong electrical charge</t>
+  </si>
+  <si>
+    <t>Advanced techiques allow production of even deeper ionized plasmas carriying extreme charge</t>
+  </si>
+  <si>
+    <t>Production of superhot plasmas with total atomic ionization. Any more energy and the plasma becomes instable with fusion reactions emerging.</t>
   </si>
 </sst>
 </file>
@@ -3808,7 +4603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K517"/>
+  <dimension ref="A1:K654"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="65.453125" customWidth="1"/>
@@ -3882,10 +4677,10 @@
     </row>
     <row r="6" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>429</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3909,15 +4704,15 @@
         <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>571</v>
+        <v>542</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>567</v>
+        <v>538</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>572</v>
+        <v>543</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3946,10 +4741,10 @@
     </row>
     <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>430</v>
+        <v>407</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4002,4110 +4797,5215 @@
     </row>
     <row r="21" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>1030</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>42</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>1034</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>44</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>46</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>480</v>
+        <v>44</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>511</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>628</v>
+        <v>45</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>629</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>481</v>
+        <v>457</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>510</v>
+        <v>488</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>1099</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>721</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>943</v>
+        <v>599</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>946</v>
+        <v>600</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>942</v>
+        <v>458</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>972</v>
+        <v>487</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>948</v>
+        <v>46</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>973</v>
+        <v>692</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>944</v>
+        <v>1061</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>358</v>
+        <v>1232</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>439</v>
+        <v>1054</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>322</v>
+        <v>894</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>648</v>
+        <v>1154</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>1158</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>893</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>1155</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>355</v>
+        <v>1159</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>306</v>
+        <v>897</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>315</v>
+        <v>1156</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>316</v>
+        <v>1160</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>895</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>58</v>
+        <v>1157</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>1161</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>1065</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>62</v>
+        <v>335</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>61</v>
+        <v>337</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>63</v>
+        <v>416</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>61</v>
+        <v>465</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>599</v>
+        <v>992</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>600</v>
+        <v>995</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>602</v>
+        <v>1103</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>636</v>
+        <v>1077</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>642</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>644</v>
+        <v>619</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>643</v>
+        <v>620</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>645</v>
+        <v>47</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>647</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>361</v>
+        <v>49</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>371</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>363</v>
+        <v>51</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>372</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>364</v>
+        <v>1112</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>372</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>365</v>
+        <v>1113</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>372</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>914</v>
+        <v>332</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>917</v>
+        <v>327</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>915</v>
+        <v>285</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>918</v>
+        <v>296</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>916</v>
+        <v>294</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>918</v>
+        <v>297</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>666</v>
+        <v>295</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>673</v>
+        <v>297</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>667</v>
+        <v>53</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>671</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>663</v>
+        <v>55</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>672</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>824</v>
+        <v>56</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>825</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>325</v>
+        <v>57</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>333</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>65</v>
+        <v>571</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>68</v>
+        <v>572</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>69</v>
+        <v>573</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>691</v>
+        <v>607</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>633</v>
+        <v>613</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>690</v>
+        <v>615</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>692</v>
+        <v>614</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>689</v>
+        <v>616</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>693</v>
+        <v>618</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>70</v>
+        <v>338</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>71</v>
+        <v>339</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>72</v>
+        <v>340</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>73</v>
+        <v>349</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>459</v>
+        <v>341</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>489</v>
+        <v>349</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>460</v>
+        <v>342</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>490</v>
+        <v>349</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>467</v>
+        <v>974</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>496</v>
+        <v>991</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>468</v>
+        <v>978</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>497</v>
+        <v>989</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>74</v>
+        <v>979</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>432</v>
+        <v>865</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>431</v>
+        <v>866</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>433</v>
+        <v>867</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>437</v>
+        <v>637</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>531</v>
+        <v>638</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>465</v>
+        <v>634</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>466</v>
+        <v>793</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>461</v>
+        <v>303</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+        <v>306</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>463</v>
+        <v>61</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>464</v>
+        <v>63</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>462</v>
+        <v>64</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>471</v>
+        <v>1115</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>472</v>
+        <v>1117</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>473</v>
+        <v>1118</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>474</v>
+        <v>65</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>476</v>
+        <v>662</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>505</v>
+        <v>604</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>475</v>
+        <v>661</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>504</v>
+        <v>663</v>
       </c>
     </row>
     <row r="98" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>469</v>
+        <v>660</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>498</v>
+        <v>664</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>470</v>
+        <v>67</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>499</v>
+        <v>68</v>
       </c>
     </row>
     <row r="100" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>522</v>
+        <v>69</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>526</v>
+        <v>70</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>523</v>
+        <v>436</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>589</v>
+        <v>466</v>
       </c>
     </row>
     <row r="102" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>521</v>
+        <v>437</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>527</v>
+        <v>467</v>
       </c>
     </row>
     <row r="103" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>76</v>
+        <v>444</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>77</v>
+        <v>473</v>
       </c>
     </row>
     <row r="104" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>78</v>
+        <v>445</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>79</v>
+        <v>474</v>
       </c>
     </row>
     <row r="105" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="106" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>82</v>
+        <v>409</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>83</v>
+        <v>486</v>
       </c>
     </row>
     <row r="107" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>84</v>
+        <v>408</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>85</v>
+        <v>483</v>
       </c>
     </row>
     <row r="108" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>427</v>
+        <v>484</v>
       </c>
     </row>
     <row r="109" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>86</v>
+        <v>414</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>87</v>
+        <v>485</v>
       </c>
     </row>
     <row r="110" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>88</v>
+        <v>507</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>89</v>
+        <v>508</v>
       </c>
     </row>
     <row r="111" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>90</v>
+        <v>442</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>570</v>
+        <v>471</v>
       </c>
     </row>
     <row r="112" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>568</v>
+        <v>443</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>569</v>
+        <v>472</v>
       </c>
     </row>
     <row r="113" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>91</v>
+        <v>438</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>92</v>
+        <v>469</v>
       </c>
     </row>
     <row r="114" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>93</v>
+        <v>440</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>94</v>
+        <v>470</v>
       </c>
     </row>
     <row r="115" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>95</v>
+        <v>441</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>96</v>
+        <v>559</v>
       </c>
     </row>
     <row r="116" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>428</v>
+        <v>468</v>
       </c>
     </row>
     <row r="117" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>97</v>
+        <v>448</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>98</v>
+        <v>477</v>
       </c>
     </row>
     <row r="118" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>99</v>
+        <v>449</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>100</v>
+        <v>478</v>
       </c>
     </row>
     <row r="119" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>101</v>
+        <v>450</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>102</v>
+        <v>479</v>
       </c>
     </row>
     <row r="120" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>103</v>
+        <v>451</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>104</v>
+        <v>480</v>
       </c>
     </row>
     <row r="121" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>105</v>
+        <v>453</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>106</v>
+        <v>482</v>
       </c>
     </row>
     <row r="122" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>107</v>
+        <v>452</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>108</v>
+        <v>481</v>
       </c>
     </row>
     <row r="123" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>109</v>
+        <v>446</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>110</v>
+        <v>475</v>
       </c>
     </row>
     <row r="124" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>111</v>
+        <v>447</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>112</v>
+        <v>476</v>
       </c>
     </row>
     <row r="125" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>113</v>
+        <v>498</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>114</v>
+        <v>502</v>
       </c>
     </row>
     <row r="126" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>115</v>
+        <v>499</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>116</v>
+        <v>560</v>
       </c>
     </row>
     <row r="127" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
     </row>
     <row r="128" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>623</v>
+        <v>1132</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>478</v>
+        <v>1133</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>117</v>
+        <v>1134</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>930</v>
+        <v>1127</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>929</v>
+        <v>1128</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>949</v>
+        <v>1129</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>931</v>
+        <v>1124</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>357</v>
+        <v>1125</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>440</v>
+        <v>1126</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>323</v>
+        <v>1136</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>326</v>
+        <v>1137</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>327</v>
+        <v>1138</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>634</v>
+        <v>73</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>356</v>
+        <v>77</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>307</v>
+        <v>79</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>308</v>
+        <v>81</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>309</v>
+        <v>400</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>126</v>
+        <v>539</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>603</v>
+        <v>88</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>366</v>
+        <v>90</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>367</v>
+        <v>92</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>368</v>
+        <v>401</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>369</v>
+        <v>94</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>909</v>
+        <v>96</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>911</v>
+        <v>98</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>912</v>
+        <v>100</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>664</v>
+        <v>102</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>665</v>
+        <v>104</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>662</v>
+        <v>1031</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>669</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="161" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>826</v>
+        <v>106</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>827</v>
+        <v>107</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>311</v>
+        <v>112</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>312</v>
+        <v>113</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>310</v>
+        <v>454</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>313</v>
+        <v>462</v>
       </c>
     </row>
     <row r="166" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>677</v>
+        <v>1098</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>676</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="167" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>674</v>
+        <v>594</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>678</v>
+        <v>595</v>
       </c>
     </row>
     <row r="168" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>675</v>
+        <v>455</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>679</v>
+        <v>463</v>
       </c>
     </row>
     <row r="169" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>441</v>
+        <v>114</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>579</v>
+        <v>115</v>
       </c>
     </row>
     <row r="170" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>442</v>
+        <v>1062</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>578</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="171" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>449</v>
+        <v>1055</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>577</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="172" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>450</v>
+        <v>881</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>576</v>
+        <v>884</v>
       </c>
     </row>
     <row r="173" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>131</v>
+        <v>880</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>132</v>
+        <v>883</v>
       </c>
     </row>
     <row r="174" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>435</v>
+        <v>898</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>590</v>
+        <v>886</v>
       </c>
     </row>
     <row r="175" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>434</v>
+        <v>882</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>573</v>
+        <v>885</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>436</v>
+        <v>1066</v>
       </c>
       <c r="B176" s="1" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>334</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>417</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>993</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>302</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>304</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>305</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>605</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>116</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>333</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>286</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>287</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>288</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>118</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>120</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>122</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>123</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="177" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A177" t="s">
-        <v>438</v>
-      </c>
-      <c r="B177" s="1" t="s">
+      <c r="B195" s="1" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="178" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A178" t="s">
-        <v>818</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A179" t="s">
-        <v>819</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A180" t="s">
-        <v>528</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A181" t="s">
-        <v>447</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A182" t="s">
-        <v>448</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A183" t="s">
-        <v>444</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A184" t="s">
-        <v>445</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A185" t="s">
-        <v>446</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A186" t="s">
-        <v>443</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A187" t="s">
-        <v>453</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A188" t="s">
-        <v>454</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A189" t="s">
-        <v>455</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A190" t="s">
-        <v>456</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A191" t="s">
-        <v>458</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A192" t="s">
-        <v>457</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A193" t="s">
-        <v>451</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A194" t="s">
-        <v>452</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A195" t="s">
-        <v>518</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>520</v>
+        <v>343</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>350</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>519</v>
+        <v>344</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>350</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>133</v>
+        <v>345</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>350</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>524</v>
+        <v>346</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>351</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>512</v>
+        <v>975</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
+        <v>976</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
         <v>977</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A202" t="s">
-        <v>978</v>
-      </c>
       <c r="B202" s="1" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>979</v>
+        <v>860</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>980</v>
+        <v>862</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>886</v>
+        <v>863</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>842</v>
+        <v>635</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>843</v>
+        <v>636</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>547</v>
+        <v>633</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>557</v>
+        <v>640</v>
       </c>
     </row>
     <row r="209" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>548</v>
+        <v>795</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>699</v>
+        <v>796</v>
       </c>
     </row>
     <row r="210" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>704</v>
+        <v>124</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>560</v>
+        <v>125</v>
       </c>
     </row>
     <row r="211" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>549</v>
+        <v>1114</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>563</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="212" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>550</v>
+        <v>126</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>700</v>
+        <v>127</v>
       </c>
     </row>
     <row r="213" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>705</v>
+        <v>290</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>565</v>
+        <v>291</v>
       </c>
     </row>
     <row r="214" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>551</v>
+        <v>289</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>558</v>
+        <v>292</v>
       </c>
     </row>
     <row r="215" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>701</v>
+        <v>647</v>
       </c>
     </row>
     <row r="216" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>706</v>
+        <v>645</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>561</v>
+        <v>649</v>
       </c>
     </row>
     <row r="217" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>553</v>
+        <v>646</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>564</v>
+        <v>650</v>
       </c>
     </row>
     <row r="218" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>554</v>
+        <v>418</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>702</v>
+        <v>550</v>
       </c>
     </row>
     <row r="219" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>707</v>
+        <v>419</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>566</v>
+        <v>549</v>
       </c>
     </row>
     <row r="220" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>555</v>
+        <v>426</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
     </row>
     <row r="221" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>556</v>
+        <v>427</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>703</v>
+        <v>547</v>
       </c>
     </row>
     <row r="222" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>708</v>
+        <v>128</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>562</v>
+        <v>129</v>
       </c>
     </row>
     <row r="223" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>135</v>
+        <v>412</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>136</v>
+        <v>561</v>
       </c>
     </row>
     <row r="224" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>137</v>
+        <v>411</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>138</v>
+        <v>544</v>
       </c>
     </row>
     <row r="225" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>139</v>
+        <v>413</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>140</v>
+        <v>545</v>
       </c>
     </row>
     <row r="226" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>141</v>
+        <v>415</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>140</v>
+        <v>546</v>
       </c>
     </row>
     <row r="227" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>142</v>
+        <v>787</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>140</v>
+        <v>785</v>
       </c>
     </row>
     <row r="228" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>650</v>
+        <v>788</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>657</v>
+        <v>786</v>
       </c>
     </row>
     <row r="229" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>654</v>
+        <v>504</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>658</v>
+        <v>505</v>
       </c>
     </row>
     <row r="230" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>655</v>
+        <v>424</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>659</v>
+        <v>562</v>
       </c>
     </row>
     <row r="231" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>143</v>
+        <v>425</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>144</v>
+        <v>563</v>
       </c>
     </row>
     <row r="232" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>145</v>
+        <v>421</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>728</v>
+        <v>422</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>731</v>
+        <v>565</v>
       </c>
     </row>
     <row r="234" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>729</v>
+        <v>423</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>730</v>
+        <v>420</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>740</v>
+        <v>567</v>
       </c>
     </row>
     <row r="236" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>514</v>
+        <v>430</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>515</v>
+        <v>460</v>
       </c>
     </row>
     <row r="237" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>620</v>
+        <v>431</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>632</v>
+        <v>551</v>
       </c>
     </row>
     <row r="238" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>621</v>
+        <v>432</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>622</v>
+        <v>552</v>
       </c>
     </row>
     <row r="239" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>627</v>
+        <v>433</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>686</v>
+        <v>553</v>
       </c>
     </row>
     <row r="240" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>684</v>
+        <v>435</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>685</v>
+        <v>434</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>940</v>
+        <v>428</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>946</v>
+        <v>554</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>964</v>
+        <v>429</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>946</v>
+        <v>555</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>968</v>
+        <v>494</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>946</v>
+        <v>557</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>939</v>
+        <v>496</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>972</v>
+        <v>506</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>965</v>
+        <v>495</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>972</v>
+        <v>556</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>969</v>
+        <v>130</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>972</v>
+        <v>131</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>947</v>
+        <v>1049</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>973</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>966</v>
+        <v>500</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>973</v>
+        <v>501</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>970</v>
+        <v>489</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>973</v>
+        <v>490</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>941</v>
+        <v>1047</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>945</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>967</v>
+        <v>924</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>945</v>
+        <v>857</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>971</v>
+        <v>925</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>945</v>
+        <v>859</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>844</v>
+        <v>926</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>845</v>
+        <v>858</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>836</v>
+        <v>927</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>833</v>
+        <v>856</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>835</v>
+        <v>855</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>834</v>
+        <v>854</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>735</v>
+        <v>1144</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>738</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>147</v>
+        <v>972</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>148</v>
+        <v>973</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>149</v>
+        <v>811</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>150</v>
+        <v>815</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>151</v>
+        <v>812</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>152</v>
+        <v>816</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>153</v>
+        <v>523</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>154</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>155</v>
+        <v>1191</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>156</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>157</v>
+        <v>524</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>158</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>159</v>
+        <v>675</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>160</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>161</v>
+        <v>525</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>162</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>163</v>
+        <v>1192</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>164</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>165</v>
+        <v>526</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>166</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>167</v>
+        <v>676</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>168</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>169</v>
+        <v>527</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>170</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>171</v>
+        <v>1193</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>173</v>
+        <v>528</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>174</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>175</v>
+        <v>677</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>176</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>177</v>
+        <v>529</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>178</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>179</v>
+        <v>1194</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>180</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>181</v>
+        <v>530</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>182</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>776</v>
+        <v>678</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>770</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>777</v>
+        <v>531</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>771</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>778</v>
+        <v>1195</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>772</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>779</v>
+        <v>532</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>758</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>780</v>
+        <v>679</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>759</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>781</v>
+        <v>1042</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>760</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>782</v>
+        <v>1041</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>764</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>783</v>
+        <v>1026</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>765</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>784</v>
+        <v>1027</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>766</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>791</v>
+        <v>132</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>761</v>
+        <v>133</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>792</v>
+        <v>1205</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>762</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>793</v>
+        <v>1221</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>763</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>785</v>
+        <v>134</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>773</v>
+        <v>135</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>786</v>
+        <v>1207</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>774</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>787</v>
+        <v>1223</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>775</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>788</v>
+        <v>136</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>767</v>
+        <v>137</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>789</v>
+        <v>138</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>768</v>
+        <v>137</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>790</v>
+        <v>139</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>769</v>
+        <v>137</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>380</v>
+        <v>621</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>597</v>
+        <v>628</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>385</v>
+        <v>625</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>389</v>
+        <v>629</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>386</v>
+        <v>626</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>388</v>
+        <v>630</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>605</v>
+        <v>140</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>606</v>
+        <v>141</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>607</v>
+        <v>1206</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>606</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>412</v>
+        <v>1222</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>420</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>414</v>
+        <v>142</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>421</v>
+        <v>143</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>416</v>
+        <v>1208</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>422</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>734</v>
+        <v>1224</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>737</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>390</v>
+        <v>699</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>393</v>
+        <v>702</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>397</v>
+        <v>700</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>394</v>
+        <v>710</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>399</v>
+        <v>701</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>394</v>
+        <v>711</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>921</v>
+        <v>491</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>928</v>
+        <v>492</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>920</v>
+        <v>1097</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>917</v>
+        <v>493</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>919</v>
+        <v>591</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>928</v>
+        <v>603</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>828</v>
+        <v>592</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>830</v>
+        <v>593</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>183</v>
+        <v>1052</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>184</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>185</v>
+        <v>1053</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>186</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>748</v>
+        <v>971</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>714</v>
+        <v>967</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>749</v>
+        <v>958</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>713</v>
+        <v>967</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>750</v>
+        <v>959</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>745</v>
+        <v>967</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>820</v>
+        <v>960</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>822</v>
+        <v>967</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>821</v>
+        <v>952</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>823</v>
+        <v>968</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>751</v>
+        <v>953</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>747</v>
+        <v>968</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>752</v>
+        <v>951</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>746</v>
+        <v>968</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>742</v>
+        <v>954</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>741</v>
+        <v>968</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>860</v>
+        <v>598</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>862</v>
+        <v>657</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>861</v>
+        <v>655</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>862</v>
+        <v>658</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>534</v>
+        <v>656</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>536</v>
+        <v>659</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>873</v>
+        <v>891</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>882</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>874</v>
+        <v>913</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>883</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>875</v>
+        <v>917</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>884</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>720</v>
+        <v>890</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>712</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>401</v>
+        <v>914</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>404</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>794</v>
+        <v>918</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>598</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>409</v>
+        <v>896</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="330" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>848</v>
+        <v>915</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>837</v>
+        <v>919</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>840</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>838</v>
+        <v>892</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>841</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>537</v>
+        <v>916</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>557</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>538</v>
+        <v>920</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>699</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>698</v>
+        <v>1237</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>560</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>539</v>
+        <v>1238</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>563</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>540</v>
+        <v>1239</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>700</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>697</v>
+        <v>813</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>565</v>
+        <v>814</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>541</v>
+        <v>994</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>558</v>
+        <v>995</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>542</v>
+        <v>1092</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>701</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>696</v>
+        <v>1093</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>561</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>543</v>
+        <v>805</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>564</v>
+        <v>802</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>544</v>
+        <v>804</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>702</v>
+        <v>803</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>566</v>
+        <v>709</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>545</v>
+        <v>144</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>559</v>
+        <v>145</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>546</v>
+        <v>146</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>703</v>
+        <v>147</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>694</v>
+        <v>148</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>562</v>
+        <v>149</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>193</v>
+        <v>156</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>194</v>
+        <v>157</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>196</v>
+        <v>159</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>651</v>
+        <v>160</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>656</v>
+        <v>161</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>652</v>
+        <v>162</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>660</v>
+        <v>163</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>653</v>
+        <v>164</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>661</v>
+        <v>165</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>199</v>
+        <v>168</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>722</v>
+        <v>170</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>725</v>
+        <v>171</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>723</v>
+        <v>172</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>726</v>
+        <v>173</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>724</v>
+        <v>174</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>727</v>
+        <v>175</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>516</v>
+        <v>176</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>517</v>
+        <v>177</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>616</v>
+        <v>178</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>618</v>
+        <v>179</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>617</v>
+        <v>745</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>619</v>
+        <v>739</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>625</v>
+        <v>746</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>626</v>
+        <v>740</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>680</v>
+        <v>747</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>682</v>
+        <v>741</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>681</v>
+        <v>748</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>683</v>
+        <v>727</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>937</v>
+        <v>749</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>933</v>
+        <v>728</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>950</v>
+        <v>750</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>953</v>
+        <v>729</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>957</v>
+        <v>751</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>960</v>
+        <v>733</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>936</v>
+        <v>752</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>932</v>
+        <v>734</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>951</v>
+        <v>753</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>954</v>
+        <v>735</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>958</v>
+        <v>760</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>961</v>
+        <v>730</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>974</v>
+        <v>761</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>935</v>
+        <v>731</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>975</v>
+        <v>762</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>955</v>
+        <v>732</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>976</v>
+        <v>754</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>962</v>
+        <v>742</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>938</v>
+        <v>755</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>934</v>
+        <v>743</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>952</v>
+        <v>756</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>956</v>
+        <v>744</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>959</v>
+        <v>757</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>963</v>
+        <v>736</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>839</v>
+        <v>758</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>482</v>
+        <v>737</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>831</v>
+        <v>759</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>833</v>
+        <v>738</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>832</v>
+        <v>1082</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>834</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>733</v>
+        <v>1083</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>736</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>201</v>
+        <v>357</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>202</v>
+        <v>568</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>203</v>
+        <v>362</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>204</v>
+        <v>366</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>205</v>
+        <v>363</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>206</v>
+        <v>365</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>207</v>
+        <v>955</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>208</v>
+        <v>966</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>209</v>
+        <v>956</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>210</v>
+        <v>966</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>211</v>
+        <v>957</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>212</v>
+        <v>966</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>213</v>
+        <v>964</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>160</v>
+        <v>966</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>214</v>
+        <v>965</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>162</v>
+        <v>966</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>215</v>
+        <v>576</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>164</v>
+        <v>577</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>216</v>
+        <v>578</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>166</v>
+        <v>577</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>217</v>
+        <v>389</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>168</v>
+        <v>397</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>218</v>
+        <v>391</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>170</v>
+        <v>398</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>219</v>
+        <v>393</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>172</v>
+        <v>399</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>220</v>
+        <v>705</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>174</v>
+        <v>708</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>221</v>
+        <v>367</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>176</v>
+        <v>370</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>222</v>
+        <v>374</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>178</v>
+        <v>371</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>223</v>
+        <v>376</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>180</v>
+        <v>371</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>224</v>
+        <v>980</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>182</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>795</v>
+        <v>981</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>865</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>796</v>
+        <v>982</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>771</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>797</v>
+        <v>872</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>772</v>
+        <v>879</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>798</v>
+        <v>871</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>799</v>
+        <v>870</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>759</v>
+        <v>879</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>760</v>
+        <v>799</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>801</v>
+        <v>180</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>867</v>
+        <v>181</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>802</v>
+        <v>182</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>765</v>
+        <v>183</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>803</v>
+        <v>719</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>766</v>
+        <v>684</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>804</v>
+        <v>720</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>868</v>
+        <v>716</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>762</v>
+        <v>791</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>806</v>
+        <v>790</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>763</v>
+        <v>792</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>807</v>
+        <v>721</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>869</v>
+        <v>718</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>808</v>
+        <v>722</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>774</v>
+        <v>717</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>809</v>
+        <v>713</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>775</v>
+        <v>712</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>810</v>
+        <v>929</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>870</v>
+        <v>685</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>811</v>
+        <v>829</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>768</v>
+        <v>831</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>812</v>
+        <v>830</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>769</v>
+        <v>831</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>379</v>
+        <v>510</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>381</v>
+        <v>512</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>384</v>
+        <v>842</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>382</v>
+        <v>851</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>387</v>
+        <v>843</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>383</v>
+        <v>852</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>608</v>
+        <v>844</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>609</v>
+        <v>853</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>610</v>
+        <v>691</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>611</v>
+        <v>683</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>635</v>
+        <v>997</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>638</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>639</v>
+        <v>998</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>641</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>640</v>
+        <v>378</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>646</v>
+        <v>381</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>411</v>
+        <v>763</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>417</v>
+        <v>569</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>413</v>
+        <v>386</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>418</v>
+        <v>387</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>415</v>
+        <v>817</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>419</v>
+        <v>818</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>732</v>
+        <v>806</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>669</v>
+        <v>809</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>391</v>
+        <v>807</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>392</v>
+        <v>810</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>398</v>
+        <v>513</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>395</v>
+        <v>533</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>400</v>
+        <v>1196</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>396</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>924</v>
+        <v>514</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>925</v>
+        <v>670</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>922</v>
+        <v>669</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>926</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>923</v>
+        <v>515</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>927</v>
+        <v>536</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>829</v>
+        <v>1197</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>827</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>225</v>
+        <v>516</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>226</v>
+        <v>671</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>227</v>
+        <v>668</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>228</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>753</v>
+        <v>517</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>716</v>
+        <v>534</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>754</v>
+        <v>1198</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>715</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>755</v>
+        <v>518</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>590</v>
+        <v>672</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>813</v>
+        <v>667</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>573</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>756</v>
+        <v>519</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>574</v>
+        <v>537</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>757</v>
+        <v>1199</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>575</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>814</v>
+        <v>520</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>816</v>
+        <v>673</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>815</v>
+        <v>666</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>817</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>744</v>
+        <v>521</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>743</v>
+        <v>535</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>872</v>
+        <v>1200</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>863</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>871</v>
+        <v>522</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>864</v>
+        <v>674</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>533</v>
+        <v>665</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>535</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>876</v>
+        <v>1040</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>881</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>877</v>
+        <v>1039</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>880</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>878</v>
+        <v>1028</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>879</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>719</v>
+        <v>1029</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>709</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>717</v>
+        <v>184</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>710</v>
+        <v>185</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>718</v>
+        <v>1201</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>711</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>402</v>
+        <v>1217</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>403</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>407</v>
+        <v>186</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>405</v>
+        <v>187</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>408</v>
+        <v>1203</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>406</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>229</v>
+        <v>1219</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>892</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>891</v>
+        <v>189</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>231</v>
+        <v>190</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>890</v>
+        <v>191</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
+        <v>192</v>
+      </c>
+      <c r="B464" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A465" t="s">
+        <v>622</v>
+      </c>
+      <c r="B465" s="1" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A466" t="s">
+        <v>623</v>
+      </c>
+      <c r="B466" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A467" t="s">
+        <v>624</v>
+      </c>
+      <c r="B467" s="1" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A468" t="s">
+        <v>194</v>
+      </c>
+      <c r="B468" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A469" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B469" s="1" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A470" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B470" s="1" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A471" t="s">
+        <v>196</v>
+      </c>
+      <c r="B471" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A472" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B472" s="1" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A473" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B473" s="1" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A474" t="s">
+        <v>693</v>
+      </c>
+      <c r="B474" s="1" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A475" t="s">
+        <v>694</v>
+      </c>
+      <c r="B475" s="1" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A476" t="s">
+        <v>695</v>
+      </c>
+      <c r="B476" s="1" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A477" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B477" s="1" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A478" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B478" s="1" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A479" t="s">
+        <v>587</v>
+      </c>
+      <c r="B479" s="1" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A480" t="s">
+        <v>588</v>
+      </c>
+      <c r="B480" s="1" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A481" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B481" s="1" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A482" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B482" s="1" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A483" t="s">
+        <v>969</v>
+      </c>
+      <c r="B483" s="1" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A484" t="s">
+        <v>945</v>
+      </c>
+      <c r="B484" s="1" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A485" t="s">
+        <v>946</v>
+      </c>
+      <c r="B485" s="1" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A486" t="s">
+        <v>947</v>
+      </c>
+      <c r="B486" s="1" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A487" t="s">
+        <v>930</v>
+      </c>
+      <c r="B487" s="1" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A488" t="s">
+        <v>931</v>
+      </c>
+      <c r="B488" s="1" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A489" t="s">
+        <v>932</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A490" t="s">
+        <v>933</v>
+      </c>
+      <c r="B490" s="1" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A491" t="s">
+        <v>596</v>
+      </c>
+      <c r="B491" s="1" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A492" t="s">
+        <v>651</v>
+      </c>
+      <c r="B492" s="1" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A493" t="s">
+        <v>652</v>
+      </c>
+      <c r="B493" s="1" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A494" t="s">
+        <v>888</v>
+      </c>
+      <c r="B494" s="1" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A495" t="s">
+        <v>899</v>
+      </c>
+      <c r="B495" s="1" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A496" t="s">
+        <v>906</v>
+      </c>
+      <c r="B496" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A497" t="s">
+        <v>887</v>
+      </c>
+      <c r="B497" s="1" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A498" t="s">
+        <v>900</v>
+      </c>
+      <c r="B498" s="1" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A499" t="s">
+        <v>907</v>
+      </c>
+      <c r="B499" s="1" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A500" t="s">
+        <v>921</v>
+      </c>
+      <c r="B500" s="1" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A501" t="s">
+        <v>922</v>
+      </c>
+      <c r="B501" s="1" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A502" t="s">
+        <v>923</v>
+      </c>
+      <c r="B502" s="1" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A503" t="s">
+        <v>889</v>
+      </c>
+      <c r="B503" s="1" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A504" t="s">
+        <v>901</v>
+      </c>
+      <c r="B504" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A505" t="s">
+        <v>908</v>
+      </c>
+      <c r="B505" s="1" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A506" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B506" s="1" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A507" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B507" s="1" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A508" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B508" s="1" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A509" t="s">
+        <v>808</v>
+      </c>
+      <c r="B509" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A510" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B510" s="1" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A511" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B511" s="1" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A512" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B512" s="1" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A513" t="s">
+        <v>800</v>
+      </c>
+      <c r="B513" s="1" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A514" t="s">
+        <v>801</v>
+      </c>
+      <c r="B514" s="1" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A515" t="s">
+        <v>704</v>
+      </c>
+      <c r="B515" s="1" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A516" t="s">
+        <v>198</v>
+      </c>
+      <c r="B516" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A517" t="s">
+        <v>200</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A518" t="s">
+        <v>202</v>
+      </c>
+      <c r="B518" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A519" t="s">
+        <v>204</v>
+      </c>
+      <c r="B519" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A520" t="s">
+        <v>206</v>
+      </c>
+      <c r="B520" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A521" t="s">
+        <v>208</v>
+      </c>
+      <c r="B521" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A522" t="s">
+        <v>210</v>
+      </c>
+      <c r="B522" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A523" t="s">
+        <v>211</v>
+      </c>
+      <c r="B523" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A524" t="s">
+        <v>212</v>
+      </c>
+      <c r="B524" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A525" t="s">
+        <v>213</v>
+      </c>
+      <c r="B525" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A526" t="s">
+        <v>214</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A527" t="s">
+        <v>215</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A528" t="s">
+        <v>216</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A529" t="s">
+        <v>217</v>
+      </c>
+      <c r="B529" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A530" t="s">
+        <v>218</v>
+      </c>
+      <c r="B530" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A531" t="s">
+        <v>219</v>
+      </c>
+      <c r="B531" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A532" t="s">
+        <v>220</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A533" t="s">
+        <v>221</v>
+      </c>
+      <c r="B533" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A534" t="s">
+        <v>764</v>
+      </c>
+      <c r="B534" s="1" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A535" t="s">
+        <v>765</v>
+      </c>
+      <c r="B535" s="1" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A536" t="s">
+        <v>766</v>
+      </c>
+      <c r="B536" s="1" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A537" t="s">
+        <v>767</v>
+      </c>
+      <c r="B537" s="1" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A538" t="s">
+        <v>768</v>
+      </c>
+      <c r="B538" s="1" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A539" t="s">
+        <v>769</v>
+      </c>
+      <c r="B539" s="1" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A540" t="s">
+        <v>770</v>
+      </c>
+      <c r="B540" s="1" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A541" t="s">
+        <v>771</v>
+      </c>
+      <c r="B541" s="1" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A542" t="s">
+        <v>772</v>
+      </c>
+      <c r="B542" s="1" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A543" t="s">
+        <v>773</v>
+      </c>
+      <c r="B543" s="1" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A544" t="s">
+        <v>774</v>
+      </c>
+      <c r="B544" s="1" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A545" t="s">
+        <v>775</v>
+      </c>
+      <c r="B545" s="1" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A546" t="s">
+        <v>776</v>
+      </c>
+      <c r="B546" s="1" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A547" t="s">
+        <v>777</v>
+      </c>
+      <c r="B547" s="1" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A548" t="s">
+        <v>778</v>
+      </c>
+      <c r="B548" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A549" t="s">
+        <v>779</v>
+      </c>
+      <c r="B549" s="1" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A550" t="s">
+        <v>780</v>
+      </c>
+      <c r="B550" s="1" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A551" t="s">
+        <v>781</v>
+      </c>
+      <c r="B551" s="1" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A552" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B552" s="1" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A553" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B553" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A554" t="s">
+        <v>356</v>
+      </c>
+      <c r="B554" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A555" t="s">
+        <v>361</v>
+      </c>
+      <c r="B555" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A556" t="s">
+        <v>364</v>
+      </c>
+      <c r="B556" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A557" t="s">
+        <v>943</v>
+      </c>
+      <c r="B557" s="1" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A558" t="s">
+        <v>938</v>
+      </c>
+      <c r="B558" s="1" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A559" t="s">
+        <v>939</v>
+      </c>
+      <c r="B559" s="1" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A560" t="s">
+        <v>940</v>
+      </c>
+      <c r="B560" s="1" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A561" t="s">
+        <v>962</v>
+      </c>
+      <c r="B561" s="1" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A562" t="s">
+        <v>579</v>
+      </c>
+      <c r="B562" s="1" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A563" t="s">
+        <v>581</v>
+      </c>
+      <c r="B563" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A564" t="s">
+        <v>606</v>
+      </c>
+      <c r="B564" s="1" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A565" t="s">
+        <v>610</v>
+      </c>
+      <c r="B565" s="1" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A566" t="s">
+        <v>611</v>
+      </c>
+      <c r="B566" s="1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A567" t="s">
+        <v>388</v>
+      </c>
+      <c r="B567" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A568" t="s">
+        <v>390</v>
+      </c>
+      <c r="B568" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A569" t="s">
+        <v>392</v>
+      </c>
+      <c r="B569" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A570" t="s">
+        <v>703</v>
+      </c>
+      <c r="B570" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A571" t="s">
+        <v>368</v>
+      </c>
+      <c r="B571" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A572" t="s">
+        <v>375</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A573" t="s">
+        <v>377</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A574" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A575" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B575" s="1" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A576" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A577" t="s">
+        <v>875</v>
+      </c>
+      <c r="B577" s="1" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A578" t="s">
+        <v>873</v>
+      </c>
+      <c r="B578" s="1" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A579" t="s">
+        <v>874</v>
+      </c>
+      <c r="B579" s="1" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A580" t="s">
+        <v>798</v>
+      </c>
+      <c r="B580" s="1" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A581" t="s">
+        <v>222</v>
+      </c>
+      <c r="B581" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A582" t="s">
+        <v>224</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A583" t="s">
+        <v>723</v>
+      </c>
+      <c r="B583" s="1" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A584" t="s">
+        <v>724</v>
+      </c>
+      <c r="B584" s="1" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A585" t="s">
+        <v>782</v>
+      </c>
+      <c r="B585" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A586" t="s">
+        <v>725</v>
+      </c>
+      <c r="B586" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A587" t="s">
+        <v>726</v>
+      </c>
+      <c r="B587" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A588" t="s">
+        <v>783</v>
+      </c>
+      <c r="B588" s="1" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A589" t="s">
+        <v>784</v>
+      </c>
+      <c r="B589" s="1" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A590" t="s">
+        <v>715</v>
+      </c>
+      <c r="B590" s="1" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A591" t="s">
+        <v>928</v>
+      </c>
+      <c r="B591" s="1" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A592" t="s">
+        <v>841</v>
+      </c>
+      <c r="B592" s="1" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A593" t="s">
+        <v>840</v>
+      </c>
+      <c r="B593" s="1" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A594" t="s">
+        <v>509</v>
+      </c>
+      <c r="B594" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A595" t="s">
+        <v>845</v>
+      </c>
+      <c r="B595" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A596" t="s">
+        <v>846</v>
+      </c>
+      <c r="B596" s="1" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A597" t="s">
+        <v>847</v>
+      </c>
+      <c r="B597" s="1" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A598" t="s">
+        <v>690</v>
+      </c>
+      <c r="B598" s="1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A599" t="s">
+        <v>688</v>
+      </c>
+      <c r="B599" s="1" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A600" t="s">
+        <v>689</v>
+      </c>
+      <c r="B600" s="1" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A601" t="s">
+        <v>999</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A602" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A603" t="s">
+        <v>379</v>
+      </c>
+      <c r="B603" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A604" t="s">
+        <v>384</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A605" t="s">
+        <v>385</v>
+      </c>
+      <c r="B605" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A606" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C606" s="2" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A607" t="s">
+        <v>226</v>
+      </c>
+      <c r="B607" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C607" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A608" t="s">
+        <v>316</v>
+      </c>
+      <c r="B608" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C608" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A609" t="s">
+        <v>228</v>
+      </c>
+      <c r="B609" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C609" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A610" t="s">
+        <v>456</v>
+      </c>
+      <c r="B610" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A611" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B611" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C611" s="2" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A612" t="s">
+        <v>230</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="C612" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A613" t="s">
+        <v>275</v>
+      </c>
+      <c r="B613" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C613" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A614" t="s">
+        <v>276</v>
+      </c>
+      <c r="B614" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C614" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A615" t="s">
+        <v>231</v>
+      </c>
+      <c r="B615" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B464" s="1" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A465" t="s">
+      <c r="C615" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A616" t="s">
+        <v>247</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C616" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A617" t="s">
+        <v>251</v>
+      </c>
+      <c r="B617" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C617" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A618" t="s">
         <v>233</v>
       </c>
-      <c r="B465" s="1" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A466" t="s">
+      <c r="B618" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B466" s="1" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A467" t="s">
+      <c r="C618" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A619" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A620" t="s">
+        <v>298</v>
+      </c>
+      <c r="B620" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C620" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A621" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B621" s="1" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A622" t="s">
+        <v>821</v>
+      </c>
+      <c r="B622" s="1" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A623" t="s">
+        <v>273</v>
+      </c>
+      <c r="B623" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C623" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A624" t="s">
+        <v>274</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C624" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A625" t="s">
+        <v>314</v>
+      </c>
+      <c r="B625" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C625" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A626" t="s">
         <v>235</v>
       </c>
-      <c r="B467" s="1" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A468" t="s">
+      <c r="B626" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B468" s="1" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A469" t="s">
+      <c r="C626" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A627" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A628" t="s">
+        <v>315</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C628" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A629" t="s">
+        <v>311</v>
+      </c>
+      <c r="B629" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C629" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A630" t="s">
         <v>237</v>
       </c>
-      <c r="B469" s="1" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A470" t="s">
+      <c r="B630" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B470" s="1" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A471" t="s">
+      <c r="C630" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A631" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B631" s="1" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A632" t="s">
+        <v>822</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A633" t="s">
         <v>239</v>
       </c>
-      <c r="B471" s="1" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A472" t="s">
+      <c r="B633" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B472" s="1" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A473" t="s">
+      <c r="C633" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A634" t="s">
+        <v>250</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C634" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A635" t="s">
+        <v>254</v>
+      </c>
+      <c r="B635" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C635" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A636" t="s">
+        <v>583</v>
+      </c>
+      <c r="B636" s="1" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A637" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B637" s="1" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A638" t="s">
+        <v>585</v>
+      </c>
+      <c r="B638" s="1" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A639" t="s">
+        <v>819</v>
+      </c>
+      <c r="B639" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A640" t="s">
+        <v>820</v>
+      </c>
+      <c r="B640" s="1" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A641" t="s">
+        <v>347</v>
+      </c>
+      <c r="B641" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C641" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A642" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B642" s="1" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A643" t="s">
+        <v>823</v>
+      </c>
+      <c r="B643" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A644" t="s">
+        <v>313</v>
+      </c>
+      <c r="B644" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A645" t="s">
         <v>241</v>
       </c>
-      <c r="B473" s="1" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A474" t="s">
+      <c r="B645" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B474" s="1" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A475" t="s">
+      <c r="C645" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A646" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B646" s="1" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A647" t="s">
         <v>243</v>
       </c>
-      <c r="B475" s="1" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A476" t="s">
+      <c r="B647" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B476" s="1" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A477" t="s">
+      <c r="C647" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A648" t="s">
+        <v>249</v>
+      </c>
+      <c r="B648" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C648" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A649" t="s">
+        <v>253</v>
+      </c>
+      <c r="B649" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C649" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A650" t="s">
         <v>245</v>
       </c>
-      <c r="B477" s="1" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A478" t="s">
+      <c r="B650" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B478" s="1" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A479" t="s">
-        <v>247</v>
-      </c>
-      <c r="B479" s="1" t="s">
+      <c r="C650" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A651" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B651" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C651" s="2" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A652" t="s">
         <v>248</v>
       </c>
-      <c r="C479" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A480" t="s">
-        <v>339</v>
-      </c>
-      <c r="B480" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C480" s="2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A481" t="s">
-        <v>249</v>
-      </c>
-      <c r="B481" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C481" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A482" t="s">
-        <v>479</v>
-      </c>
-      <c r="B482" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A483" t="s">
-        <v>251</v>
-      </c>
-      <c r="B483" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="C483" s="2" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A484" t="s">
-        <v>296</v>
-      </c>
-      <c r="B484" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C484" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A485" t="s">
-        <v>297</v>
-      </c>
-      <c r="B485" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C485" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A486" t="s">
+      <c r="B652" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C652" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A653" t="s">
         <v>252</v>
       </c>
-      <c r="B486" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C486" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A487" t="s">
-        <v>268</v>
-      </c>
-      <c r="B487" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C487" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A488" t="s">
-        <v>272</v>
-      </c>
-      <c r="B488" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C488" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A489" t="s">
-        <v>254</v>
-      </c>
-      <c r="B489" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C489" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A490" t="s">
-        <v>319</v>
-      </c>
-      <c r="B490" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C490" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A491" t="s">
-        <v>852</v>
-      </c>
-      <c r="B491" s="1" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A492" t="s">
-        <v>294</v>
-      </c>
-      <c r="B492" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="C492" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A493" t="s">
-        <v>295</v>
-      </c>
-      <c r="B493" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C493" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A494" t="s">
-        <v>337</v>
-      </c>
-      <c r="B494" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="C494" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A495" t="s">
-        <v>256</v>
-      </c>
-      <c r="B495" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C495" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A496" t="s">
-        <v>338</v>
-      </c>
-      <c r="B496" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C496" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A497" t="s">
-        <v>334</v>
-      </c>
-      <c r="B497" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C497" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A498" t="s">
+      <c r="B653" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B498" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C498" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A499" t="s">
-        <v>853</v>
-      </c>
-      <c r="B499" s="1" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A500" t="s">
-        <v>260</v>
-      </c>
-      <c r="B500" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C500" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A501" t="s">
+      <c r="C653" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B501" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C501" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A502" t="s">
-        <v>275</v>
-      </c>
-      <c r="B502" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C502" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A503" t="s">
-        <v>612</v>
-      </c>
-      <c r="B503" s="1" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A504" t="s">
-        <v>614</v>
-      </c>
-      <c r="B504" s="1" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A505" t="s">
-        <v>850</v>
-      </c>
-      <c r="B505" s="1" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A506" t="s">
-        <v>851</v>
-      </c>
-      <c r="B506" s="1" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A507" t="s">
-        <v>370</v>
-      </c>
-      <c r="B507" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="C507" s="2" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A508" t="s">
-        <v>854</v>
-      </c>
-      <c r="B508" s="1" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A509" t="s">
-        <v>336</v>
-      </c>
-      <c r="B509" s="1" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A510" t="s">
-        <v>262</v>
-      </c>
-      <c r="B510" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C510" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A511" t="s">
-        <v>264</v>
-      </c>
-      <c r="B511" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C511" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A512" t="s">
-        <v>270</v>
-      </c>
-      <c r="B512" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C512" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A513" t="s">
-        <v>274</v>
-      </c>
-      <c r="B513" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C513" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A514" t="s">
-        <v>266</v>
-      </c>
-      <c r="B514" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C514" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A515" t="s">
-        <v>269</v>
-      </c>
-      <c r="B515" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C515" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A516" t="s">
-        <v>273</v>
-      </c>
-      <c r="B516" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C516" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A517" t="s">
-        <v>335</v>
-      </c>
-      <c r="B517" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C517" s="2" t="s">
-        <v>353</v>
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A654" t="s">
+        <v>312</v>
+      </c>
+      <c r="B654" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C654" s="2" t="s">
+        <v>330</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K517">
-    <sortState ref="A2:K517">
-      <sortCondition ref="A1:A517"/>
+  <autoFilter ref="A1:K647">
+    <sortState ref="A2:K654">
+      <sortCondition ref="A1:A647"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8115,97 +10015,87 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="46.7265625" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" style="1"/>
+    <col min="3" max="3" width="9.1796875" style="2"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>361</v>
-      </c>
-      <c r="B1" t="s">
-        <v>362</v>
-      </c>
-      <c r="C1" t="s">
-        <v>371</v>
+        <v>338</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>363</v>
-      </c>
-      <c r="B2" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>364</v>
-      </c>
-      <c r="B3" t="s">
-        <v>372</v>
+        <v>343</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>365</v>
-      </c>
-      <c r="B4" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>366</v>
-      </c>
-      <c r="B5" t="s">
-        <v>373</v>
-      </c>
-      <c r="C5" t="s">
-        <v>377</v>
+        <v>347</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>367</v>
-      </c>
-      <c r="B6" t="s">
-        <v>373</v>
-      </c>
-      <c r="C6" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>368</v>
-      </c>
-      <c r="B7" t="s">
-        <v>373</v>
-      </c>
-      <c r="C7" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>369</v>
-      </c>
-      <c r="B8" t="s">
-        <v>374</v>
-      </c>
-      <c r="C8" t="s">
-        <v>378</v>
+        <v>817</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>370</v>
-      </c>
-      <c r="B9" t="s">
-        <v>375</v>
-      </c>
-      <c r="C9" t="s">
-        <v>376</v>
+        <v>1040</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1046</v>
       </c>
     </row>
   </sheetData>

--- a/gui/rebalance_localizations.xlsx
+++ b/gui/rebalance_localizations.xlsx
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">rebalance_localizations!$A$1:$K$647</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">rebalance_localizations!$A$1:$K$691</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="1246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="1317">
   <si>
     <t>ENGLISH</t>
   </si>
@@ -3079,9 +3079,6 @@
     <t>Liquid Deuterium</t>
   </si>
   <si>
-    <t>You don't want to know</t>
-  </si>
-  <si>
     <t>gui/menu/research/name/fire_control_station_artillery</t>
   </si>
   <si>
@@ -3761,6 +3758,222 @@
   </si>
   <si>
     <t>Production of superhot plasmas with total atomic ionization. Any more energy and the plasma becomes instable with fusion reactions emerging.</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/ore_mill</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/ore_mill</t>
+  </si>
+  <si>
+    <t>Ore Mill</t>
+  </si>
+  <si>
+    <t>The ore mill processed mined raw ore into minerals and therefore increasing yield of nearby strip and subsurface mines. Required by higher level mines for operation</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/ore_processing_lvl_1</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/ore_processing_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/ore_processing_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/ore_processing_lvl_1</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/ore_processing_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/ore_processing_lvl_3</t>
+  </si>
+  <si>
+    <t>Basic Ore Processing</t>
+  </si>
+  <si>
+    <t>Advanced Ore Processing</t>
+  </si>
+  <si>
+    <t>Optimal Ore Processing</t>
+  </si>
+  <si>
+    <t>Raw ores harvested from strip and subsurface mines can be more effiently processed into valuable minerals by ore mills.</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/strip_mine_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/strip_mine_lvl_3</t>
+  </si>
+  <si>
+    <t>Mines resources from surface outcrops. REQUIRES: ore mill to operate</t>
+  </si>
+  <si>
+    <t>Mines resources from surface outcrops. REQUIRES: level 2 ore mill to operate</t>
+  </si>
+  <si>
+    <t>Mines for underground resource veins. REQUIRES: level 2 ore mill to operate</t>
+  </si>
+  <si>
+    <t>Mines for underground resource veins. REQUIRES: ore mill to operate</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/ore_mill_lvl_2</t>
+  </si>
+  <si>
+    <t>The ore mill processed mined raw ore into minerals and therefore increasing yield of nearby strip and subsurface mines by +100%</t>
+  </si>
+  <si>
+    <t>The ore mill processed mined raw ore into minerals and therefore increasing yield of nearby strip and subsurface mines by +150%</t>
+  </si>
+  <si>
+    <t>The ore mill processed mined raw ore into minerals and therefore increasing yield of nearby strip and subsurface mines by +200%</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/ore_mill_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/ore_mill_lvl_4</t>
+  </si>
+  <si>
+    <t>Blast Furnace</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/blast_furnace</t>
+  </si>
+  <si>
+    <t>Produces molten metal out of refined ironium</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/blast_furnace</t>
+  </si>
+  <si>
+    <t>Metallurgy</t>
+  </si>
+  <si>
+    <t>Advanced Metallurgy</t>
+  </si>
+  <si>
+    <t>Basic metallurgy technology for production of high quality metals and alloys</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/metallurgy</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/metallurgy_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/metallurgy</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/metallurgy_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/metallurgy_lvl_3</t>
+  </si>
+  <si>
+    <t>Advanced metallurgy technology for production of high quality metals and alloys</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/metallurgy_lvl_3</t>
+  </si>
+  <si>
+    <t>Optimized Metallurgy</t>
+  </si>
+  <si>
+    <t>Optimized metallurgy technology for production of high quality metals and alloys</t>
+  </si>
+  <si>
+    <t>Molten Metal</t>
+  </si>
+  <si>
+    <t>Compressed Molten Metal</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/alloys_factory</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/alloys_factory_titanium</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/alloys_factory_uranium</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/alloys_factory_palladium</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/alloys_factory</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/alloys_factory_titanium</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/alloys_factory_uranium</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/alloys_factory_palladium</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/alloys_titanium</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/alloys_uranium</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/alloys_palladium</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/alloys_titanium</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/alloys_uranium</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/alloys_palladium</t>
+  </si>
+  <si>
+    <t>Alloys Factory (Cobalt)</t>
+  </si>
+  <si>
+    <t>Alloys Factory (Titanium)</t>
+  </si>
+  <si>
+    <t>Alloys Factory (Uranium)</t>
+  </si>
+  <si>
+    <t>Alloys Factory (Palladium)</t>
+  </si>
+  <si>
+    <t>Titanium Alloys</t>
+  </si>
+  <si>
+    <t>Uranium Alloys</t>
+  </si>
+  <si>
+    <t>Palladium Alloys</t>
+  </si>
+  <si>
+    <t>Metallurgy technology for production of titanium alloys</t>
+  </si>
+  <si>
+    <t>Metallurgy technology for production of palladium alloys</t>
+  </si>
+  <si>
+    <t>Metallurgy technology for production of deplated uraniums alloys</t>
+  </si>
+  <si>
+    <t>Produces alloys from cobalt and molten iron</t>
+  </si>
+  <si>
+    <t>Produces alloys from titanium and molten iron</t>
+  </si>
+  <si>
+    <t>Produces alloys from deplated uranium and molten iron</t>
+  </si>
+  <si>
+    <t>Produces alloys from palladium and molten iron</t>
   </si>
 </sst>
 </file>
@@ -4603,7 +4816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K654"/>
+  <dimension ref="A1:K691"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="65.453125" customWidth="1"/>
@@ -4645,319 +4858,319 @@
     </row>
     <row r="2" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>1293</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>1296</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>1294</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>1295</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>402</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>406</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>542</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>538</v>
+        <v>402</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>543</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>28</v>
+        <v>542</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>403</v>
+        <v>538</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>407</v>
+        <v>543</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>403</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>36</v>
+        <v>407</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>1030</v>
+        <v>33</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1033</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>1034</v>
+        <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1035</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1229</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>44</v>
+        <v>1029</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1230</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>45</v>
+        <v>1033</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1231</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>457</v>
+        <v>41</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>488</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>1099</v>
+        <v>42</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1086</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>599</v>
+        <v>44</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>600</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>458</v>
+        <v>45</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>487</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>457</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>692</v>
+        <v>488</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>1061</v>
+        <v>1098</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>1064</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>1232</v>
+        <v>599</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>1233</v>
+        <v>600</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>1054</v>
+        <v>458</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>1056</v>
+        <v>487</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>894</v>
+        <v>46</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>1146</v>
+        <v>692</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>1154</v>
+        <v>1060</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1150</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>1158</v>
+        <v>1274</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1150</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>893</v>
+        <v>1231</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1148</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>1155</v>
+        <v>1053</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>1151</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>1159</v>
+        <v>894</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>897</v>
+        <v>1153</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>1149</v>
@@ -4965,5047 +5178,5343 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>1160</v>
+        <v>893</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1152</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>895</v>
+        <v>1154</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>1161</v>
+        <v>897</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>1065</v>
+        <v>1155</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1068</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>335</v>
+        <v>1159</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>337</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>416</v>
+        <v>895</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>465</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>992</v>
+        <v>1156</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>995</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>301</v>
+        <v>1160</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1103</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>308</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>1077</v>
+        <v>1064</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>1102</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>619</v>
+        <v>335</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>620</v>
+        <v>337</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>416</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>48</v>
+        <v>465</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>992</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>50</v>
+        <v>995</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>301</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>52</v>
+        <v>1102</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>1112</v>
+        <v>1076</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>1113</v>
+        <v>619</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>1109</v>
+        <v>620</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>332</v>
+        <v>47</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>329</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>285</v>
+        <v>49</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>296</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>294</v>
+        <v>51</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>297</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>295</v>
+        <v>1111</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>297</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>1112</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>54</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
+        <v>332</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>285</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>294</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>294</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>295</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>295</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>53</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>55</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B71" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+    <row r="72" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>56</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+    <row r="73" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>57</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B73" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
+    <row r="74" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>59</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B74" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
+    <row r="75" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
         <v>60</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B75" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
+    <row r="76" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
         <v>570</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>571</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>572</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>607</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>615</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>616</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>338</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>340</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>341</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>342</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>974</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>978</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>979</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>865</v>
+        <v>572</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>868</v>
+        <v>573</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>866</v>
+        <v>607</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>869</v>
+        <v>613</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>867</v>
+        <v>615</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>869</v>
+        <v>614</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>637</v>
+        <v>616</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>644</v>
+        <v>618</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>638</v>
+        <v>338</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>642</v>
+        <v>339</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>634</v>
+        <v>340</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>643</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>793</v>
+        <v>341</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>794</v>
+        <v>349</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>303</v>
+        <v>342</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>310</v>
+        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>61</v>
+        <v>974</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>62</v>
+        <v>991</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>63</v>
+        <v>978</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>62</v>
+        <v>989</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>64</v>
+        <v>979</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>62</v>
+        <v>990</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>1115</v>
+        <v>865</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>1120</v>
+        <v>868</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>1117</v>
+        <v>866</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>1119</v>
+        <v>869</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>1118</v>
+        <v>867</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>1121</v>
+        <v>869</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>65</v>
+        <v>637</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>66</v>
+        <v>644</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
+        <v>638</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>634</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>793</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>303</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>61</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>63</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>64</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>65</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
         <v>662</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B109" s="1" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
+    <row r="110" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
         <v>661</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B110" s="1" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
+    <row r="111" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
         <v>660</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B111" s="1" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
+    <row r="112" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
         <v>67</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B112" s="1" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>69</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>436</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>437</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
-        <v>444</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
-        <v>445</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
-        <v>71</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>409</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>408</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>410</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>414</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
-        <v>507</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>442</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
-        <v>443</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="113" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>438</v>
+        <v>69</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>469</v>
+        <v>70</v>
       </c>
     </row>
     <row r="114" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="115" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>559</v>
+        <v>467</v>
       </c>
     </row>
     <row r="116" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="117" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="118" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>449</v>
+        <v>71</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>478</v>
+        <v>72</v>
       </c>
     </row>
     <row r="119" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>450</v>
+        <v>409</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
     </row>
     <row r="120" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>451</v>
+        <v>408</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="121" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>453</v>
+        <v>410</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="122" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>452</v>
+        <v>414</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="123" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>446</v>
+        <v>507</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>475</v>
+        <v>508</v>
       </c>
     </row>
     <row r="124" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="125" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>498</v>
+        <v>443</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>502</v>
+        <v>472</v>
       </c>
     </row>
     <row r="126" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>499</v>
+        <v>438</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>560</v>
+        <v>469</v>
       </c>
     </row>
     <row r="127" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>497</v>
+        <v>440</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
     </row>
     <row r="128" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>1132</v>
+        <v>441</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>1140</v>
+        <v>559</v>
       </c>
     </row>
     <row r="129" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>1133</v>
+        <v>439</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>1135</v>
+        <v>468</v>
       </c>
     </row>
     <row r="130" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>1134</v>
+        <v>448</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>1135</v>
+        <v>477</v>
       </c>
     </row>
     <row r="131" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>1127</v>
+        <v>449</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>1122</v>
+        <v>478</v>
       </c>
     </row>
     <row r="132" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>1128</v>
+        <v>450</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>1141</v>
+        <v>479</v>
       </c>
     </row>
     <row r="133" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>1129</v>
+        <v>451</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>1142</v>
+        <v>480</v>
       </c>
     </row>
     <row r="134" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>1124</v>
+        <v>453</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>1123</v>
+        <v>482</v>
       </c>
     </row>
     <row r="135" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>1125</v>
+        <v>452</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>1130</v>
+        <v>481</v>
       </c>
     </row>
     <row r="136" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>1126</v>
+        <v>446</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>1131</v>
+        <v>475</v>
       </c>
     </row>
     <row r="137" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>1136</v>
+        <v>447</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>1139</v>
+        <v>476</v>
       </c>
     </row>
     <row r="138" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>1137</v>
+        <v>498</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>1143</v>
+        <v>502</v>
       </c>
     </row>
     <row r="139" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>1138</v>
+        <v>499</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>1143</v>
+        <v>560</v>
       </c>
     </row>
     <row r="140" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>73</v>
+        <v>497</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>74</v>
+        <v>503</v>
       </c>
     </row>
     <row r="141" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>75</v>
+        <v>1131</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>76</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="142" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>77</v>
+        <v>1132</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>78</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="143" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>79</v>
+        <v>1133</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>80</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="144" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>81</v>
+        <v>1126</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>82</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="145" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>400</v>
+        <v>1127</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>404</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="146" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>83</v>
+        <v>1128</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>84</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="147" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>85</v>
+        <v>1123</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>86</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="148" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>87</v>
+        <v>1124</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>541</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="149" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>539</v>
+        <v>1125</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>540</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="150" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>88</v>
+        <v>1135</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>89</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="151" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>90</v>
+        <v>1136</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>91</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="152" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>92</v>
+        <v>1137</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>93</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="153" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>401</v>
+        <v>73</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>405</v>
+        <v>74</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>94</v>
+        <v>1289</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>95</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="155" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>96</v>
+        <v>1292</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>97</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="156" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>98</v>
+        <v>1290</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>99</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="157" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>100</v>
+        <v>1291</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>101</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
     </row>
     <row r="159" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>1031</v>
+        <v>79</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>1032</v>
+        <v>80</v>
       </c>
     </row>
     <row r="161" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>108</v>
+        <v>400</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>109</v>
+        <v>404</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>454</v>
+        <v>87</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>462</v>
+        <v>541</v>
       </c>
     </row>
     <row r="166" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>1098</v>
+        <v>539</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>1079</v>
+        <v>540</v>
       </c>
     </row>
     <row r="167" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>594</v>
+        <v>88</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>595</v>
+        <v>89</v>
       </c>
     </row>
     <row r="168" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>455</v>
+        <v>90</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>463</v>
+        <v>91</v>
       </c>
     </row>
     <row r="169" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
     </row>
     <row r="170" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>1062</v>
+        <v>401</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>1063</v>
+        <v>405</v>
       </c>
     </row>
     <row r="171" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>1055</v>
+        <v>94</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>1057</v>
+        <v>95</v>
       </c>
     </row>
     <row r="172" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>881</v>
+        <v>96</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>884</v>
+        <v>97</v>
       </c>
     </row>
     <row r="173" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>880</v>
+        <v>98</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>883</v>
+        <v>99</v>
       </c>
     </row>
     <row r="174" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>898</v>
+        <v>100</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>886</v>
+        <v>101</v>
       </c>
     </row>
     <row r="175" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>882</v>
+        <v>102</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>885</v>
+        <v>103</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>1066</v>
+        <v>104</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>334</v>
+        <v>1030</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>417</v>
+        <v>106</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>993</v>
+        <v>108</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>302</v>
+        <v>110</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>1100</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>304</v>
+        <v>112</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>305</v>
+        <v>454</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>605</v>
+        <v>1097</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>116</v>
+        <v>594</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>1110</v>
+        <v>455</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>1111</v>
+        <v>114</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>333</v>
+        <v>1061</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>286</v>
+        <v>1272</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>287</v>
+        <v>1054</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>288</v>
+        <v>881</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>118</v>
+        <v>880</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>120</v>
+        <v>898</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>121</v>
+        <v>886</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>122</v>
+        <v>882</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>121</v>
+        <v>885</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>123</v>
+        <v>1065</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>121</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>574</v>
+        <v>334</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>575</v>
+        <v>336</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>343</v>
+        <v>417</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>354</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>344</v>
+        <v>993</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>354</v>
+        <v>996</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>345</v>
+        <v>302</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>350</v>
+        <v>1099</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>354</v>
+        <v>307</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>346</v>
+        <v>304</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>351</v>
+        <v>1100</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>355</v>
+        <v>307</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>975</v>
+        <v>305</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>986</v>
+        <v>1100</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>976</v>
+        <v>605</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>987</v>
+        <v>608</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>977</v>
+        <v>116</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>988</v>
+        <v>117</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>860</v>
+        <v>1109</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>861</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>862</v>
+        <v>1110</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>861</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>863</v>
+        <v>333</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>861</v>
+        <v>326</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>635</v>
+        <v>286</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>639</v>
+        <v>293</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>636</v>
+        <v>287</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>641</v>
+        <v>864</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>633</v>
+        <v>288</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>795</v>
+        <v>118</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>1114</v>
+        <v>122</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>1116</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>290</v>
+        <v>1245</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>289</v>
+        <v>574</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>648</v>
+        <v>343</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>350</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>645</v>
+        <v>344</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>350</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>646</v>
+        <v>345</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>350</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>418</v>
+        <v>346</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>351</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>419</v>
+        <v>975</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>426</v>
+        <v>976</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>427</v>
+        <v>977</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>128</v>
+        <v>860</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>412</v>
+        <v>862</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>411</v>
+        <v>863</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>544</v>
+        <v>861</v>
       </c>
     </row>
     <row r="225" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>413</v>
+        <v>635</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>545</v>
+        <v>639</v>
       </c>
     </row>
     <row r="226" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>415</v>
+        <v>636</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>546</v>
+        <v>641</v>
       </c>
     </row>
     <row r="227" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>787</v>
+        <v>633</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>785</v>
+        <v>640</v>
       </c>
     </row>
     <row r="228" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>786</v>
+        <v>796</v>
       </c>
     </row>
     <row r="229" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>504</v>
+        <v>124</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>505</v>
+        <v>125</v>
       </c>
     </row>
     <row r="230" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>424</v>
+        <v>1113</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>562</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="231" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>425</v>
+        <v>126</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>563</v>
+        <v>127</v>
       </c>
     </row>
     <row r="232" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>421</v>
+        <v>290</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>564</v>
+        <v>291</v>
       </c>
     </row>
     <row r="233" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>422</v>
+        <v>289</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>565</v>
+        <v>292</v>
       </c>
     </row>
     <row r="234" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>423</v>
+        <v>648</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>566</v>
+        <v>647</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>420</v>
+        <v>645</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>567</v>
+        <v>649</v>
       </c>
     </row>
     <row r="236" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>430</v>
+        <v>646</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>460</v>
+        <v>650</v>
       </c>
     </row>
     <row r="237" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="238" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="239" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
     </row>
     <row r="240" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>461</v>
+        <v>547</v>
       </c>
     </row>
     <row r="241" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>434</v>
+        <v>128</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>558</v>
+        <v>129</v>
       </c>
     </row>
     <row r="242" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>494</v>
+        <v>413</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>496</v>
+        <v>415</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>506</v>
+        <v>546</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>495</v>
+        <v>787</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>556</v>
+        <v>785</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>130</v>
+        <v>788</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>131</v>
+        <v>786</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>1049</v>
+        <v>504</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>1048</v>
+        <v>505</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>500</v>
+        <v>424</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>501</v>
+        <v>562</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>489</v>
+        <v>425</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>490</v>
+        <v>563</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>1047</v>
+        <v>421</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>1048</v>
+        <v>564</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>924</v>
+        <v>422</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>857</v>
+        <v>565</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>925</v>
+        <v>423</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>859</v>
+        <v>566</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>926</v>
+        <v>420</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>858</v>
+        <v>567</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>927</v>
+        <v>430</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>856</v>
+        <v>460</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>855</v>
+        <v>431</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>854</v>
+        <v>551</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>1144</v>
+        <v>432</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>1145</v>
+        <v>552</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>972</v>
+        <v>433</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>973</v>
+        <v>553</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>811</v>
+        <v>435</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>815</v>
+        <v>461</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>812</v>
+        <v>434</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>816</v>
+        <v>558</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>523</v>
+        <v>428</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>1172</v>
+        <v>554</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>1191</v>
+        <v>429</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>1173</v>
+        <v>555</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>524</v>
+        <v>494</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>1180</v>
+        <v>557</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>675</v>
+        <v>496</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>1181</v>
+        <v>506</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>525</v>
+        <v>495</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>1176</v>
+        <v>556</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>1192</v>
+        <v>130</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>1175</v>
+        <v>131</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>526</v>
+        <v>1048</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>1183</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>676</v>
+        <v>500</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>1182</v>
+        <v>501</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>527</v>
+        <v>489</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>1177</v>
+        <v>490</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>1193</v>
+        <v>1046</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>1174</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>528</v>
+        <v>924</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>1184</v>
+        <v>857</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>677</v>
+        <v>925</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>1185</v>
+        <v>859</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>529</v>
+        <v>926</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>1178</v>
+        <v>858</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>1194</v>
+        <v>927</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>1173</v>
+        <v>856</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>530</v>
+        <v>855</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>1186</v>
+        <v>854</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>678</v>
+        <v>1143</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>1187</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>531</v>
+        <v>972</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>1179</v>
+        <v>973</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>1195</v>
+        <v>811</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>1190</v>
+        <v>815</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>532</v>
+        <v>812</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>1188</v>
+        <v>816</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>679</v>
+        <v>1302</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>1189</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>1042</v>
+        <v>1300</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>1045</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>1041</v>
+        <v>1301</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>1046</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1026</v>
+        <v>523</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>1036</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>1027</v>
+        <v>1190</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>1035</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>132</v>
+        <v>524</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>133</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>1205</v>
+        <v>675</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>1213</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1221</v>
+        <v>525</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>1213</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>134</v>
+        <v>1191</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>135</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>1207</v>
+        <v>526</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>1215</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>1223</v>
+        <v>676</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>1215</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>136</v>
+        <v>527</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>137</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>138</v>
+        <v>1192</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>137</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>139</v>
+        <v>528</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>137</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>621</v>
+        <v>677</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>628</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>625</v>
+        <v>529</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>629</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>626</v>
+        <v>1193</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>630</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>140</v>
+        <v>530</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>141</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>1206</v>
+        <v>678</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>1216</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>1222</v>
+        <v>531</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>1216</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>142</v>
+        <v>1194</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>143</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>1208</v>
+        <v>532</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>1214</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>1224</v>
+        <v>679</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>1214</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>699</v>
+        <v>1041</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>702</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>700</v>
+        <v>1040</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>710</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>701</v>
+        <v>1025</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>711</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>491</v>
+        <v>1026</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>492</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>1097</v>
+        <v>132</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>493</v>
+        <v>133</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>591</v>
+        <v>1204</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>603</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>592</v>
+        <v>1220</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>593</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>1052</v>
+        <v>134</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>1056</v>
+        <v>135</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>1053</v>
+        <v>1206</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>1060</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>971</v>
+        <v>1222</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>967</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>958</v>
+        <v>136</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>967</v>
+        <v>137</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>959</v>
+        <v>138</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>967</v>
+        <v>137</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>960</v>
+        <v>139</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>967</v>
+        <v>137</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>952</v>
+        <v>621</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>968</v>
+        <v>628</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>953</v>
+        <v>625</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>968</v>
+        <v>629</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>951</v>
+        <v>626</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>968</v>
+        <v>630</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>954</v>
+        <v>140</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>968</v>
+        <v>141</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>598</v>
+        <v>1205</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>657</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>655</v>
+        <v>1221</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>658</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>656</v>
+        <v>142</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>659</v>
+        <v>143</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>891</v>
+        <v>1207</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>1146</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>913</v>
+        <v>1223</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>1150</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>917</v>
+        <v>699</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>1150</v>
+        <v>702</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>890</v>
+        <v>700</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>1148</v>
+        <v>710</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>914</v>
+        <v>701</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>1151</v>
+        <v>711</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>918</v>
+        <v>491</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>1151</v>
+        <v>492</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>896</v>
+        <v>1096</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>1149</v>
+        <v>493</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>915</v>
+        <v>591</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>1152</v>
+        <v>603</v>
       </c>
     </row>
     <row r="331" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>919</v>
+        <v>592</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>1152</v>
+        <v>593</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>892</v>
+        <v>1051</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>1147</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>916</v>
+        <v>1052</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>1153</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>920</v>
+        <v>971</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>1153</v>
+        <v>967</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>1237</v>
+        <v>958</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>1243</v>
+        <v>967</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>1238</v>
+        <v>959</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>1244</v>
+        <v>967</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>1239</v>
+        <v>960</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>1245</v>
+        <v>967</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>813</v>
+        <v>952</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>814</v>
+        <v>968</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>994</v>
+        <v>953</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>995</v>
+        <v>968</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>1092</v>
+        <v>951</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>1095</v>
+        <v>968</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>1093</v>
+        <v>954</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>1096</v>
+        <v>968</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>805</v>
+        <v>598</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>802</v>
+        <v>657</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>804</v>
+        <v>655</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>803</v>
+        <v>658</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>706</v>
+        <v>656</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>709</v>
+        <v>659</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>144</v>
+        <v>891</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>145</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>146</v>
+        <v>913</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>148</v>
+        <v>917</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>149</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>150</v>
+        <v>890</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>151</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>152</v>
+        <v>914</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>153</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>154</v>
+        <v>918</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>155</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>156</v>
+        <v>896</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>157</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>158</v>
+        <v>915</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>159</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>160</v>
+        <v>919</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>161</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>162</v>
+        <v>892</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>163</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>164</v>
+        <v>916</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>165</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>166</v>
+        <v>920</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>167</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>168</v>
+        <v>1236</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>169</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>170</v>
+        <v>1237</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>171</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>172</v>
+        <v>1238</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>173</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>174</v>
+        <v>813</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>175</v>
+        <v>814</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>176</v>
+        <v>994</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>177</v>
+        <v>995</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>178</v>
+        <v>1091</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>179</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>745</v>
+        <v>1092</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>739</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>746</v>
+        <v>805</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>740</v>
+        <v>802</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>747</v>
+        <v>804</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>741</v>
+        <v>803</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>748</v>
+        <v>706</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>727</v>
+        <v>709</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>749</v>
+        <v>144</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>728</v>
+        <v>145</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>750</v>
+        <v>146</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>729</v>
+        <v>147</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>751</v>
+        <v>148</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>733</v>
+        <v>149</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>752</v>
+        <v>150</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>734</v>
+        <v>151</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>753</v>
+        <v>152</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>735</v>
+        <v>153</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>760</v>
+        <v>154</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>730</v>
+        <v>155</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>761</v>
+        <v>156</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>731</v>
+        <v>157</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>762</v>
+        <v>158</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>732</v>
+        <v>159</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>754</v>
+        <v>160</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>742</v>
+        <v>161</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>755</v>
+        <v>162</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>743</v>
+        <v>163</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>756</v>
+        <v>164</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>744</v>
+        <v>165</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>757</v>
+        <v>166</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>736</v>
+        <v>167</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>758</v>
+        <v>168</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>737</v>
+        <v>169</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>759</v>
+        <v>170</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>738</v>
+        <v>171</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>1082</v>
+        <v>172</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>1088</v>
+        <v>173</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>1083</v>
+        <v>174</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>1088</v>
+        <v>175</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>357</v>
+        <v>176</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>568</v>
+        <v>177</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>362</v>
+        <v>178</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>366</v>
+        <v>179</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>363</v>
+        <v>745</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>365</v>
+        <v>739</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>955</v>
+        <v>746</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>966</v>
+        <v>740</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>956</v>
+        <v>747</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>966</v>
+        <v>741</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>957</v>
+        <v>748</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>966</v>
+        <v>727</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>964</v>
+        <v>749</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>966</v>
+        <v>728</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>965</v>
+        <v>750</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>966</v>
+        <v>729</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>576</v>
+        <v>751</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>577</v>
+        <v>733</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>578</v>
+        <v>752</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>577</v>
+        <v>734</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>389</v>
+        <v>753</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>397</v>
+        <v>735</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>391</v>
+        <v>760</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>398</v>
+        <v>730</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>393</v>
+        <v>761</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>399</v>
+        <v>731</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>705</v>
+        <v>762</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>708</v>
+        <v>732</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>367</v>
+        <v>754</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>370</v>
+        <v>742</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>374</v>
+        <v>755</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>371</v>
+        <v>743</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>376</v>
+        <v>756</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>371</v>
+        <v>744</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>980</v>
+        <v>757</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>1023</v>
+        <v>736</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>981</v>
+        <v>758</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>1024</v>
+        <v>737</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>982</v>
+        <v>759</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>1025</v>
+        <v>738</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>872</v>
+        <v>1278</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>879</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>871</v>
+        <v>1279</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>868</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>870</v>
+        <v>1282</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>879</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>797</v>
+        <v>1081</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>799</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>180</v>
+        <v>1082</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>181</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>182</v>
+        <v>357</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>183</v>
+        <v>568</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>719</v>
+        <v>362</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>684</v>
+        <v>366</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>720</v>
+        <v>363</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>716</v>
+        <v>365</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>789</v>
+        <v>1252</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>791</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>790</v>
+        <v>1253</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>792</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>721</v>
+        <v>1254</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>718</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>722</v>
+        <v>955</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>717</v>
+        <v>966</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>713</v>
+        <v>956</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>712</v>
+        <v>966</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>929</v>
+        <v>957</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>685</v>
+        <v>966</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>829</v>
+        <v>964</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>831</v>
+        <v>966</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>830</v>
+        <v>965</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>831</v>
+        <v>966</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>510</v>
+        <v>576</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>512</v>
+        <v>577</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>842</v>
+        <v>578</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>851</v>
+        <v>577</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>843</v>
+        <v>389</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>852</v>
+        <v>397</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>844</v>
+        <v>391</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>853</v>
+        <v>398</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>691</v>
+        <v>393</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>683</v>
+        <v>399</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>997</v>
+        <v>705</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>1004</v>
+        <v>708</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>998</v>
+        <v>367</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>1003</v>
+        <v>370</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>763</v>
+        <v>376</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>569</v>
+        <v>371</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>386</v>
+        <v>980</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>387</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>817</v>
+        <v>981</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>818</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>806</v>
+        <v>982</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>809</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>807</v>
+        <v>872</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>810</v>
+        <v>879</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>513</v>
+        <v>871</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>533</v>
+        <v>868</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>1196</v>
+        <v>870</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>1162</v>
+        <v>879</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>514</v>
+        <v>797</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>670</v>
+        <v>799</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>669</v>
+        <v>180</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>1165</v>
+        <v>181</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>515</v>
+        <v>182</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>536</v>
+        <v>183</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>1197</v>
+        <v>719</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>1168</v>
+        <v>684</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>516</v>
+        <v>720</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>671</v>
+        <v>716</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>668</v>
+        <v>789</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>1169</v>
+        <v>791</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>517</v>
+        <v>790</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>534</v>
+        <v>792</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>1198</v>
+        <v>721</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>1163</v>
+        <v>718</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>518</v>
+        <v>722</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>672</v>
+        <v>717</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>667</v>
+        <v>713</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>1166</v>
+        <v>712</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>519</v>
+        <v>929</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>537</v>
+        <v>685</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>1199</v>
+        <v>829</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>1170</v>
+        <v>831</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>520</v>
+        <v>830</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>673</v>
+        <v>831</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>666</v>
+        <v>510</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>1171</v>
+        <v>512</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>521</v>
+        <v>842</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>535</v>
+        <v>851</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>1200</v>
+        <v>843</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>1164</v>
+        <v>852</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>522</v>
+        <v>844</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>674</v>
+        <v>853</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>665</v>
+        <v>691</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>1167</v>
+        <v>683</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>1040</v>
+        <v>997</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>1043</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>1039</v>
+        <v>998</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>1044</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>1028</v>
+        <v>378</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>1037</v>
+        <v>381</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>1029</v>
+        <v>763</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>1038</v>
+        <v>569</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>184</v>
+        <v>386</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>185</v>
+        <v>387</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>1201</v>
+        <v>817</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>1209</v>
+        <v>818</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>1217</v>
+        <v>806</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>1225</v>
+        <v>809</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>186</v>
+        <v>807</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>187</v>
+        <v>810</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>1203</v>
+        <v>1299</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>1211</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>1219</v>
+        <v>1297</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>1227</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>188</v>
+        <v>1298</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>189</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>190</v>
+        <v>513</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>191</v>
+        <v>533</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>192</v>
+        <v>1195</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>193</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>622</v>
+        <v>514</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>627</v>
+        <v>670</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>623</v>
+        <v>669</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>631</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>624</v>
+        <v>515</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>632</v>
+        <v>536</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>194</v>
+        <v>1196</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>195</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>1202</v>
+        <v>516</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>1210</v>
+        <v>671</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>1218</v>
+        <v>668</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>1226</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>196</v>
+        <v>517</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>197</v>
+        <v>534</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>1204</v>
+        <v>1197</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>1212</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>1220</v>
+        <v>518</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>1228</v>
+        <v>672</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>693</v>
+        <v>667</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>696</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>694</v>
+        <v>519</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>697</v>
+        <v>537</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>695</v>
+        <v>1198</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>698</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>1104</v>
+        <v>520</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>493</v>
+        <v>673</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>1105</v>
+        <v>666</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>1087</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>587</v>
+        <v>521</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>589</v>
+        <v>535</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>588</v>
+        <v>1199</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>590</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>1050</v>
+        <v>522</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>1058</v>
+        <v>674</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>1051</v>
+        <v>665</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>1059</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>969</v>
+        <v>1039</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>970</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>945</v>
+        <v>1038</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>948</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>946</v>
+        <v>1027</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>949</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>947</v>
+        <v>1028</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>950</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>930</v>
+        <v>184</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>934</v>
+        <v>185</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>931</v>
+        <v>1200</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>936</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>932</v>
+        <v>1216</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>935</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>933</v>
+        <v>186</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>937</v>
+        <v>187</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>596</v>
+        <v>1202</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>597</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>651</v>
+        <v>1218</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>653</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>652</v>
+        <v>188</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>654</v>
+        <v>189</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>888</v>
+        <v>190</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>884</v>
+        <v>191</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>899</v>
+        <v>192</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>902</v>
+        <v>193</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>906</v>
+        <v>622</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>909</v>
+        <v>627</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>887</v>
+        <v>623</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>883</v>
+        <v>631</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>900</v>
+        <v>624</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>903</v>
+        <v>632</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>907</v>
+        <v>194</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>910</v>
+        <v>195</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>921</v>
+        <v>1201</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>886</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>922</v>
+        <v>1217</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>904</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>923</v>
+        <v>196</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>911</v>
+        <v>197</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>889</v>
+        <v>1203</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>885</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>901</v>
+        <v>1219</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>905</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>908</v>
+        <v>693</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>912</v>
+        <v>696</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>1234</v>
+        <v>694</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>1240</v>
+        <v>697</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>1235</v>
+        <v>695</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>1241</v>
+        <v>698</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>1236</v>
+        <v>1103</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>1242</v>
+        <v>493</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>808</v>
+        <v>1104</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>459</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>1019</v>
+        <v>587</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>996</v>
+        <v>589</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>1090</v>
+        <v>588</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>1089</v>
+        <v>590</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>1091</v>
+        <v>1049</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>1094</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>800</v>
+        <v>1050</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>802</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>801</v>
+        <v>969</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>803</v>
+        <v>970</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>704</v>
+        <v>945</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>707</v>
+        <v>948</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>198</v>
+        <v>946</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>199</v>
+        <v>949</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>200</v>
+        <v>947</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>201</v>
+        <v>950</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>202</v>
+        <v>930</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>203</v>
+        <v>934</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>204</v>
+        <v>931</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>205</v>
+        <v>936</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>206</v>
+        <v>932</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>207</v>
+        <v>935</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>208</v>
+        <v>933</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>209</v>
+        <v>937</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>210</v>
+        <v>596</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>157</v>
+        <v>597</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>211</v>
+        <v>651</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>159</v>
+        <v>653</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>212</v>
+        <v>652</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>161</v>
+        <v>654</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>213</v>
+        <v>888</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>163</v>
+        <v>884</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>214</v>
+        <v>899</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>165</v>
+        <v>902</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>215</v>
+        <v>906</v>
       </c>
       <c r="B527" s="1" t="s">
-        <v>167</v>
+        <v>909</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>216</v>
+        <v>887</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>169</v>
+        <v>883</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>217</v>
+        <v>900</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>171</v>
+        <v>903</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>218</v>
+        <v>907</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>173</v>
+        <v>910</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>219</v>
+        <v>921</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>175</v>
+        <v>886</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>220</v>
+        <v>922</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>177</v>
+        <v>904</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>221</v>
+        <v>923</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>179</v>
+        <v>911</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>764</v>
+        <v>889</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>834</v>
+        <v>885</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>765</v>
+        <v>901</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>740</v>
+        <v>905</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>766</v>
+        <v>908</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>741</v>
+        <v>912</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>767</v>
+        <v>1233</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>835</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>768</v>
+        <v>1234</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>728</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>769</v>
+        <v>1235</v>
       </c>
       <c r="B539" s="1" t="s">
-        <v>729</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>770</v>
+        <v>808</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>836</v>
+        <v>459</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>771</v>
+        <v>1018</v>
       </c>
       <c r="B541" s="1" t="s">
-        <v>734</v>
+        <v>996</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>772</v>
+        <v>1089</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>735</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>773</v>
+        <v>1090</v>
       </c>
       <c r="B543" s="1" t="s">
-        <v>837</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>774</v>
+        <v>800</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>731</v>
+        <v>802</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>775</v>
+        <v>801</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>732</v>
+        <v>803</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>776</v>
+        <v>704</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>838</v>
+        <v>707</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>777</v>
+        <v>198</v>
       </c>
       <c r="B547" s="1" t="s">
-        <v>743</v>
+        <v>199</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>778</v>
+        <v>200</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>744</v>
+        <v>201</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>779</v>
+        <v>202</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>839</v>
+        <v>203</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>780</v>
+        <v>204</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>737</v>
+        <v>205</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>781</v>
+        <v>206</v>
       </c>
       <c r="B551" s="1" t="s">
-        <v>738</v>
+        <v>207</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>1080</v>
+        <v>208</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>1084</v>
+        <v>209</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>1081</v>
+        <v>210</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>1085</v>
+        <v>157</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>356</v>
+        <v>211</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>358</v>
+        <v>159</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>361</v>
+        <v>212</v>
       </c>
       <c r="B555" s="1" t="s">
-        <v>359</v>
+        <v>161</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>364</v>
+        <v>213</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>360</v>
+        <v>163</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>943</v>
+        <v>214</v>
       </c>
       <c r="B557" s="1" t="s">
-        <v>941</v>
+        <v>165</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>938</v>
+        <v>215</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>942</v>
+        <v>167</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>939</v>
+        <v>216</v>
       </c>
       <c r="B559" s="1" t="s">
-        <v>944</v>
+        <v>169</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>940</v>
+        <v>217</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>961</v>
+        <v>171</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>962</v>
+        <v>218</v>
       </c>
       <c r="B561" s="1" t="s">
-        <v>963</v>
+        <v>173</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>579</v>
+        <v>219</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>580</v>
+        <v>175</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>581</v>
+        <v>220</v>
       </c>
       <c r="B563" s="1" t="s">
-        <v>582</v>
+        <v>177</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>606</v>
+        <v>221</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>609</v>
+        <v>179</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>610</v>
+        <v>764</v>
       </c>
       <c r="B565" s="1" t="s">
-        <v>612</v>
+        <v>834</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>611</v>
+        <v>765</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>617</v>
+        <v>740</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>388</v>
+        <v>766</v>
       </c>
       <c r="B567" s="1" t="s">
-        <v>394</v>
+        <v>741</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>390</v>
+        <v>767</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>395</v>
+        <v>835</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>392</v>
+        <v>768</v>
       </c>
       <c r="B569" s="1" t="s">
-        <v>396</v>
+        <v>728</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>703</v>
+        <v>769</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>640</v>
+        <v>729</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>368</v>
+        <v>770</v>
       </c>
       <c r="B571" s="1" t="s">
-        <v>369</v>
+        <v>836</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>375</v>
+        <v>771</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>372</v>
+        <v>734</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>377</v>
+        <v>772</v>
       </c>
       <c r="B573" s="1" t="s">
-        <v>373</v>
+        <v>735</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>1020</v>
+        <v>773</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>983</v>
+        <v>837</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>1021</v>
+        <v>774</v>
       </c>
       <c r="B575" s="1" t="s">
-        <v>984</v>
+        <v>731</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>1022</v>
+        <v>775</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>985</v>
+        <v>732</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>875</v>
+        <v>776</v>
       </c>
       <c r="B577" s="1" t="s">
-        <v>876</v>
+        <v>838</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>873</v>
+        <v>777</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>877</v>
+        <v>743</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>874</v>
+        <v>778</v>
       </c>
       <c r="B579" s="1" t="s">
-        <v>878</v>
+        <v>744</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>798</v>
+        <v>779</v>
       </c>
       <c r="B580" s="1" t="s">
-        <v>796</v>
+        <v>839</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>222</v>
+        <v>780</v>
       </c>
       <c r="B581" s="1" t="s">
-        <v>223</v>
+        <v>737</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>224</v>
+        <v>781</v>
       </c>
       <c r="B582" s="1" t="s">
-        <v>225</v>
+        <v>738</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>723</v>
+        <v>1280</v>
       </c>
       <c r="B583" s="1" t="s">
-        <v>686</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>724</v>
+        <v>1281</v>
       </c>
       <c r="B584" s="1" t="s">
-        <v>561</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>782</v>
+        <v>1284</v>
       </c>
       <c r="B585" s="1" t="s">
-        <v>544</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>725</v>
+        <v>1079</v>
       </c>
       <c r="B586" s="1" t="s">
-        <v>545</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>726</v>
+        <v>1080</v>
       </c>
       <c r="B587" s="1" t="s">
-        <v>546</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>783</v>
+        <v>356</v>
       </c>
       <c r="B588" s="1" t="s">
-        <v>785</v>
+        <v>358</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>784</v>
+        <v>361</v>
       </c>
       <c r="B589" s="1" t="s">
-        <v>786</v>
+        <v>359</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>715</v>
+        <v>364</v>
       </c>
       <c r="B590" s="1" t="s">
-        <v>714</v>
+        <v>360</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>928</v>
+        <v>1249</v>
       </c>
       <c r="B591" s="1" t="s">
-        <v>687</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B592" s="1" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A593" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B593" s="1" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A594" t="s">
+        <v>943</v>
+      </c>
+      <c r="B594" s="1" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A595" t="s">
+        <v>938</v>
+      </c>
+      <c r="B595" s="1" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A596" t="s">
+        <v>939</v>
+      </c>
+      <c r="B596" s="1" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A597" t="s">
+        <v>940</v>
+      </c>
+      <c r="B597" s="1" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A598" t="s">
+        <v>962</v>
+      </c>
+      <c r="B598" s="1" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A599" t="s">
+        <v>579</v>
+      </c>
+      <c r="B599" s="1" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A600" t="s">
+        <v>581</v>
+      </c>
+      <c r="B600" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A601" t="s">
+        <v>606</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A602" t="s">
+        <v>610</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A603" t="s">
+        <v>611</v>
+      </c>
+      <c r="B603" s="1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A604" t="s">
+        <v>388</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A605" t="s">
+        <v>390</v>
+      </c>
+      <c r="B605" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A606" t="s">
+        <v>392</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A607" t="s">
+        <v>703</v>
+      </c>
+      <c r="B607" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A608" t="s">
+        <v>368</v>
+      </c>
+      <c r="B608" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A609" t="s">
+        <v>375</v>
+      </c>
+      <c r="B609" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A610" t="s">
+        <v>377</v>
+      </c>
+      <c r="B610" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A611" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B611" s="1" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A612" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A613" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B613" s="1" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A614" t="s">
+        <v>875</v>
+      </c>
+      <c r="B614" s="1" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A615" t="s">
+        <v>873</v>
+      </c>
+      <c r="B615" s="1" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A616" t="s">
+        <v>874</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A617" t="s">
+        <v>798</v>
+      </c>
+      <c r="B617" s="1" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A618" t="s">
+        <v>222</v>
+      </c>
+      <c r="B618" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A619" t="s">
+        <v>224</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A620" t="s">
+        <v>723</v>
+      </c>
+      <c r="B620" s="1" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A621" t="s">
+        <v>724</v>
+      </c>
+      <c r="B621" s="1" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A622" t="s">
+        <v>782</v>
+      </c>
+      <c r="B622" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A623" t="s">
+        <v>725</v>
+      </c>
+      <c r="B623" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A624" t="s">
+        <v>726</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A625" t="s">
+        <v>783</v>
+      </c>
+      <c r="B625" s="1" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A626" t="s">
+        <v>784</v>
+      </c>
+      <c r="B626" s="1" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A627" t="s">
+        <v>715</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A628" t="s">
+        <v>928</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A629" t="s">
         <v>841</v>
       </c>
-      <c r="B592" s="1" t="s">
+      <c r="B629" s="1" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A593" t="s">
+    <row r="630" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A630" t="s">
         <v>840</v>
       </c>
-      <c r="B593" s="1" t="s">
+      <c r="B630" s="1" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A594" t="s">
+    <row r="631" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A631" t="s">
         <v>509</v>
       </c>
-      <c r="B594" s="1" t="s">
+      <c r="B631" s="1" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A595" t="s">
+    <row r="632" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A632" t="s">
         <v>845</v>
       </c>
-      <c r="B595" s="1" t="s">
+      <c r="B632" s="1" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A596" t="s">
+    <row r="633" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A633" t="s">
         <v>846</v>
       </c>
-      <c r="B596" s="1" t="s">
+      <c r="B633" s="1" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A597" t="s">
+    <row r="634" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A634" t="s">
         <v>847</v>
       </c>
-      <c r="B597" s="1" t="s">
+      <c r="B634" s="1" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A598" t="s">
+    <row r="635" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A635" t="s">
         <v>690</v>
       </c>
-      <c r="B598" s="1" t="s">
+      <c r="B635" s="1" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A599" t="s">
+    <row r="636" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A636" t="s">
         <v>688</v>
       </c>
-      <c r="B599" s="1" t="s">
+      <c r="B636" s="1" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A600" t="s">
+    <row r="637" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A637" t="s">
         <v>689</v>
       </c>
-      <c r="B600" s="1" t="s">
+      <c r="B637" s="1" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A601" t="s">
+    <row r="638" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A638" t="s">
         <v>999</v>
       </c>
-      <c r="B601" s="1" t="s">
+      <c r="B638" s="1" t="s">
         <v>1001</v>
       </c>
     </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A602" t="s">
+    <row r="639" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A639" t="s">
         <v>1000</v>
       </c>
-      <c r="B602" s="1" t="s">
+      <c r="B639" s="1" t="s">
         <v>1002</v>
       </c>
     </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A603" t="s">
+    <row r="640" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A640" t="s">
         <v>379</v>
       </c>
-      <c r="B603" s="1" t="s">
+      <c r="B640" s="1" t="s">
         <v>380</v>
-      </c>
-    </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A604" t="s">
-        <v>384</v>
-      </c>
-      <c r="B604" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A605" t="s">
-        <v>385</v>
-      </c>
-      <c r="B605" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A606" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B606" s="1" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C606" s="2" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A607" t="s">
-        <v>226</v>
-      </c>
-      <c r="B607" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C607" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A608" t="s">
-        <v>316</v>
-      </c>
-      <c r="B608" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C608" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A609" t="s">
-        <v>228</v>
-      </c>
-      <c r="B609" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="C609" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A610" t="s">
-        <v>456</v>
-      </c>
-      <c r="B610" s="1" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A611" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B611" s="1" t="s">
-        <v>1070</v>
-      </c>
-      <c r="C611" s="2" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A612" t="s">
-        <v>230</v>
-      </c>
-      <c r="B612" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="C612" s="2" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A613" t="s">
-        <v>275</v>
-      </c>
-      <c r="B613" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C613" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A614" t="s">
-        <v>276</v>
-      </c>
-      <c r="B614" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C614" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A615" t="s">
-        <v>231</v>
-      </c>
-      <c r="B615" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C615" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A616" t="s">
-        <v>247</v>
-      </c>
-      <c r="B616" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C616" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A617" t="s">
-        <v>251</v>
-      </c>
-      <c r="B617" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C617" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A618" t="s">
-        <v>233</v>
-      </c>
-      <c r="B618" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C618" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A619" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B619" s="1" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A620" t="s">
-        <v>298</v>
-      </c>
-      <c r="B620" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C620" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A621" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B621" s="1" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A622" t="s">
-        <v>821</v>
-      </c>
-      <c r="B622" s="1" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A623" t="s">
-        <v>273</v>
-      </c>
-      <c r="B623" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C623" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A624" t="s">
-        <v>274</v>
-      </c>
-      <c r="B624" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C624" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A625" t="s">
-        <v>314</v>
-      </c>
-      <c r="B625" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C625" s="2" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A626" t="s">
-        <v>235</v>
-      </c>
-      <c r="B626" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C626" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A627" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B627" s="1" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A628" t="s">
-        <v>315</v>
-      </c>
-      <c r="B628" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C628" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A629" t="s">
-        <v>311</v>
-      </c>
-      <c r="B629" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C629" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A630" t="s">
-        <v>237</v>
-      </c>
-      <c r="B630" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C630" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A631" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B631" s="1" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A632" t="s">
-        <v>822</v>
-      </c>
-      <c r="B632" s="1" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A633" t="s">
-        <v>239</v>
-      </c>
-      <c r="B633" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C633" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A634" t="s">
-        <v>250</v>
-      </c>
-      <c r="B634" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C634" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A635" t="s">
-        <v>254</v>
-      </c>
-      <c r="B635" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C635" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A636" t="s">
-        <v>583</v>
-      </c>
-      <c r="B636" s="1" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A637" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B637" s="1" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A638" t="s">
-        <v>585</v>
-      </c>
-      <c r="B638" s="1" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A639" t="s">
-        <v>819</v>
-      </c>
-      <c r="B639" s="1" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A640" t="s">
-        <v>820</v>
-      </c>
-      <c r="B640" s="1" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>347</v>
+        <v>384</v>
       </c>
       <c r="B641" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C641" s="2" t="s">
-        <v>353</v>
+        <v>382</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>1005</v>
+        <v>385</v>
       </c>
       <c r="B642" s="1" t="s">
-        <v>1012</v>
+        <v>383</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>823</v>
+        <v>1072</v>
       </c>
       <c r="B643" s="1" t="s">
-        <v>828</v>
+        <v>1073</v>
+      </c>
+      <c r="C643" s="2" t="s">
+        <v>1074</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>313</v>
+        <v>226</v>
       </c>
       <c r="B644" s="1" t="s">
-        <v>319</v>
+        <v>227</v>
+      </c>
+      <c r="C644" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>241</v>
+        <v>316</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>242</v>
+        <v>318</v>
       </c>
       <c r="C645" s="2" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>1006</v>
+        <v>228</v>
       </c>
       <c r="B646" s="1" t="s">
-        <v>1013</v>
+        <v>229</v>
+      </c>
+      <c r="C646" s="2" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>243</v>
+        <v>456</v>
       </c>
       <c r="B647" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C647" s="2" t="s">
-        <v>244</v>
+        <v>464</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>249</v>
+        <v>1077</v>
       </c>
       <c r="B648" s="1" t="s">
-        <v>256</v>
+        <v>1069</v>
       </c>
       <c r="C648" s="2" t="s">
-        <v>268</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="B649" s="1" t="s">
-        <v>259</v>
+        <v>601</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>269</v>
+        <v>602</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="B650" s="1" t="s">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="C650" s="2" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>1069</v>
+        <v>276</v>
       </c>
       <c r="B651" s="1" t="s">
-        <v>1072</v>
+        <v>279</v>
       </c>
       <c r="C651" s="2" t="s">
-        <v>1076</v>
+        <v>283</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="B652" s="1" t="s">
-        <v>257</v>
+        <v>232</v>
       </c>
       <c r="C652" s="2" t="s">
-        <v>270</v>
+        <v>232</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B653" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C653" s="2" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
+        <v>251</v>
+      </c>
+      <c r="B654" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C654" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A655" t="s">
+        <v>233</v>
+      </c>
+      <c r="B655" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C655" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A656" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B656" s="1" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A657" t="s">
+        <v>298</v>
+      </c>
+      <c r="B657" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C657" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A658" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B658" s="1" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A659" t="s">
+        <v>821</v>
+      </c>
+      <c r="B659" s="1" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A660" t="s">
+        <v>273</v>
+      </c>
+      <c r="B660" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C660" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A661" t="s">
+        <v>274</v>
+      </c>
+      <c r="B661" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C661" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A662" t="s">
+        <v>314</v>
+      </c>
+      <c r="B662" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C662" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A663" t="s">
+        <v>235</v>
+      </c>
+      <c r="B663" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C663" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A664" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B664" s="1" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A665" t="s">
+        <v>315</v>
+      </c>
+      <c r="B665" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C665" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A666" t="s">
+        <v>311</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C666" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A667" t="s">
+        <v>237</v>
+      </c>
+      <c r="B667" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C667" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A668" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B668" s="1" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A669" t="s">
+        <v>822</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A670" t="s">
+        <v>239</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C670" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A671" t="s">
+        <v>250</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C671" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A672" t="s">
+        <v>254</v>
+      </c>
+      <c r="B672" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C672" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A673" t="s">
+        <v>583</v>
+      </c>
+      <c r="B673" s="1" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A674" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B674" s="1" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A675" t="s">
+        <v>585</v>
+      </c>
+      <c r="B675" s="1" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A676" t="s">
+        <v>819</v>
+      </c>
+      <c r="B676" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A677" t="s">
+        <v>820</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A678" t="s">
+        <v>347</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C678" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A679" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B679" s="1" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A680" t="s">
+        <v>823</v>
+      </c>
+      <c r="B680" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A681" t="s">
+        <v>313</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A682" t="s">
+        <v>241</v>
+      </c>
+      <c r="B682" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C682" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A683" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B683" s="1" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A684" t="s">
+        <v>243</v>
+      </c>
+      <c r="B684" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C684" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A685" t="s">
+        <v>249</v>
+      </c>
+      <c r="B685" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C685" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A686" t="s">
+        <v>253</v>
+      </c>
+      <c r="B686" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C686" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A687" t="s">
+        <v>245</v>
+      </c>
+      <c r="B687" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C687" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A688" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B688" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C688" s="2" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A689" t="s">
+        <v>248</v>
+      </c>
+      <c r="B689" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C689" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A690" t="s">
+        <v>252</v>
+      </c>
+      <c r="B690" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C690" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A691" t="s">
         <v>312</v>
       </c>
-      <c r="B654" s="1" t="s">
+      <c r="B691" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C654" s="2" t="s">
+      <c r="C691" s="2" t="s">
         <v>330</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K647">
-    <sortState ref="A2:K654">
-      <sortCondition ref="A1:A647"/>
+  <autoFilter ref="A1:K691">
+    <sortState ref="A2:K691">
+      <sortCondition ref="A1:A691"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10068,34 +10577,34 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
   </sheetData>

--- a/gui/rebalance_localizations.xlsx
+++ b/gui/rebalance_localizations.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WinData\EpicGames\Riftbreaker\TheRiftbreaker\mods\rebalance\gui\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WinData\steam\steamapps\common\Riftbreaker\mods\rebalance\gui\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">rebalance_localizations!$A$1:$K$691</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">rebalance_localizations!$A$1:$K$721</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="1317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="1394">
   <si>
     <t>ENGLISH</t>
   </si>
@@ -223,9 +223,6 @@
     <t>gui/hud/building_description/strip_mine</t>
   </si>
   <si>
-    <t>Mines resources from surface outcrops</t>
-  </si>
-  <si>
     <t>gui/hud/building_description/supercoolant_refinery_lvl_2</t>
   </si>
   <si>
@@ -913,12 +910,6 @@
     <t>gui/hud/building_description/mining_drill_lvl_3</t>
   </si>
   <si>
-    <t>Mines for underground resource veins</t>
-  </si>
-  <si>
-    <t>Mines for underground resource veins. More effective by dissolving metals</t>
-  </si>
-  <si>
     <t>resource_name/fluorine</t>
   </si>
   <si>
@@ -3808,18 +3799,6 @@
     <t>gui/hud/building_description/strip_mine_lvl_3</t>
   </si>
   <si>
-    <t>Mines resources from surface outcrops. REQUIRES: ore mill to operate</t>
-  </si>
-  <si>
-    <t>Mines resources from surface outcrops. REQUIRES: level 2 ore mill to operate</t>
-  </si>
-  <si>
-    <t>Mines for underground resource veins. REQUIRES: level 2 ore mill to operate</t>
-  </si>
-  <si>
-    <t>Mines for underground resource veins. REQUIRES: ore mill to operate</t>
-  </si>
-  <si>
     <t>gui/hud/building_description/ore_mill_lvl_2</t>
   </si>
   <si>
@@ -3974,6 +3953,258 @@
   </si>
   <si>
     <t>Produces alloys from palladium and molten iron</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/ore_mill_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/ore_mill_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/ore_mill_lvl_4</t>
+  </si>
+  <si>
+    <t>Ore Mill (+100%)</t>
+  </si>
+  <si>
+    <t>Ore Mill (+150%)</t>
+  </si>
+  <si>
+    <t>Ore Mill (+200%)</t>
+  </si>
+  <si>
+    <t>Mines resources from surface outcrops. Wastes 50% of resource deposit</t>
+  </si>
+  <si>
+    <t>Mines resources from surface outcrops. REQUIRES: ore mill to operate. Wastes 25% of resource deposit</t>
+  </si>
+  <si>
+    <t>Mines for underground resource veins. REQUIRES: ore mill to operate. Wastes 50% of resource deposit</t>
+  </si>
+  <si>
+    <t>Mines resources from surface outcrops. REQUIRES: ore mill to operate. No wasted resources</t>
+  </si>
+  <si>
+    <t>Mines for underground resource veins. REQUIRES: ore mill to operate. Wastes 25% of resource deposit</t>
+  </si>
+  <si>
+    <t>Mines for underground resource veins. REQUIRES: ore mill to operate. No wasted resorces</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/regenerating_extractor</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/regenerating_extractor</t>
+  </si>
+  <si>
+    <t>Mycilium Extractor</t>
+  </si>
+  <si>
+    <t>Extracts resources from sourface deposits via special mycelia and use of resin. This is much slower but long term sustainable extraction that does not deplete the deposit.</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/regenerating_extractor</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/regenerating_extractor_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/regenerating_extractor_lvl_3</t>
+  </si>
+  <si>
+    <t>Mycelium Extractor</t>
+  </si>
+  <si>
+    <t>Improved Mycelium Extractor</t>
+  </si>
+  <si>
+    <t>Optimized Mycelium Extractor</t>
+  </si>
+  <si>
+    <t>The newly discovered resin resource allows to power special local mycelia that are able to extract most resources in a sustainable way albeit much slower then conventional methods. This method applies to surface outcrops only and does not deplete them.</t>
+  </si>
+  <si>
+    <t>Improvments on the mycelium allow a hiegher yield at increased maintencance</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/regenerating_extractor_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/regenerating_extractor_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/regenerating_extractor</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/cryo_technology_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/cryo_technology_lvl_2</t>
+  </si>
+  <si>
+    <t>Advanced Cryo Technology</t>
+  </si>
+  <si>
+    <t>Improved harnessing of ferdonite allows even more effective application of specialized ground cooling. This creates larger areas usable for buildings in magma biome</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/heat_charger</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/heat_charger_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/heat_charger_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/heat_charger</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/heat_charger</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/heat_charger</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/heat_charger_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/heat_charger_lvl_3</t>
+  </si>
+  <si>
+    <t>Thermal Ionization</t>
+  </si>
+  <si>
+    <t>Improved Thermal Ionization</t>
+  </si>
+  <si>
+    <t>Optimized Thermal Ionization</t>
+  </si>
+  <si>
+    <t>Utilizes extreme heat enegry to achieve and maintain highly ionized plasmas. But charge seperation remains difficult allowing for only low extraction of supercharged plasma</t>
+  </si>
+  <si>
+    <t>Improves thermal ionization and the consequent charge separation process by application of rhodonite to greatly increase yield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimizes thermal ionization process by usage of palladium components to maximazie yield </t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/thermal_ion_charger</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/thermal_ion_charger</t>
+  </si>
+  <si>
+    <t>Uses extreme ambient heat to ionize air into superchareged plasma</t>
+  </si>
+  <si>
+    <t>Ambient Heat Ion Charger</t>
+  </si>
+  <si>
+    <t>Thermal Ion Charger</t>
+  </si>
+  <si>
+    <t>Uses extreme heat energy of magma to ionize air into superchareged plasma</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/planet_defense</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/planet_defense_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/planet_defense_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/planet_defense</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/planet_defense_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/planet_defense_lvl_3</t>
+  </si>
+  <si>
+    <t>Obital Defense</t>
+  </si>
+  <si>
+    <t>Advanced Orbital Defense</t>
+  </si>
+  <si>
+    <t>Optimized Orbital Defense</t>
+  </si>
+  <si>
+    <t>Upgrades the planetary scanner satelites with powerful orbital defense laser thus changes the buildings from a purely passive role to an active one.</t>
+  </si>
+  <si>
+    <t>Upgrades firepower for orbital defense satelites</t>
+  </si>
+  <si>
+    <t>Optimized firepower for orbital defense satelites</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/planet_defense</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/planet_defense</t>
+  </si>
+  <si>
+    <t>Orbital Defense Station</t>
+  </si>
+  <si>
+    <t>Expanded planetary scanner with orbital defense laser satelites</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/tower_cannon_cooled_lvl_2</t>
+  </si>
+  <si>
+    <t>90mm Gun Tower - Supercooled</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/tower_ice_big</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/tower_ice_big</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/tower_ice_big</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/tower_ice_big_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/tower_ice_big_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/tower_ice_big</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/tower_ice_big_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/tower_ice_big_lvl_3</t>
+  </si>
+  <si>
+    <t>Piercer Tower</t>
+  </si>
+  <si>
+    <t>Landlocked version of the floating piercer tower. Requires large upkeep of cooling liquid.</t>
+  </si>
+  <si>
+    <t>Landlocked Piercer Tower Variant</t>
+  </si>
+  <si>
+    <t>Optimized Piercer Tower</t>
+  </si>
+  <si>
+    <t>Advanced Piercer Tower</t>
+  </si>
+  <si>
+    <t>Landlocked version of the floating piercer tower. Requires large fluid upkeep used for cooling</t>
+  </si>
+  <si>
+    <t>Upgraded firepower for piercer tower</t>
   </si>
 </sst>
 </file>
@@ -4816,7 +5047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K691"/>
+  <dimension ref="A1:K729"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="65.453125" customWidth="1"/>
@@ -4858,34 +5089,34 @@
     </row>
     <row r="2" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1293</v>
+        <v>1286</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1313</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>1296</v>
+        <v>1289</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1316</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>1294</v>
+        <v>1287</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1314</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>1295</v>
+        <v>1288</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1315</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4922,10 +5153,10 @@
     </row>
     <row r="10" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4949,15 +5180,15 @@
         <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4986,10 +5217,10 @@
     </row>
     <row r="18" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5042,18 +5273,18 @@
     </row>
     <row r="25" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>1029</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5061,7 +5292,7 @@
         <v>41</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5077,7 +5308,7 @@
         <v>44</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5085,39 +5316,39 @@
         <v>45</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5125,544 +5356,544 @@
         <v>46</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>1060</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>1274</v>
+        <v>1267</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1273</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>1064</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>989</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>992</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>47</v>
+        <v>1344</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>48</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>1111</v>
+        <v>51</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>1105</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>332</v>
+        <v>1109</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="C64" s="2" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>285</v>
-      </c>
       <c r="B65" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>324</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
+        <v>284</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>293</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>294</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>294</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>1264</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>295</v>
-      </c>
       <c r="B68" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>295</v>
+        <v>53</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>60</v>
+        <v>1243</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>1246</v>
+        <v>1258</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>1269</v>
+        <v>1263</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>1270</v>
+        <v>567</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
+        <v>569</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>570</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>572</v>
+        <v>1373</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>573</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B82" s="1" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>612</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+      <c r="B84" s="1" t="s">
         <v>615</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>616</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>974</v>
+        <v>1322</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>865</v>
+        <v>976</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>868</v>
+        <v>987</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>637</v>
+        <v>864</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>644</v>
+        <v>866</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>793</v>
+        <v>631</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>794</v>
+        <v>640</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>303</v>
+        <v>790</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>310</v>
+        <v>791</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>61</v>
+        <v>300</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>62</v>
+        <v>303</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>62</v>
@@ -5670,7 +5901,7 @@
     </row>
     <row r="102" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>62</v>
@@ -5678,354 +5909,354 @@
     </row>
     <row r="103" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>1114</v>
+        <v>64</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>1119</v>
+        <v>62</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>1116</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>65</v>
+        <v>1114</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>66</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>1259</v>
+        <v>65</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>1261</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>1262</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>662</v>
+        <v>1257</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>604</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>663</v>
+        <v>601</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
+        <v>658</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>660</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>67</v>
+        <v>657</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>68</v>
+        <v>661</v>
       </c>
     </row>
     <row r="113" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="114" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>436</v>
+        <v>68</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>466</v>
+        <v>69</v>
       </c>
     </row>
     <row r="115" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>437</v>
+        <v>1355</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>467</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="116" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
     </row>
     <row r="117" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
     </row>
     <row r="118" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>71</v>
+        <v>441</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>72</v>
+        <v>470</v>
       </c>
     </row>
     <row r="119" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>409</v>
+        <v>442</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>486</v>
+        <v>471</v>
       </c>
     </row>
     <row r="120" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>408</v>
+        <v>70</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>483</v>
+        <v>71</v>
       </c>
     </row>
     <row r="121" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="122" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="123" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>507</v>
+        <v>407</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>442</v>
+        <v>411</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
     </row>
     <row r="125" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>443</v>
+        <v>504</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>438</v>
+        <v>1379</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>469</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="127" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="128" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>559</v>
+        <v>469</v>
       </c>
     </row>
     <row r="129" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="130" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
     </row>
     <row r="131" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>478</v>
+        <v>556</v>
       </c>
     </row>
     <row r="132" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
     </row>
     <row r="133" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
     </row>
     <row r="134" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
     </row>
     <row r="135" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="136" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="137" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="138" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>498</v>
+        <v>449</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>502</v>
+        <v>478</v>
       </c>
     </row>
     <row r="139" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>499</v>
+        <v>443</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>560</v>
+        <v>472</v>
       </c>
     </row>
     <row r="140" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>497</v>
+        <v>444</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>503</v>
+        <v>473</v>
       </c>
     </row>
     <row r="141" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>1131</v>
+        <v>495</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>1139</v>
+        <v>499</v>
       </c>
     </row>
     <row r="142" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>1132</v>
+        <v>496</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>1134</v>
+        <v>557</v>
       </c>
     </row>
     <row r="143" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>1133</v>
+        <v>494</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>1134</v>
+        <v>500</v>
       </c>
     </row>
     <row r="144" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="145" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>1140</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="146" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>1141</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="147" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6033,7 +6264,7 @@
         <v>1123</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="148" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6041,7 +6272,7 @@
         <v>1124</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="149" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6049,2036 +6280,2036 @@
         <v>1125</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="150" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>1135</v>
+        <v>1120</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1138</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="151" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>1136</v>
+        <v>1121</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>1142</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="152" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>1137</v>
+        <v>1122</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>1142</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="153" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>73</v>
+        <v>1132</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>74</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>1289</v>
+        <v>1133</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>1303</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="155" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>1292</v>
+        <v>1134</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>1306</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="156" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>1290</v>
+        <v>72</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>1304</v>
+        <v>73</v>
       </c>
     </row>
     <row r="157" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>1291</v>
+        <v>1282</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>1305</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>75</v>
+        <v>1285</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>76</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="159" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>77</v>
+        <v>1283</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>78</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>79</v>
+        <v>1284</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>400</v>
+        <v>76</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>87</v>
+        <v>397</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>541</v>
+        <v>401</v>
       </c>
     </row>
     <row r="166" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>540</v>
+        <v>83</v>
       </c>
     </row>
     <row r="167" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="168" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>91</v>
+        <v>538</v>
       </c>
     </row>
     <row r="169" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>92</v>
+        <v>536</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>93</v>
+        <v>537</v>
       </c>
     </row>
     <row r="170" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>401</v>
+        <v>87</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>405</v>
+        <v>88</v>
       </c>
     </row>
     <row r="171" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="172" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="173" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>98</v>
+        <v>398</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>99</v>
+        <v>402</v>
       </c>
     </row>
     <row r="174" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="175" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="177" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>1030</v>
+        <v>99</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>1031</v>
+        <v>100</v>
       </c>
     </row>
     <row r="178" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="179" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="180" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>110</v>
+        <v>1027</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>111</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="181" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="182" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>454</v>
+        <v>107</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>462</v>
+        <v>108</v>
       </c>
     </row>
     <row r="183" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>1097</v>
+        <v>109</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>1078</v>
+        <v>110</v>
       </c>
     </row>
     <row r="184" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>594</v>
+        <v>111</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>595</v>
+        <v>112</v>
       </c>
     </row>
     <row r="185" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="186" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>114</v>
+        <v>1094</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>115</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="187" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>1061</v>
+        <v>591</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>1062</v>
+        <v>592</v>
       </c>
     </row>
     <row r="188" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>1272</v>
+        <v>452</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>1271</v>
+        <v>460</v>
       </c>
     </row>
     <row r="189" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>1054</v>
+        <v>113</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>1056</v>
+        <v>114</v>
       </c>
     </row>
     <row r="190" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>881</v>
+        <v>1058</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>884</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="191" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>880</v>
+        <v>1265</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>883</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="192" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>898</v>
+        <v>1051</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>886</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>1065</v>
+        <v>877</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>1066</v>
+        <v>880</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>334</v>
+        <v>895</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>336</v>
+        <v>883</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>417</v>
+        <v>879</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>459</v>
+        <v>882</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>993</v>
+        <v>1062</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>996</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>304</v>
+        <v>414</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>1100</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>307</v>
+        <v>456</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>305</v>
+        <v>990</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>1100</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>307</v>
+        <v>993</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>605</v>
+        <v>299</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>608</v>
+        <v>1096</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>116</v>
+        <v>301</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>117</v>
+        <v>1097</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>1109</v>
+        <v>302</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>1107</v>
+        <v>1097</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>1110</v>
+        <v>602</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>1106</v>
+        <v>605</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>333</v>
+        <v>1345</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>328</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>286</v>
+        <v>115</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>293</v>
+        <v>116</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>287</v>
+        <v>1106</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>864</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>288</v>
+        <v>1107</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>864</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>118</v>
+        <v>330</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>119</v>
+        <v>323</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>120</v>
+        <v>285</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>121</v>
+        <v>292</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>122</v>
+        <v>286</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>121</v>
+        <v>861</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>123</v>
+        <v>287</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>121</v>
+        <v>861</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>1245</v>
+        <v>117</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>1247</v>
+        <v>118</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>574</v>
+        <v>119</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>575</v>
+        <v>120</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>343</v>
+        <v>121</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>354</v>
+        <v>120</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>344</v>
+        <v>122</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>354</v>
+        <v>120</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>345</v>
+        <v>1242</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>354</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>346</v>
+        <v>1310</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>355</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>975</v>
+        <v>1311</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>986</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>976</v>
+        <v>1312</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>987</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>977</v>
+        <v>571</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>988</v>
+        <v>572</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>860</v>
+        <v>1374</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>861</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>862</v>
+        <v>340</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>861</v>
+        <v>347</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>863</v>
+        <v>341</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>347</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>635</v>
+        <v>342</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>347</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
+        <v>343</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>972</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>973</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>974</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>857</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>859</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>860</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>632</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A227" t="s">
+    </row>
+    <row r="235" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
         <v>633</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A228" t="s">
-        <v>795</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A229" t="s">
+      <c r="B235" s="1" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>630</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>792</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>123</v>
+      </c>
+      <c r="B238" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B229" s="1" t="s">
+    </row>
+    <row r="239" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="230" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A230" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B230" s="1" t="s">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="231" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A231" t="s">
+      <c r="B240" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A232" t="s">
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>289</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B232" s="1" t="s">
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>288</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>291</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A233" t="s">
-        <v>289</v>
-      </c>
-      <c r="B233" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A234" t="s">
-        <v>648</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A235" t="s">
-        <v>645</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="236" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A236" t="s">
-        <v>646</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="237" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A237" t="s">
-        <v>418</v>
-      </c>
-      <c r="B237" s="1" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A238" t="s">
-        <v>419</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A239" t="s">
-        <v>426</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A240" t="s">
-        <v>427</v>
-      </c>
-      <c r="B240" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="241" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A241" t="s">
-        <v>128</v>
-      </c>
-      <c r="B241" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A242" t="s">
-        <v>412</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>411</v>
+        <v>645</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>544</v>
+        <v>644</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>413</v>
+        <v>642</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>545</v>
+        <v>646</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>415</v>
+        <v>643</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>546</v>
+        <v>647</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>787</v>
+        <v>1356</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>785</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>788</v>
+        <v>415</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>786</v>
+        <v>547</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>504</v>
+        <v>416</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>505</v>
+        <v>546</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>562</v>
+        <v>545</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>563</v>
+        <v>544</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>421</v>
+        <v>127</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>564</v>
+        <v>128</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>566</v>
+        <v>541</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>567</v>
+        <v>542</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>460</v>
+        <v>543</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>431</v>
+        <v>784</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>551</v>
+        <v>782</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>432</v>
+        <v>785</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>552</v>
+        <v>783</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>433</v>
+        <v>501</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>553</v>
+        <v>502</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>435</v>
+        <v>1380</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>461</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>494</v>
+        <v>419</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>496</v>
+        <v>420</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>506</v>
+        <v>563</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>495</v>
+        <v>417</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>130</v>
+        <v>427</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>131</v>
+        <v>457</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>1048</v>
+        <v>428</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>1047</v>
+        <v>548</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>500</v>
+        <v>429</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>501</v>
+        <v>549</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>489</v>
+        <v>430</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>490</v>
+        <v>550</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>1046</v>
+        <v>432</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>1047</v>
+        <v>458</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>924</v>
+        <v>431</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>857</v>
+        <v>555</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>925</v>
+        <v>425</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>859</v>
+        <v>551</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>926</v>
+        <v>426</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>858</v>
+        <v>552</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>927</v>
+        <v>491</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>856</v>
+        <v>554</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>855</v>
+        <v>493</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>854</v>
+        <v>503</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>1143</v>
+        <v>492</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>1144</v>
+        <v>553</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>972</v>
+        <v>129</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>973</v>
+        <v>130</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>811</v>
+        <v>1045</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>815</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>812</v>
+        <v>497</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>816</v>
+        <v>498</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>1302</v>
+        <v>486</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>1311</v>
+        <v>487</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>1300</v>
+        <v>1043</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>1310</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>1301</v>
+        <v>921</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>1312</v>
+        <v>854</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>523</v>
+        <v>922</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>1171</v>
+        <v>856</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>1190</v>
+        <v>923</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>1172</v>
+        <v>855</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>524</v>
+        <v>924</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>1179</v>
+        <v>853</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>675</v>
+        <v>852</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>1180</v>
+        <v>851</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>525</v>
+        <v>1140</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>1175</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>1191</v>
+        <v>969</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>1174</v>
+        <v>970</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>526</v>
+        <v>808</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>1182</v>
+        <v>812</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>676</v>
+        <v>809</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>1181</v>
+        <v>813</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>527</v>
+        <v>1295</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>1176</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>1192</v>
+        <v>1293</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>1173</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>528</v>
+        <v>1294</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>1183</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>677</v>
+        <v>520</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>1184</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>529</v>
+        <v>1187</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>1177</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>1193</v>
+        <v>521</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>530</v>
+        <v>672</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>1185</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>678</v>
+        <v>522</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>1186</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>531</v>
+        <v>1188</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>1178</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>1194</v>
+        <v>523</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>1189</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>532</v>
+        <v>673</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>1187</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>679</v>
+        <v>524</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>1188</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>1041</v>
+        <v>1189</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>1044</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>1040</v>
+        <v>525</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>1045</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>1025</v>
+        <v>674</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>1035</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>1026</v>
+        <v>526</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>1034</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>132</v>
+        <v>1190</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>133</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>1204</v>
+        <v>527</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>1212</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>1220</v>
+        <v>675</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>1212</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>134</v>
+        <v>528</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>135</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>1206</v>
+        <v>1191</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>1214</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>1222</v>
+        <v>529</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>1214</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>136</v>
+        <v>676</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>137</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>138</v>
+        <v>1038</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>137</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>139</v>
+        <v>1037</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>137</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>621</v>
+        <v>1022</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>628</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>625</v>
+        <v>1023</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>629</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>626</v>
+        <v>131</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>630</v>
+        <v>132</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>140</v>
+        <v>1201</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>141</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>1205</v>
+        <v>1217</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>1221</v>
+        <v>133</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>1215</v>
+        <v>134</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>142</v>
+        <v>1203</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>143</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>1207</v>
+        <v>1219</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>1223</v>
+        <v>135</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>1213</v>
+        <v>136</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>699</v>
+        <v>137</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>702</v>
+        <v>136</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>700</v>
+        <v>138</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>710</v>
+        <v>136</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>701</v>
+        <v>618</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>711</v>
+        <v>625</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>491</v>
+        <v>622</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.35">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>1096</v>
+        <v>623</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>493</v>
+        <v>627</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>591</v>
+        <v>139</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="331" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>592</v>
+        <v>1202</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>593</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>1051</v>
+        <v>1218</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>1055</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>1052</v>
+        <v>141</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>1059</v>
+        <v>142</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>971</v>
+        <v>1204</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>967</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>958</v>
+        <v>1220</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>967</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>959</v>
+        <v>696</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>967</v>
+        <v>699</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>960</v>
+        <v>697</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>967</v>
+        <v>707</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>952</v>
+        <v>698</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>968</v>
+        <v>708</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>953</v>
+        <v>488</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>968</v>
+        <v>489</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>951</v>
+        <v>1093</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>968</v>
+        <v>490</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>954</v>
+        <v>588</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>968</v>
+        <v>600</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>657</v>
+        <v>590</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>655</v>
+        <v>1048</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>658</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>656</v>
+        <v>1049</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>659</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>891</v>
+        <v>968</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>1145</v>
+        <v>964</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>913</v>
+        <v>955</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>1149</v>
+        <v>964</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>917</v>
+        <v>956</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>1149</v>
+        <v>964</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>890</v>
+        <v>957</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>1147</v>
+        <v>964</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>914</v>
+        <v>949</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>1150</v>
+        <v>965</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>918</v>
+        <v>950</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>1150</v>
+        <v>965</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>896</v>
+        <v>948</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>1148</v>
+        <v>965</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>915</v>
+        <v>951</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>1151</v>
+        <v>965</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>919</v>
+        <v>595</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>1151</v>
+        <v>654</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>892</v>
+        <v>652</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>1146</v>
+        <v>655</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>916</v>
+        <v>653</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>1152</v>
+        <v>656</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>920</v>
+        <v>1338</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>1152</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>1236</v>
+        <v>888</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>1242</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>1237</v>
+        <v>910</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>1243</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>1238</v>
+        <v>914</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>1244</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>813</v>
+        <v>887</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>814</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>994</v>
+        <v>911</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>995</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>1091</v>
+        <v>915</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>1094</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>1092</v>
+        <v>893</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>1095</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>805</v>
+        <v>912</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>802</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>804</v>
+        <v>916</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>803</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>706</v>
+        <v>889</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>709</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>144</v>
+        <v>913</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>145</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>146</v>
+        <v>917</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>148</v>
+        <v>1233</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>149</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>150</v>
+        <v>1234</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>151</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>152</v>
+        <v>1235</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>153</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>154</v>
+        <v>810</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>155</v>
+        <v>811</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>156</v>
+        <v>991</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>157</v>
+        <v>992</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>158</v>
+        <v>1088</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>159</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>160</v>
+        <v>1089</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>161</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>162</v>
+        <v>802</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>163</v>
+        <v>799</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>164</v>
+        <v>801</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>165</v>
+        <v>800</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>166</v>
+        <v>703</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>167</v>
+        <v>706</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>170</v>
+        <v>1346</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>171</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>172</v>
+        <v>1347</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>173</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>174</v>
+        <v>1348</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>175</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>745</v>
+        <v>149</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>739</v>
+        <v>150</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>746</v>
+        <v>151</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>740</v>
+        <v>152</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>747</v>
+        <v>153</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>741</v>
+        <v>154</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>748</v>
+        <v>155</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>727</v>
+        <v>156</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>749</v>
+        <v>157</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>728</v>
+        <v>158</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>750</v>
+        <v>159</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>729</v>
+        <v>160</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>751</v>
+        <v>161</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>733</v>
+        <v>162</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>752</v>
+        <v>163</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>734</v>
+        <v>164</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>753</v>
+        <v>165</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>735</v>
+        <v>166</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>760</v>
+        <v>167</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>730</v>
+        <v>168</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>761</v>
+        <v>169</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>731</v>
+        <v>170</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>762</v>
+        <v>171</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>732</v>
+        <v>172</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>754</v>
+        <v>173</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>742</v>
+        <v>174</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>755</v>
+        <v>175</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>743</v>
+        <v>176</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>756</v>
+        <v>177</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>744</v>
+        <v>178</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>757</v>
+        <v>742</v>
       </c>
       <c r="B400" s="1" t="s">
         <v>736</v>
@@ -8086,7 +8317,7 @@
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>758</v>
+        <v>743</v>
       </c>
       <c r="B401" s="1" t="s">
         <v>737</v>
@@ -8094,7 +8325,7 @@
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>759</v>
+        <v>744</v>
       </c>
       <c r="B402" s="1" t="s">
         <v>738</v>
@@ -8102,2419 +8333,2723 @@
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>1278</v>
+        <v>745</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>1277</v>
+        <v>724</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>1279</v>
+        <v>746</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>1283</v>
+        <v>725</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>1282</v>
+        <v>747</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>1286</v>
+        <v>726</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>1081</v>
+        <v>748</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>1087</v>
+        <v>730</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>1082</v>
+        <v>749</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>1087</v>
+        <v>731</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>357</v>
+        <v>750</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>568</v>
+        <v>732</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>362</v>
+        <v>757</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>366</v>
+        <v>727</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>363</v>
+        <v>758</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>365</v>
+        <v>728</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>1252</v>
+        <v>759</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>1258</v>
+        <v>729</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>1253</v>
+        <v>751</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>1258</v>
+        <v>739</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>1254</v>
+        <v>752</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>1258</v>
+        <v>740</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>955</v>
+        <v>753</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>966</v>
+        <v>741</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>956</v>
+        <v>754</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>966</v>
+        <v>733</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>957</v>
+        <v>755</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>966</v>
+        <v>734</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>964</v>
+        <v>756</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>966</v>
+        <v>735</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>965</v>
+        <v>1271</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>966</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>576</v>
+        <v>1272</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>577</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>578</v>
+        <v>1275</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>577</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>389</v>
+        <v>1078</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>397</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>391</v>
+        <v>1079</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>398</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>393</v>
+        <v>354</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>399</v>
+        <v>565</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>705</v>
+        <v>359</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>708</v>
+        <v>363</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>374</v>
+        <v>1249</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>371</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>376</v>
+        <v>1250</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>371</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>980</v>
+        <v>1251</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>1022</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>981</v>
+        <v>952</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>1023</v>
+        <v>963</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>982</v>
+        <v>953</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>1024</v>
+        <v>963</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>872</v>
+        <v>954</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>879</v>
+        <v>963</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>871</v>
+        <v>961</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>868</v>
+        <v>963</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>870</v>
+        <v>962</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>879</v>
+        <v>963</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>797</v>
+        <v>573</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>799</v>
+        <v>574</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>180</v>
+        <v>575</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>181</v>
+        <v>574</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>182</v>
+        <v>1364</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>183</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>719</v>
+        <v>1365</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>684</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>720</v>
+        <v>1366</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>716</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>789</v>
+        <v>386</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>791</v>
+        <v>394</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>790</v>
+        <v>388</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>792</v>
+        <v>395</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>721</v>
+        <v>390</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>718</v>
+        <v>396</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>722</v>
+        <v>702</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>713</v>
+        <v>364</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>712</v>
+        <v>367</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>929</v>
+        <v>371</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>685</v>
+        <v>368</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>829</v>
+        <v>373</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>831</v>
+        <v>368</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>830</v>
+        <v>1336</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>831</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>510</v>
+        <v>1334</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>512</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>842</v>
+        <v>1335</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>851</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>843</v>
+        <v>977</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>852</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>844</v>
+        <v>978</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>853</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>691</v>
+        <v>979</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>683</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>997</v>
+        <v>869</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>1004</v>
+        <v>876</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>998</v>
+        <v>868</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>1003</v>
+        <v>865</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>378</v>
+        <v>867</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>381</v>
+        <v>876</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>763</v>
+        <v>794</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>569</v>
+        <v>796</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>386</v>
+        <v>179</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>387</v>
+        <v>180</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>817</v>
+        <v>181</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>818</v>
+        <v>182</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>806</v>
+        <v>716</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>809</v>
+        <v>681</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>807</v>
+        <v>717</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>810</v>
+        <v>713</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>1299</v>
+        <v>786</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>1309</v>
+        <v>788</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>1297</v>
+        <v>787</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>1307</v>
+        <v>789</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>1298</v>
+        <v>718</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>1308</v>
+        <v>715</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>513</v>
+        <v>719</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>533</v>
+        <v>714</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>1195</v>
+        <v>1384</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>1161</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>514</v>
+        <v>1385</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>670</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>669</v>
+        <v>1386</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>1164</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>515</v>
+        <v>710</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>536</v>
+        <v>709</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>1196</v>
+        <v>926</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>1167</v>
+        <v>682</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>516</v>
+        <v>826</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>671</v>
+        <v>828</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>668</v>
+        <v>827</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>1168</v>
+        <v>828</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>534</v>
+        <v>509</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>1197</v>
+        <v>839</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>1162</v>
+        <v>848</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>518</v>
+        <v>840</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>672</v>
+        <v>849</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>667</v>
+        <v>841</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>1165</v>
+        <v>850</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>519</v>
+        <v>688</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>537</v>
+        <v>680</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>1198</v>
+        <v>994</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>1169</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>520</v>
+        <v>995</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>673</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>666</v>
+        <v>375</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>1170</v>
+        <v>378</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>521</v>
+        <v>760</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>535</v>
+        <v>566</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>1199</v>
+        <v>383</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>1163</v>
+        <v>384</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>522</v>
+        <v>814</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>674</v>
+        <v>815</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>665</v>
+        <v>803</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>1166</v>
+        <v>806</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>1039</v>
+        <v>804</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>1042</v>
+        <v>807</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>1038</v>
+        <v>1292</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>1043</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>1027</v>
+        <v>1290</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>1036</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>1028</v>
+        <v>1291</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>1037</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>184</v>
+        <v>510</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>185</v>
+        <v>530</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>1200</v>
+        <v>1192</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>1208</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>1216</v>
+        <v>511</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>1224</v>
+        <v>667</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>186</v>
+        <v>666</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>187</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>1202</v>
+        <v>512</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>1210</v>
+        <v>533</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>1218</v>
+        <v>1193</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>1226</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>188</v>
+        <v>513</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>189</v>
+        <v>668</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>190</v>
+        <v>665</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>191</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>192</v>
+        <v>514</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>193</v>
+        <v>531</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>622</v>
+        <v>1194</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>627</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>623</v>
+        <v>515</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>631</v>
+        <v>669</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>624</v>
+        <v>664</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>632</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>194</v>
+        <v>516</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>195</v>
+        <v>534</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>1209</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>1217</v>
+        <v>517</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>1225</v>
+        <v>670</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>196</v>
+        <v>663</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>197</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>1203</v>
+        <v>518</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>1211</v>
+        <v>532</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>1219</v>
+        <v>1196</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>1227</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>693</v>
+        <v>519</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>696</v>
+        <v>671</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>694</v>
+        <v>662</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>697</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>695</v>
+        <v>1036</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>698</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>1103</v>
+        <v>1035</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>493</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>1104</v>
+        <v>1024</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>1086</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>587</v>
+        <v>1025</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>589</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>588</v>
+        <v>183</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>590</v>
+        <v>184</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>1049</v>
+        <v>1197</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>1057</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>1050</v>
+        <v>1213</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>1058</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>969</v>
+        <v>185</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>970</v>
+        <v>186</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>945</v>
+        <v>1199</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>948</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>946</v>
+        <v>1215</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>949</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>947</v>
+        <v>187</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>950</v>
+        <v>188</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>930</v>
+        <v>189</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>934</v>
+        <v>190</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>931</v>
+        <v>191</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>936</v>
+        <v>192</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>932</v>
+        <v>619</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>935</v>
+        <v>624</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>933</v>
+        <v>620</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>937</v>
+        <v>628</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>596</v>
+        <v>621</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>597</v>
+        <v>629</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>651</v>
+        <v>193</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>653</v>
+        <v>194</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>652</v>
+        <v>1198</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>654</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>888</v>
+        <v>1214</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>884</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>899</v>
+        <v>195</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>902</v>
+        <v>196</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>906</v>
+        <v>1200</v>
       </c>
       <c r="B527" s="1" t="s">
-        <v>909</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>887</v>
+        <v>1216</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>883</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>900</v>
+        <v>690</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>903</v>
+        <v>693</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>907</v>
+        <v>691</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>910</v>
+        <v>694</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>921</v>
+        <v>692</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>886</v>
+        <v>695</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>922</v>
+        <v>1100</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>904</v>
+        <v>490</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>923</v>
+        <v>1101</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>911</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>889</v>
+        <v>584</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>885</v>
+        <v>586</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>901</v>
+        <v>585</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>905</v>
+        <v>587</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>908</v>
+        <v>1046</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>912</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>1233</v>
+        <v>1047</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>1239</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>1234</v>
+        <v>966</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>1240</v>
+        <v>967</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>1235</v>
+        <v>942</v>
       </c>
       <c r="B539" s="1" t="s">
-        <v>1241</v>
+        <v>945</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>808</v>
+        <v>943</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>459</v>
+        <v>946</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>1018</v>
+        <v>944</v>
       </c>
       <c r="B541" s="1" t="s">
-        <v>996</v>
+        <v>947</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>1089</v>
+        <v>927</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>1088</v>
+        <v>931</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>1090</v>
+        <v>928</v>
       </c>
       <c r="B543" s="1" t="s">
-        <v>1093</v>
+        <v>933</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>800</v>
+        <v>929</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>802</v>
+        <v>932</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>801</v>
+        <v>930</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>803</v>
+        <v>934</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>704</v>
+        <v>593</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>707</v>
+        <v>594</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>198</v>
+        <v>648</v>
       </c>
       <c r="B547" s="1" t="s">
-        <v>199</v>
+        <v>650</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>200</v>
+        <v>649</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>201</v>
+        <v>651</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>202</v>
+        <v>1337</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>203</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>204</v>
+        <v>885</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>205</v>
+        <v>881</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>206</v>
+        <v>896</v>
       </c>
       <c r="B551" s="1" t="s">
-        <v>207</v>
+        <v>899</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>208</v>
+        <v>903</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>209</v>
+        <v>906</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>210</v>
+        <v>884</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>157</v>
+        <v>880</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>211</v>
+        <v>897</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>159</v>
+        <v>900</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>212</v>
+        <v>904</v>
       </c>
       <c r="B555" s="1" t="s">
-        <v>161</v>
+        <v>907</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>213</v>
+        <v>918</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>163</v>
+        <v>883</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>214</v>
+        <v>919</v>
       </c>
       <c r="B557" s="1" t="s">
-        <v>165</v>
+        <v>901</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>215</v>
+        <v>920</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>167</v>
+        <v>908</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>216</v>
+        <v>886</v>
       </c>
       <c r="B559" s="1" t="s">
-        <v>169</v>
+        <v>882</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>217</v>
+        <v>898</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>171</v>
+        <v>902</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>218</v>
+        <v>905</v>
       </c>
       <c r="B561" s="1" t="s">
-        <v>173</v>
+        <v>909</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>219</v>
+        <v>1230</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>175</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>220</v>
+        <v>1231</v>
       </c>
       <c r="B563" s="1" t="s">
-        <v>177</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>221</v>
+        <v>1232</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>179</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>764</v>
+        <v>805</v>
       </c>
       <c r="B565" s="1" t="s">
-        <v>834</v>
+        <v>456</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>765</v>
+        <v>1015</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>740</v>
+        <v>993</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>766</v>
+        <v>1086</v>
       </c>
       <c r="B567" s="1" t="s">
-        <v>741</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>767</v>
+        <v>1087</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>835</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="B569" s="1" t="s">
-        <v>728</v>
+        <v>799</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>769</v>
+        <v>798</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>729</v>
+        <v>800</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>770</v>
+        <v>701</v>
       </c>
       <c r="B571" s="1" t="s">
-        <v>836</v>
+        <v>704</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>771</v>
+        <v>197</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>734</v>
+        <v>198</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>772</v>
+        <v>1341</v>
       </c>
       <c r="B573" s="1" t="s">
-        <v>735</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>773</v>
+        <v>1342</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>837</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>774</v>
+        <v>1343</v>
       </c>
       <c r="B575" s="1" t="s">
-        <v>731</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>775</v>
+        <v>199</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>732</v>
+        <v>200</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>776</v>
+        <v>201</v>
       </c>
       <c r="B577" s="1" t="s">
-        <v>838</v>
+        <v>202</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>777</v>
+        <v>203</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>743</v>
+        <v>204</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>778</v>
+        <v>205</v>
       </c>
       <c r="B579" s="1" t="s">
-        <v>744</v>
+        <v>206</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>779</v>
+        <v>207</v>
       </c>
       <c r="B580" s="1" t="s">
-        <v>839</v>
+        <v>208</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>780</v>
+        <v>209</v>
       </c>
       <c r="B581" s="1" t="s">
-        <v>737</v>
+        <v>156</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>781</v>
+        <v>210</v>
       </c>
       <c r="B582" s="1" t="s">
-        <v>738</v>
+        <v>158</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>1280</v>
+        <v>211</v>
       </c>
       <c r="B583" s="1" t="s">
-        <v>1275</v>
+        <v>160</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>1281</v>
+        <v>212</v>
       </c>
       <c r="B584" s="1" t="s">
-        <v>1276</v>
+        <v>162</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>1284</v>
+        <v>213</v>
       </c>
       <c r="B585" s="1" t="s">
-        <v>1285</v>
+        <v>164</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>1079</v>
+        <v>214</v>
       </c>
       <c r="B586" s="1" t="s">
-        <v>1083</v>
+        <v>166</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>1080</v>
+        <v>215</v>
       </c>
       <c r="B587" s="1" t="s">
-        <v>1084</v>
+        <v>168</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>356</v>
+        <v>216</v>
       </c>
       <c r="B588" s="1" t="s">
-        <v>358</v>
+        <v>170</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>361</v>
+        <v>217</v>
       </c>
       <c r="B589" s="1" t="s">
-        <v>359</v>
+        <v>172</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>364</v>
+        <v>218</v>
       </c>
       <c r="B590" s="1" t="s">
-        <v>360</v>
+        <v>174</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>1249</v>
+        <v>219</v>
       </c>
       <c r="B591" s="1" t="s">
-        <v>1255</v>
+        <v>176</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>1250</v>
+        <v>220</v>
       </c>
       <c r="B592" s="1" t="s">
-        <v>1256</v>
+        <v>178</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>1251</v>
+        <v>761</v>
       </c>
       <c r="B593" s="1" t="s">
-        <v>1257</v>
+        <v>831</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>943</v>
+        <v>762</v>
       </c>
       <c r="B594" s="1" t="s">
-        <v>941</v>
+        <v>737</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>938</v>
+        <v>763</v>
       </c>
       <c r="B595" s="1" t="s">
-        <v>942</v>
+        <v>738</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>939</v>
+        <v>764</v>
       </c>
       <c r="B596" s="1" t="s">
-        <v>944</v>
+        <v>832</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>940</v>
+        <v>765</v>
       </c>
       <c r="B597" s="1" t="s">
-        <v>961</v>
+        <v>725</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>962</v>
+        <v>766</v>
       </c>
       <c r="B598" s="1" t="s">
-        <v>963</v>
+        <v>726</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>579</v>
+        <v>767</v>
       </c>
       <c r="B599" s="1" t="s">
-        <v>580</v>
+        <v>833</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>581</v>
+        <v>768</v>
       </c>
       <c r="B600" s="1" t="s">
-        <v>582</v>
+        <v>731</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>606</v>
+        <v>769</v>
       </c>
       <c r="B601" s="1" t="s">
-        <v>609</v>
+        <v>732</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>610</v>
+        <v>770</v>
       </c>
       <c r="B602" s="1" t="s">
-        <v>612</v>
+        <v>834</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>611</v>
+        <v>771</v>
       </c>
       <c r="B603" s="1" t="s">
-        <v>617</v>
+        <v>728</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>388</v>
+        <v>772</v>
       </c>
       <c r="B604" s="1" t="s">
-        <v>394</v>
+        <v>729</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>390</v>
+        <v>773</v>
       </c>
       <c r="B605" s="1" t="s">
-        <v>395</v>
+        <v>835</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>392</v>
+        <v>774</v>
       </c>
       <c r="B606" s="1" t="s">
-        <v>396</v>
+        <v>740</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>703</v>
+        <v>775</v>
       </c>
       <c r="B607" s="1" t="s">
-        <v>640</v>
+        <v>741</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>368</v>
+        <v>776</v>
       </c>
       <c r="B608" s="1" t="s">
-        <v>369</v>
+        <v>836</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>375</v>
+        <v>777</v>
       </c>
       <c r="B609" s="1" t="s">
-        <v>372</v>
+        <v>734</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>377</v>
+        <v>778</v>
       </c>
       <c r="B610" s="1" t="s">
-        <v>373</v>
+        <v>735</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>1019</v>
+        <v>1273</v>
       </c>
       <c r="B611" s="1" t="s">
-        <v>983</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>1020</v>
+        <v>1274</v>
       </c>
       <c r="B612" s="1" t="s">
-        <v>984</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>1021</v>
+        <v>1277</v>
       </c>
       <c r="B613" s="1" t="s">
-        <v>985</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>875</v>
+        <v>1076</v>
       </c>
       <c r="B614" s="1" t="s">
-        <v>876</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>873</v>
+        <v>1077</v>
       </c>
       <c r="B615" s="1" t="s">
-        <v>877</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>874</v>
+        <v>353</v>
       </c>
       <c r="B616" s="1" t="s">
-        <v>878</v>
+        <v>355</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>798</v>
+        <v>358</v>
       </c>
       <c r="B617" s="1" t="s">
-        <v>796</v>
+        <v>356</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>222</v>
+        <v>361</v>
       </c>
       <c r="B618" s="1" t="s">
-        <v>223</v>
+        <v>357</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>224</v>
+        <v>1246</v>
       </c>
       <c r="B619" s="1" t="s">
-        <v>225</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>723</v>
+        <v>1247</v>
       </c>
       <c r="B620" s="1" t="s">
-        <v>686</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>724</v>
+        <v>1248</v>
       </c>
       <c r="B621" s="1" t="s">
-        <v>561</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>782</v>
+        <v>940</v>
       </c>
       <c r="B622" s="1" t="s">
-        <v>544</v>
+        <v>938</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>725</v>
+        <v>935</v>
       </c>
       <c r="B623" s="1" t="s">
-        <v>545</v>
+        <v>939</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>726</v>
+        <v>936</v>
       </c>
       <c r="B624" s="1" t="s">
-        <v>546</v>
+        <v>941</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>783</v>
+        <v>937</v>
       </c>
       <c r="B625" s="1" t="s">
-        <v>785</v>
+        <v>958</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>784</v>
+        <v>959</v>
       </c>
       <c r="B626" s="1" t="s">
-        <v>786</v>
+        <v>960</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>715</v>
+        <v>576</v>
       </c>
       <c r="B627" s="1" t="s">
-        <v>714</v>
+        <v>577</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>928</v>
+        <v>578</v>
       </c>
       <c r="B628" s="1" t="s">
-        <v>687</v>
+        <v>579</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>841</v>
+        <v>1361</v>
       </c>
       <c r="B629" s="1" t="s">
-        <v>832</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>840</v>
+        <v>1362</v>
       </c>
       <c r="B630" s="1" t="s">
-        <v>833</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>509</v>
+        <v>1363</v>
       </c>
       <c r="B631" s="1" t="s">
-        <v>511</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>845</v>
+        <v>603</v>
       </c>
       <c r="B632" s="1" t="s">
-        <v>850</v>
+        <v>606</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>846</v>
+        <v>607</v>
       </c>
       <c r="B633" s="1" t="s">
-        <v>849</v>
+        <v>609</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>847</v>
+        <v>608</v>
       </c>
       <c r="B634" s="1" t="s">
-        <v>848</v>
+        <v>614</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>690</v>
+        <v>385</v>
       </c>
       <c r="B635" s="1" t="s">
-        <v>680</v>
+        <v>391</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>688</v>
+        <v>387</v>
       </c>
       <c r="B636" s="1" t="s">
-        <v>681</v>
+        <v>392</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>689</v>
+        <v>389</v>
       </c>
       <c r="B637" s="1" t="s">
-        <v>682</v>
+        <v>393</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>999</v>
+        <v>700</v>
       </c>
       <c r="B638" s="1" t="s">
-        <v>1001</v>
+        <v>637</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>1000</v>
+        <v>365</v>
       </c>
       <c r="B639" s="1" t="s">
-        <v>1002</v>
+        <v>366</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B640" s="1" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="641" spans="1:3" x14ac:dyDescent="0.35">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="B641" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.35">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>385</v>
+        <v>1326</v>
       </c>
       <c r="B642" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>1072</v>
+        <v>1327</v>
       </c>
       <c r="B643" s="1" t="s">
-        <v>1073</v>
-      </c>
-      <c r="C643" s="2" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>226</v>
+        <v>1328</v>
       </c>
       <c r="B644" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C644" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>316</v>
+        <v>1016</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C645" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.35">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>228</v>
+        <v>1017</v>
       </c>
       <c r="B646" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="C646" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.35">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>456</v>
+        <v>1018</v>
       </c>
       <c r="B647" s="1" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.35">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>1077</v>
+        <v>872</v>
       </c>
       <c r="B648" s="1" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C648" s="2" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.35">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>230</v>
+        <v>870</v>
       </c>
       <c r="B649" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="C649" s="2" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.35">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>275</v>
+        <v>871</v>
       </c>
       <c r="B650" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C650" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.35">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>276</v>
+        <v>795</v>
       </c>
       <c r="B651" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C651" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.35">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B652" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C652" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.35">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="B653" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C653" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.35">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>251</v>
+        <v>720</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C654" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.35">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
-        <v>233</v>
+        <v>721</v>
       </c>
       <c r="B655" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C655" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.35">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
-        <v>1009</v>
+        <v>779</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.35">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
-        <v>298</v>
+        <v>1377</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C657" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
-        <v>1008</v>
+        <v>722</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.35">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>821</v>
+        <v>723</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.35">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>273</v>
+        <v>780</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C660" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.35">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
-        <v>274</v>
+        <v>781</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C661" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.35">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
-        <v>314</v>
+        <v>1381</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C662" s="2" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
-        <v>235</v>
+        <v>1382</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>1287</v>
-      </c>
-      <c r="C663" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
-        <v>1010</v>
+        <v>1383</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
-        <v>315</v>
+        <v>712</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C665" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.35">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
-        <v>311</v>
+        <v>925</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C666" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.35">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
-        <v>237</v>
+        <v>838</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C667" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.35">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
-        <v>1007</v>
+        <v>837</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.35">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
-        <v>822</v>
+        <v>506</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.35">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
-        <v>239</v>
+        <v>842</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C670" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.35">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
-        <v>250</v>
+        <v>843</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C671" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.35">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
-        <v>254</v>
+        <v>844</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C672" s="2" t="s">
-        <v>267</v>
+        <v>845</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
-        <v>583</v>
+        <v>687</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>584</v>
+        <v>677</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>1011</v>
+        <v>685</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>1014</v>
+        <v>678</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
-        <v>585</v>
+        <v>686</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>586</v>
+        <v>679</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
-        <v>819</v>
+        <v>996</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>825</v>
+        <v>998</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
-        <v>820</v>
+        <v>997</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>826</v>
+        <v>999</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
-        <v>347</v>
+        <v>376</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C678" s="2" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
-        <v>1005</v>
+        <v>381</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>1012</v>
+        <v>379</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
-        <v>823</v>
+        <v>382</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>828</v>
+        <v>380</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
-        <v>313</v>
+        <v>1069</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>319</v>
+        <v>1070</v>
+      </c>
+      <c r="C681" s="2" t="s">
+        <v>1071</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="C682" s="2" t="s">
-        <v>309</v>
+        <v>226</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
-        <v>1006</v>
+        <v>313</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>1013</v>
+        <v>315</v>
+      </c>
+      <c r="C683" s="2" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="C684" s="2" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
-        <v>249</v>
+        <v>453</v>
       </c>
       <c r="B685" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C685" s="2" t="s">
-        <v>268</v>
+        <v>461</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
-        <v>253</v>
+        <v>1074</v>
       </c>
       <c r="B686" s="1" t="s">
-        <v>259</v>
+        <v>1066</v>
       </c>
       <c r="C686" s="2" t="s">
-        <v>269</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>246</v>
+        <v>598</v>
       </c>
       <c r="C687" s="2" t="s">
-        <v>246</v>
+        <v>599</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
-        <v>1068</v>
+        <v>274</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>1071</v>
+        <v>279</v>
       </c>
       <c r="C688" s="2" t="s">
-        <v>1075</v>
+        <v>276</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C689" s="2" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="C690" s="2" t="s">
-        <v>271</v>
+        <v>231</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
+        <v>246</v>
+      </c>
+      <c r="B691" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C691" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A692" t="s">
+        <v>250</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C692" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A693" t="s">
+        <v>232</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C693" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A694" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B694" s="1" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A695" t="s">
+        <v>295</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C695" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A696" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B696" s="1" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A697" t="s">
+        <v>818</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="698" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A698" t="s">
+        <v>272</v>
+      </c>
+      <c r="B698" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C698" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="699" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A699" t="s">
+        <v>273</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C699" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A700" t="s">
+        <v>311</v>
+      </c>
+      <c r="B700" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C700" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="701" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A701" t="s">
+        <v>234</v>
+      </c>
+      <c r="B701" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C701" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="702" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A702" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B702" s="1" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="703" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A703" t="s">
         <v>312</v>
       </c>
-      <c r="B691" s="1" t="s">
+      <c r="B703" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C703" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="C691" s="2" t="s">
-        <v>330</v>
+    </row>
+    <row r="704" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A704" t="s">
+        <v>308</v>
+      </c>
+      <c r="B704" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C704" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="705" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A705" t="s">
+        <v>236</v>
+      </c>
+      <c r="B705" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C705" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="706" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A706" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B706" s="1" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="707" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A707" t="s">
+        <v>819</v>
+      </c>
+      <c r="B707" s="1" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="708" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A708" t="s">
+        <v>238</v>
+      </c>
+      <c r="B708" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C708" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="709" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A709" t="s">
+        <v>249</v>
+      </c>
+      <c r="B709" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C709" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="710" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A710" t="s">
+        <v>253</v>
+      </c>
+      <c r="B710" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C710" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="711" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A711" t="s">
+        <v>580</v>
+      </c>
+      <c r="B711" s="1" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="712" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A712" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B712" s="1" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="713" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A713" t="s">
+        <v>582</v>
+      </c>
+      <c r="B713" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="714" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A714" t="s">
+        <v>816</v>
+      </c>
+      <c r="B714" s="1" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="715" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A715" t="s">
+        <v>817</v>
+      </c>
+      <c r="B715" s="1" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="716" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A716" t="s">
+        <v>344</v>
+      </c>
+      <c r="B716" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C716" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="717" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A717" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B717" s="1" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="718" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A718" t="s">
+        <v>820</v>
+      </c>
+      <c r="B718" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="719" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A719" t="s">
+        <v>310</v>
+      </c>
+      <c r="B719" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="720" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A720" t="s">
+        <v>240</v>
+      </c>
+      <c r="B720" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C720" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="721" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A721" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B721" s="1" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="722" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A722" t="s">
+        <v>242</v>
+      </c>
+      <c r="B722" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C722" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="723" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A723" t="s">
+        <v>248</v>
+      </c>
+      <c r="B723" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C723" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="724" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A724" t="s">
+        <v>252</v>
+      </c>
+      <c r="B724" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C724" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="725" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A725" t="s">
+        <v>244</v>
+      </c>
+      <c r="B725" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C725" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="726" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A726" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B726" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C726" s="2" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="727" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A727" t="s">
+        <v>247</v>
+      </c>
+      <c r="B727" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C727" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="728" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A728" t="s">
+        <v>251</v>
+      </c>
+      <c r="B728" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C728" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="729" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A729" t="s">
+        <v>309</v>
+      </c>
+      <c r="B729" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C729" s="2" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K691">
-    <sortState ref="A2:K691">
-      <sortCondition ref="A1:A691"/>
+  <autoFilter ref="A1:K721">
+    <sortState ref="A2:K729">
+      <sortCondition ref="A1:A721"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10524,7 +11059,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.7265625" customWidth="1"/>
@@ -10534,77 +11069,93 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>338</v>
+        <v>1379</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>339</v>
+        <v>1388</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>343</v>
+        <v>1380</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>350</v>
+        <v>1387</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>1039</v>
+        <v>1381</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1042</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>1038</v>
+        <v>1382</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1043</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>1041</v>
+        <v>1383</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1044</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>1040</v>
+        <v>1384</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1045</v>
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1393</v>
       </c>
     </row>
   </sheetData>

--- a/gui/rebalance_localizations.xlsx
+++ b/gui/rebalance_localizations.xlsx
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">rebalance_localizations!$A$1:$K$921</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">rebalance_localizations!$A$1:$K$930</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1925" uniqueCount="1741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1959" uniqueCount="1758">
   <si>
     <t>ENGLISH</t>
   </si>
@@ -5246,6 +5246,57 @@
   </si>
   <si>
     <t>Optimized Morphing Flux Capacitor</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/mini_miner_lvl_1</t>
+  </si>
+  <si>
+    <t>gui/hud/building_description/irradiator</t>
+  </si>
+  <si>
+    <t>gui/hud/building_name/irradiator</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/irradiator_lvl_1</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/irradiator_lvl_3</t>
+  </si>
+  <si>
+    <t>gui/menu/research/name/irradiator_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/irradiator_lvl_2</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/irradiator_lvl_3</t>
+  </si>
+  <si>
+    <t>Irradiator</t>
+  </si>
+  <si>
+    <t>Material Irradiation</t>
+  </si>
+  <si>
+    <t>Advanced Material Irradiation</t>
+  </si>
+  <si>
+    <t>Optimized Material Irradiation</t>
+  </si>
+  <si>
+    <t>gui/menu/research/description/irradiator_lvl_1</t>
+  </si>
+  <si>
+    <t>The process of irradiating materials with high energy eleoctromagnetic radiation to produce various instable isotops of chemical elements and process it into a indurialized fissium flux for wider application</t>
+  </si>
+  <si>
+    <t>Irradiates materials with high energy EM-radiation to produce radioactive isotopes then bundled into fissium flux</t>
+  </si>
+  <si>
+    <t>resource_name/fissonium_compressed</t>
+  </si>
+  <si>
+    <t>Packaged Fissonium Flux</t>
   </si>
 </sst>
 </file>
@@ -6089,7 +6140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K921"/>
+  <dimension ref="A1:K930"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="65.453125" customWidth="1"/>
@@ -6743,122 +6794,122 @@
     </row>
     <row r="78" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>1560</v>
+        <v>1742</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>622</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>1088</v>
+        <v>1562</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>1082</v>
+        <v>621</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>315</v>
+        <v>1089</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>312</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>1422</v>
+        <v>315</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>1428</v>
+        <v>310</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>270</v>
+        <v>1425</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>1436</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>1548</v>
+        <v>280</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>1544</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>1721</v>
+        <v>1548</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>1723</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>46</v>
+        <v>1721</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>47</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>47</v>
@@ -6866,7 +6917,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>47</v>
@@ -6874,15 +6925,15 @@
     </row>
     <row r="94" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>51</v>
@@ -6890,7 +6941,7 @@
     </row>
     <row r="96" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>51</v>
@@ -6898,114 +6949,114 @@
     </row>
     <row r="97" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>1223</v>
+        <v>53</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>1225</v>
+        <v>51</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>1238</v>
+        <v>1223</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>1433</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>549</v>
+        <v>1240</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>550</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>1344</v>
+        <v>551</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>1347</v>
+        <v>552</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>1490</v>
+        <v>1344</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>1493</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>585</v>
+        <v>1490</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>591</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>321</v>
+        <v>594</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>331</v>
+        <v>596</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>332</v>
+        <v>322</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>332</v>
@@ -7013,7 +7064,7 @@
     </row>
     <row r="111" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>332</v>
@@ -7021,87 +7072,87 @@
     </row>
     <row r="112" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>1293</v>
+        <v>325</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>1296</v>
+        <v>332</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>1513</v>
+        <v>1293</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>1511</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>1701</v>
+        <v>1513</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>1713</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>952</v>
+        <v>1701</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>969</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>1633</v>
+        <v>957</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>1638</v>
+        <v>968</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>843</v>
+        <v>1634</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>846</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>847</v>
@@ -7109,58 +7160,58 @@
     </row>
     <row r="123" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>615</v>
+        <v>845</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>622</v>
+        <v>847</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>771</v>
+        <v>612</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>772</v>
+        <v>621</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>286</v>
+        <v>771</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>293</v>
+        <v>772</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>54</v>
+        <v>286</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>55</v>
+        <v>289</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="129" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>55</v>
@@ -7168,7 +7219,7 @@
     </row>
     <row r="130" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>55</v>
@@ -7176,431 +7227,431 @@
     </row>
     <row r="131" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>1091</v>
+        <v>57</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>1096</v>
+        <v>55</v>
       </c>
     </row>
     <row r="132" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="133" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="134" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>58</v>
+        <v>1094</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>1290</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="135" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>1236</v>
+        <v>58</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="136" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="137" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>640</v>
+        <v>1237</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>582</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="138" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>641</v>
+        <v>582</v>
       </c>
     </row>
     <row r="139" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="140" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>59</v>
+        <v>638</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>60</v>
+        <v>642</v>
       </c>
     </row>
     <row r="141" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="142" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>1326</v>
+        <v>61</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>1331</v>
+        <v>62</v>
       </c>
     </row>
     <row r="143" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>419</v>
+        <v>1326</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>449</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="144" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="145" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="146" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="147" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>63</v>
+        <v>428</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>64</v>
+        <v>457</v>
       </c>
     </row>
     <row r="148" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>392</v>
+        <v>63</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>469</v>
+        <v>64</v>
       </c>
     </row>
     <row r="149" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="150" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="151" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="152" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>490</v>
+        <v>397</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>491</v>
+        <v>468</v>
       </c>
     </row>
     <row r="153" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>1614</v>
+        <v>490</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>1619</v>
+        <v>491</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>1595</v>
+        <v>1614</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>1582</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="155" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="156" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>1594</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="157" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>1579</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="159" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>1615</v>
+        <v>1599</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>1620</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>1697</v>
+        <v>1615</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>1693</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="161" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>1649</v>
+        <v>1697</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>1675</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>1350</v>
+        <v>1651</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>1359</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>425</v>
+        <v>1350</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>454</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="166" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>1367</v>
+        <v>426</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>1366</v>
+        <v>455</v>
       </c>
     </row>
     <row r="167" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>421</v>
+        <v>1367</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>452</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="168" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="169" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>538</v>
+        <v>453</v>
       </c>
     </row>
     <row r="170" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>451</v>
+        <v>538</v>
       </c>
     </row>
     <row r="171" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
     </row>
     <row r="172" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="173" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="174" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="175" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="177" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="178" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="179" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>481</v>
+        <v>430</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>485</v>
+        <v>459</v>
       </c>
     </row>
     <row r="180" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>539</v>
+        <v>485</v>
       </c>
     </row>
     <row r="181" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>486</v>
+        <v>539</v>
       </c>
     </row>
     <row r="182" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>1108</v>
+        <v>480</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>1116</v>
+        <v>486</v>
       </c>
     </row>
     <row r="183" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="184" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>1111</v>
@@ -7608,71 +7659,71 @@
     </row>
     <row r="185" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>1098</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="186" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>1117</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="187" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="188" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>1100</v>
+        <v>1105</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>1099</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="189" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>1106</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="190" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="191" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>1112</v>
+        <v>1102</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>1115</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="192" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="193" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>1119</v>
@@ -7680,461 +7731,458 @@
     </row>
     <row r="194" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>65</v>
+        <v>1114</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>66</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="195" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>1259</v>
+        <v>65</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>1273</v>
+        <v>66</v>
       </c>
     </row>
     <row r="196" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="197" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="198" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="199" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>67</v>
+        <v>1261</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>1405</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="200" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="201" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="202" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="203" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>383</v>
+        <v>70</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>387</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="204" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>71</v>
+        <v>383</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>1409</v>
+        <v>387</v>
       </c>
     </row>
     <row r="205" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>1417</v>
+        <v>71</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>72</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="206" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>1481</v>
+        <v>1417</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>1487</v>
+        <v>72</v>
       </c>
     </row>
     <row r="207" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="208" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="209" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>73</v>
+        <v>1484</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>1410</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="210" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>1419</v>
+        <v>73</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>1420</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="211" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>74</v>
+        <v>1419</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>1411</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="212" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>522</v>
+        <v>74</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="213" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>75</v>
+        <v>522</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="214" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="215" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>1416</v>
+        <v>76</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>77</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="216" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>1483</v>
+        <v>1416</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>1486</v>
+        <v>77</v>
       </c>
     </row>
     <row r="217" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="218" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="219" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>78</v>
+        <v>1485</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>1415</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="220" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>1418</v>
+        <v>78</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>1421</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="221" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>384</v>
+        <v>1418</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>388</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="222" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>79</v>
+        <v>384</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>80</v>
+        <v>388</v>
       </c>
     </row>
     <row r="223" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="224" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="225" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="226" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="227" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="228" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>1008</v>
+        <v>89</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>1009</v>
+        <v>90</v>
       </c>
     </row>
     <row r="229" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>91</v>
+        <v>1008</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>92</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="230" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="231" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="232" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="233" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>437</v>
+        <v>97</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>445</v>
+        <v>98</v>
       </c>
     </row>
     <row r="234" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>1074</v>
+        <v>437</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>1056</v>
+        <v>445</v>
       </c>
     </row>
     <row r="235" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>572</v>
+        <v>1074</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>573</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="236" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>438</v>
+        <v>572</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>446</v>
+        <v>573</v>
       </c>
     </row>
     <row r="237" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>99</v>
+        <v>438</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>100</v>
+        <v>446</v>
       </c>
     </row>
     <row r="238" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>1039</v>
+        <v>99</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>1040</v>
+        <v>100</v>
       </c>
     </row>
     <row r="239" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>1242</v>
+        <v>1039</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>1241</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="240" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>1032</v>
+        <v>1242</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>1034</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>859</v>
+        <v>1032</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>862</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>876</v>
+        <v>858</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>1043</v>
+        <v>860</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>1044</v>
+        <v>863</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>317</v>
+        <v>1043</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>319</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>400</v>
+        <v>317</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>442</v>
+        <v>319</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>971</v>
+        <v>400</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>974</v>
+        <v>442</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>285</v>
+        <v>971</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>290</v>
+        <v>974</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>290</v>
@@ -8142,7 +8190,7 @@
     </row>
     <row r="251" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>1077</v>
@@ -8153,173 +8201,176 @@
     </row>
     <row r="252" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>583</v>
+        <v>288</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>586</v>
+        <v>1077</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>1316</v>
+        <v>583</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>1329</v>
+        <v>586</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>101</v>
+        <v>1316</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>102</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>1666</v>
+        <v>101</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>1687</v>
+        <v>102</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>1554</v>
+        <v>1666</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>1557</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>1555</v>
+        <v>1743</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>1558</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>1086</v>
+        <v>1555</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>1084</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>1087</v>
+        <v>1556</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>1083</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>316</v>
+        <v>1086</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>311</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>1423</v>
+        <v>1087</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>1426</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>1424</v>
+        <v>316</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>1427</v>
+        <v>309</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>271</v>
+        <v>1423</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>278</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>272</v>
+        <v>1424</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>842</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>842</v>
+        <v>278</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>1549</v>
+        <v>272</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>1542</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>1546</v>
+        <v>842</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>1722</v>
+        <v>273</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>1738</v>
+        <v>842</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>103</v>
+        <v>1549</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>104</v>
+        <v>1542</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>1546</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>105</v>
+        <v>1722</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>106</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>106</v>
@@ -8327,77 +8378,71 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>1222</v>
+        <v>107</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>1224</v>
+        <v>106</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>1287</v>
+        <v>108</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>1430</v>
+        <v>106</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>1288</v>
+        <v>1222</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>1431</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>553</v>
+        <v>1288</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>554</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>1345</v>
+        <v>1289</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>1346</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>326</v>
+        <v>553</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C279" s="2" t="s">
-        <v>337</v>
+        <v>554</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>327</v>
+        <v>1345</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C280" s="2" t="s">
-        <v>337</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B281" s="1" t="s">
         <v>333</v>
@@ -8408,98 +8453,104 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1294</v>
+        <v>328</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>1295</v>
+        <v>333</v>
+      </c>
+      <c r="C283" s="2" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>1514</v>
+        <v>329</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>1515</v>
+        <v>334</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>1702</v>
+        <v>1294</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>1712</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>953</v>
+        <v>1514</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>964</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>954</v>
+        <v>1702</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>965</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>1631</v>
+        <v>954</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>1637</v>
+        <v>965</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>1632</v>
+        <v>955</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>1642</v>
+        <v>966</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>838</v>
+        <v>1631</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>839</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>840</v>
+        <v>1632</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>839</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>839</v>
@@ -8507,951 +8558,951 @@
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>613</v>
+        <v>840</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>617</v>
+        <v>839</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>614</v>
+        <v>841</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>619</v>
+        <v>839</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>773</v>
+        <v>614</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>774</v>
+        <v>619</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>109</v>
+        <v>611</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>110</v>
+        <v>618</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>1090</v>
+        <v>773</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>1092</v>
+        <v>774</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>275</v>
+        <v>1090</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>276</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>274</v>
+        <v>111</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>277</v>
+        <v>112</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>626</v>
+        <v>275</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>625</v>
+        <v>276</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>623</v>
+        <v>274</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>627</v>
+        <v>277</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>1327</v>
+        <v>623</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>1330</v>
+        <v>627</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>401</v>
+        <v>624</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>529</v>
+        <v>628</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>402</v>
+        <v>1327</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>528</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>113</v>
+        <v>409</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>114</v>
+        <v>527</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>540</v>
+        <v>526</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>394</v>
+        <v>113</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>523</v>
+        <v>114</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>765</v>
+        <v>396</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>763</v>
+        <v>524</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>766</v>
+        <v>398</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>764</v>
+        <v>525</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>487</v>
+        <v>765</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>488</v>
+        <v>763</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>1613</v>
+        <v>766</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>1617</v>
+        <v>764</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>1600</v>
+        <v>487</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>1566</v>
+        <v>488</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>1601</v>
+        <v>1613</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>1565</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>1593</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>1564</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>1616</v>
+        <v>1603</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>1618</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>1696</v>
+        <v>1604</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>1692</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>1650</v>
+        <v>1616</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>1673</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>1652</v>
+        <v>1696</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>1674</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>1351</v>
+        <v>1650</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>1358</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>407</v>
+        <v>1652</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>541</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>408</v>
+        <v>1351</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>542</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>1368</v>
+        <v>407</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>1365</v>
+        <v>541</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>405</v>
+        <v>1368</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>544</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>443</v>
+        <v>545</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>530</v>
+        <v>546</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>531</v>
+        <v>443</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>444</v>
+        <v>531</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>533</v>
+        <v>444</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>477</v>
+        <v>411</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>479</v>
+        <v>412</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>489</v>
+        <v>534</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>115</v>
+        <v>479</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>116</v>
+        <v>489</v>
       </c>
     </row>
     <row r="349" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>1439</v>
+        <v>478</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>1440</v>
+        <v>535</v>
       </c>
     </row>
     <row r="350" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>1441</v>
+        <v>115</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>1442</v>
+        <v>116</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>1446</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>1026</v>
+        <v>1451</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>1025</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>483</v>
+        <v>1453</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>484</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>472</v>
+        <v>1026</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>473</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>1024</v>
+        <v>483</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>1025</v>
+        <v>484</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>902</v>
+        <v>472</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>835</v>
+        <v>473</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>903</v>
+        <v>1024</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>837</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>833</v>
+        <v>904</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>1120</v>
+        <v>905</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>1121</v>
+        <v>834</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>950</v>
+        <v>833</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>951</v>
+        <v>832</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>789</v>
+        <v>1120</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>793</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>790</v>
+        <v>950</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>794</v>
+        <v>951</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>1272</v>
+        <v>789</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>1281</v>
+        <v>793</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>1270</v>
+        <v>790</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>1280</v>
+        <v>794</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>506</v>
+        <v>1270</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>1148</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>1167</v>
+        <v>1271</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>1149</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>653</v>
+        <v>1167</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>1157</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>1592</v>
+        <v>507</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>1536</v>
+        <v>653</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>1537</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>508</v>
+        <v>1592</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>1152</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>1168</v>
+        <v>1536</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>1151</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>1159</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>654</v>
+        <v>1168</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>1158</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>1591</v>
+        <v>509</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>510</v>
+        <v>654</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>1153</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>1169</v>
+        <v>1591</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>1150</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>1160</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>655</v>
+        <v>1169</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>1161</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>1583</v>
+        <v>511</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>512</v>
+        <v>655</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>1170</v>
+        <v>1583</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>1149</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>1162</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>656</v>
+        <v>1170</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>1163</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>1584</v>
+        <v>513</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>514</v>
+        <v>656</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>1171</v>
+        <v>1584</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>1164</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>657</v>
+        <v>1171</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>1585</v>
+        <v>515</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>1534</v>
+        <v>657</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>1535</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>1019</v>
+        <v>1585</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>1022</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>1018</v>
+        <v>1534</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>1023</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>1003</v>
+        <v>1019</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>1013</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>1004</v>
+        <v>1018</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>1012</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>117</v>
+        <v>1003</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>118</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>1181</v>
+        <v>1004</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>1189</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>1197</v>
+        <v>117</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>1189</v>
+        <v>118</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>119</v>
+        <v>1181</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>120</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>1183</v>
+        <v>1197</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>1199</v>
+        <v>119</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>1191</v>
+        <v>120</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>121</v>
+        <v>1183</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>122</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>123</v>
+        <v>1199</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>122</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B412" s="1" t="s">
         <v>122</v>
@@ -9459,183 +9510,183 @@
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>599</v>
+        <v>123</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>606</v>
+        <v>122</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>603</v>
+        <v>124</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>607</v>
+        <v>122</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>125</v>
+        <v>603</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>126</v>
+        <v>607</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>1182</v>
+        <v>604</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>1192</v>
+        <v>608</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>1198</v>
+        <v>125</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>1192</v>
+        <v>126</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>127</v>
+        <v>1182</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>128</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>1184</v>
+        <v>1198</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>1200</v>
+        <v>127</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>1190</v>
+        <v>128</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>677</v>
+        <v>1184</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>680</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>678</v>
+        <v>1200</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>688</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>474</v>
+        <v>678</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>475</v>
+        <v>688</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>1073</v>
+        <v>679</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>1526</v>
+        <v>689</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>1519</v>
+        <v>474</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>1525</v>
+        <v>475</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>570</v>
+        <v>1073</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>581</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>571</v>
+        <v>1519</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>1523</v>
+        <v>570</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>1524</v>
+        <v>581</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>1029</v>
+        <v>571</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>1033</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>1030</v>
+        <v>1523</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>1037</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>949</v>
+        <v>1029</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>945</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>936</v>
+        <v>1030</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>945</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>937</v>
+        <v>949</v>
       </c>
       <c r="B435" s="1" t="s">
         <v>945</v>
@@ -9643,7 +9694,7 @@
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B436" s="1" t="s">
         <v>945</v>
@@ -9651,23 +9702,23 @@
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>946</v>
@@ -9675,7 +9726,7 @@
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B440" s="1" t="s">
         <v>946</v>
@@ -9683,183 +9734,183 @@
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>576</v>
+        <v>929</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>635</v>
+        <v>946</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>633</v>
+        <v>932</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>636</v>
+        <v>946</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>634</v>
+        <v>576</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>1309</v>
+        <v>633</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>1311</v>
+        <v>636</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>869</v>
+        <v>634</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>1122</v>
+        <v>637</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>891</v>
+        <v>1309</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>1126</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>895</v>
+        <v>869</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>868</v>
+        <v>891</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>896</v>
+        <v>868</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>874</v>
+        <v>892</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>897</v>
+        <v>874</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>870</v>
+        <v>893</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>898</v>
+        <v>870</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>1213</v>
+        <v>894</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>1219</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>1214</v>
+        <v>898</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>1220</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>1455</v>
+        <v>1214</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>1461</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>1463</v>
+        <v>1215</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>1468</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>1469</v>
+        <v>1463</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>1468</v>
@@ -9867,3777 +9918,3849 @@
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>791</v>
+        <v>1458</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>792</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>972</v>
+        <v>1469</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>973</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>1068</v>
+        <v>791</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>1071</v>
+        <v>792</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>1069</v>
+        <v>972</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>1072</v>
+        <v>973</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>1517</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>783</v>
+        <v>1069</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>780</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>782</v>
+        <v>1069</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>781</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>684</v>
+        <v>783</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>687</v>
+        <v>780</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>129</v>
+        <v>782</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>130</v>
+        <v>781</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>1317</v>
+        <v>684</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>1323</v>
+        <v>687</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>1318</v>
+        <v>129</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>1324</v>
+        <v>130</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>1663</v>
+        <v>1318</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>1685</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>1664</v>
+        <v>1319</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>1686</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>1689</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>1690</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>131</v>
+        <v>1667</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>132</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>133</v>
+        <v>1668</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>134</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>145</v>
+        <v>1753</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>146</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>147</v>
+        <v>1747</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>148</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>149</v>
+        <v>1748</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>150</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>723</v>
+        <v>155</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>717</v>
+        <v>156</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>724</v>
+        <v>157</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>718</v>
+        <v>158</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>725</v>
+        <v>159</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>719</v>
+        <v>160</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>726</v>
+        <v>161</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>705</v>
+        <v>162</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>727</v>
+        <v>163</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>706</v>
+        <v>164</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>707</v>
+        <v>717</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>722</v>
+        <v>708</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>1248</v>
+        <v>733</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>1247</v>
+        <v>721</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>1249</v>
+        <v>734</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>1253</v>
+        <v>722</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>1252</v>
+        <v>735</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>1256</v>
+        <v>714</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>1495</v>
+        <v>736</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>1497</v>
+        <v>715</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>1500</v>
+        <v>737</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>1506</v>
+        <v>716</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>1501</v>
+        <v>1248</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>1507</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>1502</v>
+        <v>1249</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>1508</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>1550</v>
+        <v>1252</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>1544</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>1551</v>
+        <v>1495</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>1545</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>1717</v>
+        <v>1500</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>1720</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>1718</v>
+        <v>1501</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>1725</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>1719</v>
+        <v>1502</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>1724</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>1059</v>
+        <v>1550</v>
       </c>
       <c r="B527" s="1" t="s">
-        <v>1531</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>1060</v>
+        <v>1551</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>1532</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>1528</v>
+        <v>1717</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>1533</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>340</v>
+        <v>1718</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>547</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>345</v>
+        <v>1719</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>349</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>346</v>
+        <v>1059</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>348</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>1229</v>
+        <v>1060</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>1235</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>1230</v>
+        <v>1528</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>1235</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>1231</v>
+        <v>340</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>1235</v>
+        <v>547</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>933</v>
+        <v>345</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>944</v>
+        <v>349</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>934</v>
+        <v>346</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>944</v>
+        <v>348</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>935</v>
+        <v>1229</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>944</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>942</v>
+        <v>1230</v>
       </c>
       <c r="B539" s="1" t="s">
-        <v>944</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>943</v>
+        <v>1231</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>944</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>555</v>
+        <v>933</v>
       </c>
       <c r="B541" s="1" t="s">
-        <v>556</v>
+        <v>944</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>557</v>
+        <v>934</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>556</v>
+        <v>944</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>1335</v>
+        <v>935</v>
       </c>
       <c r="B543" s="1" t="s">
-        <v>1341</v>
+        <v>944</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>1336</v>
+        <v>942</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>1342</v>
+        <v>944</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>1337</v>
+        <v>943</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>1343</v>
+        <v>944</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>372</v>
+        <v>555</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>380</v>
+        <v>556</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>374</v>
+        <v>557</v>
       </c>
       <c r="B547" s="1" t="s">
-        <v>381</v>
+        <v>556</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>376</v>
+        <v>1335</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>382</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>683</v>
+        <v>1336</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>686</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>350</v>
+        <v>1337</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>353</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="B551" s="1" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>1307</v>
+        <v>376</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>1303</v>
+        <v>382</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>1305</v>
+        <v>683</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>1304</v>
+        <v>686</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>1306</v>
+        <v>350</v>
       </c>
       <c r="B555" s="1" t="s">
-        <v>1304</v>
+        <v>353</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>1510</v>
+        <v>357</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>1512</v>
+        <v>354</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>1706</v>
+        <v>359</v>
       </c>
       <c r="B557" s="1" t="s">
-        <v>1709</v>
+        <v>354</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>1707</v>
+        <v>1307</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>1710</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>1708</v>
+        <v>1305</v>
       </c>
       <c r="B559" s="1" t="s">
-        <v>1711</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>958</v>
+        <v>1306</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>1000</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>959</v>
+        <v>1510</v>
       </c>
       <c r="B561" s="1" t="s">
-        <v>1001</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>960</v>
+        <v>1706</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>1002</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>1629</v>
+        <v>1707</v>
       </c>
       <c r="B563" s="1" t="s">
-        <v>1640</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>1630</v>
+        <v>1708</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>1641</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>850</v>
+        <v>958</v>
       </c>
       <c r="B565" s="1" t="s">
-        <v>857</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>849</v>
+        <v>959</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>846</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>848</v>
+        <v>960</v>
       </c>
       <c r="B567" s="1" t="s">
-        <v>857</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>775</v>
+        <v>1629</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>777</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>165</v>
+        <v>1630</v>
       </c>
       <c r="B569" s="1" t="s">
-        <v>166</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>167</v>
+        <v>850</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>168</v>
+        <v>857</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>697</v>
+        <v>849</v>
       </c>
       <c r="B571" s="1" t="s">
-        <v>662</v>
+        <v>846</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>698</v>
+        <v>848</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>694</v>
+        <v>857</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="B573" s="1" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>768</v>
+        <v>165</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>770</v>
+        <v>166</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>699</v>
+        <v>167</v>
       </c>
       <c r="B575" s="1" t="s">
-        <v>696</v>
+        <v>168</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>695</v>
+        <v>662</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>1659</v>
+        <v>698</v>
       </c>
       <c r="B577" s="1" t="s">
-        <v>1682</v>
+        <v>694</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>1660</v>
+        <v>767</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>1682</v>
+        <v>769</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>1657</v>
+        <v>768</v>
       </c>
       <c r="B579" s="1" t="s">
-        <v>1681</v>
+        <v>770</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>1658</v>
+        <v>699</v>
       </c>
       <c r="B580" s="1" t="s">
-        <v>1681</v>
+        <v>696</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>1355</v>
+        <v>700</v>
       </c>
       <c r="B581" s="1" t="s">
-        <v>1363</v>
+        <v>695</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>1356</v>
+        <v>1659</v>
       </c>
       <c r="B582" s="1" t="s">
-        <v>1364</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>1357</v>
+        <v>1660</v>
       </c>
       <c r="B583" s="1" t="s">
-        <v>1364</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>691</v>
+        <v>1657</v>
       </c>
       <c r="B584" s="1" t="s">
-        <v>690</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>907</v>
+        <v>1658</v>
       </c>
       <c r="B585" s="1" t="s">
-        <v>663</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>807</v>
+        <v>1355</v>
       </c>
       <c r="B586" s="1" t="s">
-        <v>809</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>808</v>
+        <v>1356</v>
       </c>
       <c r="B587" s="1" t="s">
-        <v>809</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>1610</v>
+        <v>1357</v>
       </c>
       <c r="B588" s="1" t="s">
-        <v>1624</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>1609</v>
+        <v>691</v>
       </c>
       <c r="B589" s="1" t="s">
-        <v>1625</v>
+        <v>690</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>1574</v>
+        <v>907</v>
       </c>
       <c r="B590" s="1" t="s">
-        <v>1575</v>
+        <v>663</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>1573</v>
+        <v>807</v>
       </c>
       <c r="B591" s="1" t="s">
-        <v>1576</v>
+        <v>809</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>1571</v>
+        <v>808</v>
       </c>
       <c r="B592" s="1" t="s">
-        <v>1577</v>
+        <v>809</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>1572</v>
+        <v>1610</v>
       </c>
       <c r="B593" s="1" t="s">
-        <v>1578</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="B594" s="1" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>1611</v>
+        <v>1574</v>
       </c>
       <c r="B595" s="1" t="s">
-        <v>1626</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>1372</v>
+        <v>1573</v>
       </c>
       <c r="B596" s="1" t="s">
-        <v>1370</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>493</v>
+        <v>1571</v>
       </c>
       <c r="B597" s="1" t="s">
-        <v>495</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>820</v>
+        <v>1572</v>
       </c>
       <c r="B598" s="1" t="s">
-        <v>829</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>821</v>
+        <v>1612</v>
       </c>
       <c r="B599" s="1" t="s">
-        <v>830</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>822</v>
+        <v>1611</v>
       </c>
       <c r="B600" s="1" t="s">
-        <v>831</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>669</v>
+        <v>1372</v>
       </c>
       <c r="B601" s="1" t="s">
-        <v>661</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>1381</v>
+        <v>493</v>
       </c>
       <c r="B602" s="1" t="s">
-        <v>1386</v>
+        <v>495</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>1382</v>
+        <v>820</v>
       </c>
       <c r="B603" s="1" t="s">
-        <v>1387</v>
+        <v>829</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>1383</v>
+        <v>821</v>
       </c>
       <c r="B604" s="1" t="s">
-        <v>1385</v>
+        <v>830</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>1384</v>
+        <v>822</v>
       </c>
       <c r="B605" s="1" t="s">
-        <v>1388</v>
+        <v>831</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>975</v>
+        <v>669</v>
       </c>
       <c r="B606" s="1" t="s">
-        <v>982</v>
+        <v>661</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>976</v>
+        <v>1381</v>
       </c>
       <c r="B607" s="1" t="s">
-        <v>981</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>361</v>
+        <v>1382</v>
       </c>
       <c r="B608" s="1" t="s">
-        <v>364</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>741</v>
+        <v>1383</v>
       </c>
       <c r="B609" s="1" t="s">
-        <v>548</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>369</v>
+        <v>1384</v>
       </c>
       <c r="B610" s="1" t="s">
-        <v>370</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>795</v>
+        <v>975</v>
       </c>
       <c r="B611" s="1" t="s">
-        <v>796</v>
+        <v>982</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>784</v>
+        <v>976</v>
       </c>
       <c r="B612" s="1" t="s">
-        <v>787</v>
+        <v>981</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>785</v>
+        <v>361</v>
       </c>
       <c r="B613" s="1" t="s">
-        <v>788</v>
+        <v>364</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>1269</v>
+        <v>741</v>
       </c>
       <c r="B614" s="1" t="s">
-        <v>1279</v>
+        <v>548</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>1267</v>
+        <v>369</v>
       </c>
       <c r="B615" s="1" t="s">
-        <v>1277</v>
+        <v>370</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>1268</v>
+        <v>795</v>
       </c>
       <c r="B616" s="1" t="s">
-        <v>1278</v>
+        <v>796</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>496</v>
+        <v>784</v>
       </c>
       <c r="B617" s="1" t="s">
-        <v>516</v>
+        <v>787</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>1172</v>
+        <v>785</v>
       </c>
       <c r="B618" s="1" t="s">
-        <v>1138</v>
+        <v>788</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>497</v>
+        <v>1269</v>
       </c>
       <c r="B619" s="1" t="s">
-        <v>648</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>647</v>
+        <v>1267</v>
       </c>
       <c r="B620" s="1" t="s">
-        <v>1141</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>1586</v>
+        <v>1268</v>
       </c>
       <c r="B621" s="1" t="s">
-        <v>1141</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>1737</v>
+        <v>496</v>
       </c>
       <c r="B622" s="1" t="s">
-        <v>1736</v>
+        <v>516</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>1538</v>
+        <v>1172</v>
       </c>
       <c r="B623" s="1" t="s">
-        <v>1541</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B624" s="1" t="s">
-        <v>519</v>
+        <v>648</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>1173</v>
+        <v>647</v>
       </c>
       <c r="B625" s="1" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>499</v>
+        <v>1586</v>
       </c>
       <c r="B626" s="1" t="s">
-        <v>649</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>646</v>
+        <v>1737</v>
       </c>
       <c r="B627" s="1" t="s">
-        <v>1145</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>1587</v>
+        <v>1538</v>
       </c>
       <c r="B628" s="1" t="s">
-        <v>1145</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B629" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B630" s="1" t="s">
-        <v>1139</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B631" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B632" s="1" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B633" s="1" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B634" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B635" s="1" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B636" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B637" s="1" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B638" s="1" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B639" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B640" s="1" t="s">
-        <v>1140</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B641" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B642" s="1" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="B643" s="1" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>1539</v>
+        <v>504</v>
       </c>
       <c r="B644" s="1" t="s">
-        <v>1540</v>
+        <v>518</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>1017</v>
+        <v>1176</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>1020</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>1016</v>
+        <v>505</v>
       </c>
       <c r="B646" s="1" t="s">
-        <v>1021</v>
+        <v>652</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>1005</v>
+        <v>643</v>
       </c>
       <c r="B647" s="1" t="s">
-        <v>1014</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>1006</v>
+        <v>1590</v>
       </c>
       <c r="B648" s="1" t="s">
-        <v>1015</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>169</v>
+        <v>1539</v>
       </c>
       <c r="B649" s="1" t="s">
-        <v>170</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>1177</v>
+        <v>1017</v>
       </c>
       <c r="B650" s="1" t="s">
-        <v>1185</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>1193</v>
+        <v>1016</v>
       </c>
       <c r="B651" s="1" t="s">
-        <v>1201</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>171</v>
+        <v>1005</v>
       </c>
       <c r="B652" s="1" t="s">
-        <v>172</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>1179</v>
+        <v>1006</v>
       </c>
       <c r="B653" s="1" t="s">
-        <v>1187</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>1195</v>
+        <v>169</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>1203</v>
+        <v>170</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
-        <v>173</v>
+        <v>1177</v>
       </c>
       <c r="B655" s="1" t="s">
-        <v>174</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
-        <v>175</v>
+        <v>1193</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>176</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
-        <v>600</v>
+        <v>1179</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>605</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>601</v>
+        <v>1195</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>609</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>602</v>
+        <v>173</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>610</v>
+        <v>174</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
-        <v>1178</v>
+        <v>177</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>1186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
-        <v>1194</v>
+        <v>600</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>1202</v>
+        <v>605</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
-        <v>181</v>
+        <v>601</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>182</v>
+        <v>609</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
-        <v>1180</v>
+        <v>602</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1188</v>
+        <v>610</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
-        <v>1196</v>
+        <v>179</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1204</v>
+        <v>180</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
-        <v>671</v>
+        <v>1178</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>674</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
-        <v>672</v>
+        <v>1194</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>675</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
-        <v>673</v>
+        <v>181</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>676</v>
+        <v>182</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
-        <v>1080</v>
+        <v>1180</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>476</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
-        <v>1081</v>
+        <v>1196</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1064</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
-        <v>1520</v>
+        <v>671</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1522</v>
+        <v>674</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
-        <v>566</v>
+        <v>672</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>568</v>
+        <v>675</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>567</v>
+        <v>673</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>569</v>
+        <v>676</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
-        <v>1518</v>
+        <v>1080</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>1521</v>
+        <v>476</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
-        <v>1027</v>
+        <v>1081</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>1035</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
-        <v>1028</v>
+        <v>1520</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>1036</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
-        <v>947</v>
+        <v>566</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>948</v>
+        <v>568</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
-        <v>923</v>
+        <v>567</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>926</v>
+        <v>569</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
-        <v>924</v>
+        <v>1518</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>927</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
-        <v>925</v>
+        <v>1027</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>928</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
-        <v>908</v>
+        <v>1028</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>912</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
-        <v>909</v>
+        <v>947</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>914</v>
+        <v>948</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
-        <v>910</v>
+        <v>923</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>913</v>
+        <v>926</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
-        <v>911</v>
+        <v>924</v>
       </c>
       <c r="B685" s="1" t="s">
-        <v>915</v>
+        <v>927</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
-        <v>574</v>
+        <v>925</v>
       </c>
       <c r="B686" s="1" t="s">
-        <v>575</v>
+        <v>928</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
-        <v>629</v>
+        <v>908</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>631</v>
+        <v>912</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
-        <v>630</v>
+        <v>909</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>632</v>
+        <v>914</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>1308</v>
+        <v>910</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>1310</v>
+        <v>913</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>866</v>
+        <v>911</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>862</v>
+        <v>915</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
-        <v>877</v>
+        <v>574</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>880</v>
+        <v>575</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
-        <v>884</v>
+        <v>629</v>
       </c>
       <c r="B692" s="1" t="s">
-        <v>887</v>
+        <v>631</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
-        <v>865</v>
+        <v>630</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>861</v>
+        <v>632</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
-        <v>878</v>
+        <v>1308</v>
       </c>
       <c r="B694" s="1" t="s">
-        <v>881</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
-        <v>885</v>
+        <v>866</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>888</v>
+        <v>862</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
-        <v>899</v>
+        <v>877</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>864</v>
+        <v>880</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
-        <v>900</v>
+        <v>884</v>
       </c>
       <c r="B697" s="1" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
-        <v>901</v>
+        <v>865</v>
       </c>
       <c r="B698" s="1" t="s">
-        <v>889</v>
+        <v>861</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
-        <v>867</v>
+        <v>878</v>
       </c>
       <c r="B699" s="1" t="s">
-        <v>863</v>
+        <v>881</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="B700" s="1" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>886</v>
+        <v>899</v>
       </c>
       <c r="B701" s="1" t="s">
-        <v>890</v>
+        <v>864</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
-        <v>1210</v>
+        <v>900</v>
       </c>
       <c r="B702" s="1" t="s">
-        <v>1216</v>
+        <v>882</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
-        <v>1211</v>
+        <v>901</v>
       </c>
       <c r="B703" s="1" t="s">
-        <v>1217</v>
+        <v>889</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
-        <v>1212</v>
+        <v>867</v>
       </c>
       <c r="B704" s="1" t="s">
-        <v>1218</v>
+        <v>863</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
-        <v>1456</v>
+        <v>879</v>
       </c>
       <c r="B705" s="1" t="s">
-        <v>1457</v>
+        <v>883</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
-        <v>1464</v>
+        <v>886</v>
       </c>
       <c r="B706" s="1" t="s">
-        <v>1466</v>
+        <v>890</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
-        <v>1459</v>
+        <v>1210</v>
       </c>
       <c r="B707" s="1" t="s">
-        <v>1462</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
-        <v>1465</v>
+        <v>1211</v>
       </c>
       <c r="B708" s="1" t="s">
-        <v>1467</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
-        <v>786</v>
+        <v>1212</v>
       </c>
       <c r="B709" s="1" t="s">
-        <v>442</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
-        <v>996</v>
+        <v>1456</v>
       </c>
       <c r="B710" s="1" t="s">
-        <v>974</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
-        <v>1066</v>
+        <v>1464</v>
       </c>
       <c r="B711" s="1" t="s">
-        <v>1065</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
-        <v>1067</v>
+        <v>1459</v>
       </c>
       <c r="B712" s="1" t="s">
-        <v>1070</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
-        <v>1067</v>
+        <v>1465</v>
       </c>
       <c r="B713" s="1" t="s">
-        <v>1516</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="B714" s="1" t="s">
-        <v>780</v>
+        <v>442</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
-        <v>779</v>
+        <v>996</v>
       </c>
       <c r="B715" s="1" t="s">
-        <v>781</v>
+        <v>974</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
-        <v>682</v>
+        <v>1066</v>
       </c>
       <c r="B716" s="1" t="s">
-        <v>685</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
-        <v>183</v>
+        <v>1067</v>
       </c>
       <c r="B717" s="1" t="s">
-        <v>184</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
-        <v>1312</v>
+        <v>1067</v>
       </c>
       <c r="B718" s="1" t="s">
-        <v>1320</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
-        <v>1313</v>
+        <v>778</v>
       </c>
       <c r="B719" s="1" t="s">
-        <v>1321</v>
+        <v>780</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
-        <v>1314</v>
+        <v>779</v>
       </c>
       <c r="B720" s="1" t="s">
-        <v>1322</v>
+        <v>781</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
-        <v>1661</v>
+        <v>682</v>
       </c>
       <c r="B721" s="1" t="s">
-        <v>1683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
-        <v>1662</v>
+        <v>183</v>
       </c>
       <c r="B722" s="1" t="s">
-        <v>1684</v>
+        <v>184</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
-        <v>1669</v>
+        <v>1312</v>
       </c>
       <c r="B723" s="1" t="s">
-        <v>1687</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
-        <v>1670</v>
+        <v>1313</v>
       </c>
       <c r="B724" s="1" t="s">
-        <v>1691</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
-        <v>185</v>
+        <v>1314</v>
       </c>
       <c r="B725" s="1" t="s">
-        <v>186</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
-        <v>187</v>
+        <v>1661</v>
       </c>
       <c r="B726" s="1" t="s">
-        <v>188</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
-        <v>189</v>
+        <v>1662</v>
       </c>
       <c r="B727" s="1" t="s">
-        <v>190</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
-        <v>191</v>
+        <v>1669</v>
       </c>
       <c r="B728" s="1" t="s">
-        <v>192</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
-        <v>193</v>
+        <v>1670</v>
       </c>
       <c r="B729" s="1" t="s">
-        <v>194</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B730" s="1" t="s">
-        <v>142</v>
+        <v>186</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="B731" s="1" t="s">
-        <v>144</v>
+        <v>188</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B732" s="1" t="s">
-        <v>146</v>
+        <v>190</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B733" s="1" t="s">
-        <v>148</v>
+        <v>192</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B734" s="1" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
-        <v>200</v>
+        <v>1744</v>
       </c>
       <c r="B735" s="1" t="s">
-        <v>152</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
-        <v>201</v>
+        <v>1746</v>
       </c>
       <c r="B736" s="1" t="s">
-        <v>154</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
-        <v>202</v>
+        <v>1745</v>
       </c>
       <c r="B737" s="1" t="s">
-        <v>156</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B738" s="1" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B739" s="1" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B740" s="1" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B741" s="1" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
-        <v>742</v>
+        <v>199</v>
       </c>
       <c r="B742" s="1" t="s">
-        <v>812</v>
+        <v>150</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
-        <v>743</v>
+        <v>200</v>
       </c>
       <c r="B743" s="1" t="s">
-        <v>718</v>
+        <v>152</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
-        <v>744</v>
+        <v>201</v>
       </c>
       <c r="B744" s="1" t="s">
-        <v>719</v>
+        <v>154</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
-        <v>745</v>
+        <v>202</v>
       </c>
       <c r="B745" s="1" t="s">
-        <v>813</v>
+        <v>156</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
-        <v>746</v>
+        <v>203</v>
       </c>
       <c r="B746" s="1" t="s">
-        <v>706</v>
+        <v>158</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
-        <v>747</v>
+        <v>204</v>
       </c>
       <c r="B747" s="1" t="s">
-        <v>707</v>
+        <v>160</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
-        <v>748</v>
+        <v>205</v>
       </c>
       <c r="B748" s="1" t="s">
-        <v>814</v>
+        <v>162</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
-        <v>749</v>
+        <v>206</v>
       </c>
       <c r="B749" s="1" t="s">
-        <v>712</v>
+        <v>164</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="B750" s="1" t="s">
-        <v>713</v>
+        <v>812</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A751" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="B751" s="1" t="s">
-        <v>815</v>
+        <v>718</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
+        <v>744</v>
+      </c>
+      <c r="B752" s="1" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A753" t="s">
+        <v>745</v>
+      </c>
+      <c r="B753" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A754" t="s">
+        <v>746</v>
+      </c>
+      <c r="B754" s="1" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A755" t="s">
+        <v>747</v>
+      </c>
+      <c r="B755" s="1" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A756" t="s">
+        <v>748</v>
+      </c>
+      <c r="B756" s="1" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A757" t="s">
+        <v>749</v>
+      </c>
+      <c r="B757" s="1" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A758" t="s">
+        <v>750</v>
+      </c>
+      <c r="B758" s="1" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A759" t="s">
+        <v>751</v>
+      </c>
+      <c r="B759" s="1" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A760" t="s">
         <v>752</v>
       </c>
-      <c r="B752" s="1" t="s">
+      <c r="B760" s="1" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="753" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A753" t="s">
+    <row r="761" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A761" t="s">
         <v>753</v>
       </c>
-      <c r="B753" s="1" t="s">
+      <c r="B761" s="1" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="754" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A754" t="s">
+    <row r="762" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A762" t="s">
         <v>754</v>
       </c>
-      <c r="B754" s="1" t="s">
+      <c r="B762" s="1" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="755" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A755" t="s">
+    <row r="763" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A763" t="s">
         <v>755</v>
       </c>
-      <c r="B755" s="1" t="s">
+      <c r="B763" s="1" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="756" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A756" t="s">
+    <row r="764" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A764" t="s">
         <v>756</v>
       </c>
-      <c r="B756" s="1" t="s">
+      <c r="B764" s="1" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="757" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A757" t="s">
+    <row r="765" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A765" t="s">
         <v>757</v>
       </c>
-      <c r="B757" s="1" t="s">
+      <c r="B765" s="1" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="758" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A758" t="s">
+    <row r="766" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A766" t="s">
         <v>758</v>
       </c>
-      <c r="B758" s="1" t="s">
+      <c r="B766" s="1" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="759" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A759" t="s">
+    <row r="767" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A767" t="s">
         <v>759</v>
       </c>
-      <c r="B759" s="1" t="s">
+      <c r="B767" s="1" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="760" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A760" t="s">
+    <row r="768" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A768" t="s">
         <v>1250</v>
       </c>
-      <c r="B760" s="1" t="s">
+      <c r="B768" s="1" t="s">
         <v>1245</v>
       </c>
     </row>
-    <row r="761" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A761" t="s">
+    <row r="769" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A769" t="s">
         <v>1251</v>
       </c>
-      <c r="B761" s="1" t="s">
+      <c r="B769" s="1" t="s">
         <v>1246</v>
       </c>
     </row>
-    <row r="762" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A762" t="s">
+    <row r="770" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A770" t="s">
         <v>1254</v>
       </c>
-      <c r="B762" s="1" t="s">
+      <c r="B770" s="1" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="763" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A763" t="s">
+    <row r="771" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A771" t="s">
         <v>1494</v>
       </c>
-      <c r="B763" s="1" t="s">
+      <c r="B771" s="1" t="s">
         <v>1496</v>
       </c>
     </row>
-    <row r="764" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A764" t="s">
+    <row r="772" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A772" t="s">
         <v>1498</v>
       </c>
-      <c r="B764" s="1" t="s">
+      <c r="B772" s="1" t="s">
         <v>1505</v>
       </c>
     </row>
-    <row r="765" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A765" t="s">
+    <row r="773" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A773" t="s">
         <v>1498</v>
       </c>
-      <c r="B765" s="1" t="s">
+      <c r="B773" s="1" t="s">
         <v>1503</v>
       </c>
     </row>
-    <row r="766" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A766" t="s">
+    <row r="774" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A774" t="s">
         <v>1499</v>
       </c>
-      <c r="B766" s="1" t="s">
+      <c r="B774" s="1" t="s">
         <v>1504</v>
       </c>
     </row>
-    <row r="767" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A767" t="s">
+    <row r="775" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A775" t="s">
         <v>1552</v>
       </c>
-      <c r="B767" s="1" t="s">
+      <c r="B775" s="1" t="s">
         <v>1542</v>
       </c>
-      <c r="C767" s="2" t="s">
+      <c r="C775" s="2" t="s">
         <v>1546</v>
       </c>
     </row>
-    <row r="768" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A768" t="s">
+    <row r="776" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A776" t="s">
         <v>1553</v>
       </c>
-      <c r="B768" s="1" t="s">
+      <c r="B776" s="1" t="s">
         <v>1543</v>
       </c>
-      <c r="C768" s="2" t="s">
+      <c r="C776" s="2" t="s">
         <v>1547</v>
       </c>
     </row>
-    <row r="769" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A769" t="s">
+    <row r="777" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A777" t="s">
         <v>1714</v>
       </c>
-      <c r="B769" s="1" t="s">
+      <c r="B777" s="1" t="s">
         <v>1738</v>
       </c>
     </row>
-    <row r="770" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A770" t="s">
+    <row r="778" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A778" t="s">
         <v>1715</v>
       </c>
-      <c r="B770" s="1" t="s">
+      <c r="B778" s="1" t="s">
         <v>1739</v>
       </c>
     </row>
-    <row r="771" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A771" t="s">
+    <row r="779" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A779" t="s">
         <v>1716</v>
       </c>
-      <c r="B771" s="1" t="s">
+      <c r="B779" s="1" t="s">
         <v>1740</v>
       </c>
     </row>
-    <row r="772" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A772" t="s">
+    <row r="780" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A780" t="s">
         <v>1057</v>
       </c>
-      <c r="B772" s="1" t="s">
+      <c r="B780" s="1" t="s">
         <v>1061</v>
       </c>
     </row>
-    <row r="773" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A773" t="s">
+    <row r="781" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A781" t="s">
         <v>1058</v>
       </c>
-      <c r="B773" s="1" t="s">
+      <c r="B781" s="1" t="s">
         <v>1062</v>
       </c>
     </row>
-    <row r="774" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A774" t="s">
+    <row r="782" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A782" t="s">
         <v>1529</v>
       </c>
-      <c r="B774" s="1" t="s">
+      <c r="B782" s="1" t="s">
         <v>1530</v>
       </c>
     </row>
-    <row r="775" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A775" t="s">
+    <row r="783" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A783" t="s">
         <v>339</v>
       </c>
-      <c r="B775" s="1" t="s">
+      <c r="B783" s="1" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="776" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A776" t="s">
+    <row r="784" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A784" t="s">
         <v>344</v>
       </c>
-      <c r="B776" s="1" t="s">
+      <c r="B784" s="1" t="s">
         <v>342</v>
-      </c>
-    </row>
-    <row r="777" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A777" t="s">
-        <v>347</v>
-      </c>
-      <c r="B777" s="1" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="778" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A778" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B778" s="1" t="s">
-        <v>1232</v>
-      </c>
-    </row>
-    <row r="779" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A779" t="s">
-        <v>1227</v>
-      </c>
-      <c r="B779" s="1" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="780" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A780" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B780" s="1" t="s">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="781" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A781" t="s">
-        <v>921</v>
-      </c>
-      <c r="B781" s="1" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="782" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A782" t="s">
-        <v>916</v>
-      </c>
-      <c r="B782" s="1" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="783" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A783" t="s">
-        <v>917</v>
-      </c>
-      <c r="B783" s="1" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="784" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A784" t="s">
-        <v>918</v>
-      </c>
-      <c r="B784" s="1" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="785" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A785" t="s">
-        <v>940</v>
+        <v>347</v>
       </c>
       <c r="B785" s="1" t="s">
-        <v>941</v>
+        <v>343</v>
       </c>
     </row>
     <row r="786" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A786" t="s">
-        <v>558</v>
+        <v>1226</v>
       </c>
       <c r="B786" s="1" t="s">
-        <v>559</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A787" t="s">
-        <v>560</v>
+        <v>1227</v>
       </c>
       <c r="B787" s="1" t="s">
-        <v>561</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="788" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A788" t="s">
-        <v>1332</v>
+        <v>1228</v>
       </c>
       <c r="B788" s="1" t="s">
-        <v>1338</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="789" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A789" t="s">
-        <v>1333</v>
+        <v>921</v>
       </c>
       <c r="B789" s="1" t="s">
-        <v>1339</v>
+        <v>919</v>
       </c>
     </row>
     <row r="790" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A790" t="s">
-        <v>1334</v>
+        <v>916</v>
       </c>
       <c r="B790" s="1" t="s">
-        <v>1340</v>
+        <v>920</v>
       </c>
     </row>
     <row r="791" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A791" t="s">
-        <v>584</v>
+        <v>917</v>
       </c>
       <c r="B791" s="1" t="s">
-        <v>587</v>
+        <v>922</v>
       </c>
     </row>
     <row r="792" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A792" t="s">
-        <v>588</v>
+        <v>918</v>
       </c>
       <c r="B792" s="1" t="s">
-        <v>590</v>
+        <v>939</v>
       </c>
     </row>
     <row r="793" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A793" t="s">
-        <v>589</v>
+        <v>940</v>
       </c>
       <c r="B793" s="1" t="s">
-        <v>595</v>
+        <v>941</v>
       </c>
     </row>
     <row r="794" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A794" t="s">
-        <v>371</v>
+        <v>558</v>
       </c>
       <c r="B794" s="1" t="s">
-        <v>377</v>
+        <v>559</v>
       </c>
     </row>
     <row r="795" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A795" t="s">
-        <v>373</v>
+        <v>560</v>
       </c>
       <c r="B795" s="1" t="s">
-        <v>378</v>
+        <v>561</v>
       </c>
     </row>
     <row r="796" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A796" t="s">
-        <v>375</v>
+        <v>1332</v>
       </c>
       <c r="B796" s="1" t="s">
-        <v>379</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="797" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A797" t="s">
-        <v>681</v>
+        <v>1333</v>
       </c>
       <c r="B797" s="1" t="s">
-        <v>618</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="798" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A798" t="s">
-        <v>351</v>
+        <v>1334</v>
       </c>
       <c r="B798" s="1" t="s">
-        <v>352</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="799" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A799" t="s">
-        <v>358</v>
+        <v>584</v>
       </c>
       <c r="B799" s="1" t="s">
-        <v>355</v>
+        <v>587</v>
       </c>
     </row>
     <row r="800" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A800" t="s">
-        <v>360</v>
+        <v>588</v>
       </c>
       <c r="B800" s="1" t="s">
-        <v>356</v>
+        <v>590</v>
       </c>
     </row>
     <row r="801" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A801" t="s">
-        <v>1297</v>
+        <v>589</v>
       </c>
       <c r="B801" s="1" t="s">
-        <v>1300</v>
+        <v>595</v>
       </c>
     </row>
     <row r="802" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A802" t="s">
-        <v>1298</v>
+        <v>371</v>
       </c>
       <c r="B802" s="1" t="s">
-        <v>1301</v>
+        <v>377</v>
       </c>
     </row>
     <row r="803" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A803" t="s">
-        <v>1299</v>
+        <v>373</v>
       </c>
       <c r="B803" s="1" t="s">
-        <v>1302</v>
+        <v>378</v>
       </c>
     </row>
     <row r="804" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A804" t="s">
-        <v>1509</v>
+        <v>375</v>
       </c>
       <c r="B804" s="1" t="s">
-        <v>1511</v>
+        <v>379</v>
       </c>
     </row>
     <row r="805" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A805" t="s">
-        <v>1705</v>
+        <v>681</v>
       </c>
       <c r="B805" s="1" t="s">
-        <v>1712</v>
+        <v>618</v>
       </c>
     </row>
     <row r="806" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A806" t="s">
-        <v>1703</v>
+        <v>351</v>
       </c>
       <c r="B806" s="1" t="s">
-        <v>1710</v>
+        <v>352</v>
       </c>
     </row>
     <row r="807" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A807" t="s">
-        <v>1704</v>
+        <v>358</v>
       </c>
       <c r="B807" s="1" t="s">
-        <v>1711</v>
+        <v>355</v>
       </c>
     </row>
     <row r="808" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A808" t="s">
-        <v>997</v>
+        <v>360</v>
       </c>
       <c r="B808" s="1" t="s">
-        <v>961</v>
+        <v>356</v>
       </c>
     </row>
     <row r="809" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A809" t="s">
-        <v>998</v>
+        <v>1297</v>
       </c>
       <c r="B809" s="1" t="s">
-        <v>962</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="810" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A810" t="s">
-        <v>999</v>
+        <v>1298</v>
       </c>
       <c r="B810" s="1" t="s">
-        <v>963</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="811" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A811" t="s">
-        <v>1627</v>
+        <v>1299</v>
       </c>
       <c r="B811" s="1" t="s">
-        <v>1636</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="812" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A812" t="s">
-        <v>1628</v>
+        <v>1509</v>
       </c>
       <c r="B812" s="1" t="s">
-        <v>1635</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="813" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A813" t="s">
-        <v>853</v>
+        <v>1705</v>
       </c>
       <c r="B813" s="1" t="s">
-        <v>854</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="814" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A814" t="s">
-        <v>851</v>
+        <v>1703</v>
       </c>
       <c r="B814" s="1" t="s">
-        <v>855</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="815" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A815" t="s">
-        <v>852</v>
+        <v>1704</v>
       </c>
       <c r="B815" s="1" t="s">
-        <v>856</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="816" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A816" t="s">
-        <v>776</v>
+        <v>997</v>
       </c>
       <c r="B816" s="1" t="s">
-        <v>774</v>
+        <v>961</v>
       </c>
     </row>
     <row r="817" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A817" t="s">
-        <v>207</v>
+        <v>998</v>
       </c>
       <c r="B817" s="1" t="s">
-        <v>208</v>
+        <v>962</v>
       </c>
     </row>
     <row r="818" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A818" t="s">
-        <v>209</v>
+        <v>999</v>
       </c>
       <c r="B818" s="1" t="s">
-        <v>210</v>
+        <v>963</v>
       </c>
     </row>
     <row r="819" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A819" t="s">
-        <v>701</v>
+        <v>1627</v>
       </c>
       <c r="B819" s="1" t="s">
-        <v>664</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="820" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A820" t="s">
-        <v>702</v>
+        <v>1628</v>
       </c>
       <c r="B820" s="1" t="s">
-        <v>540</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="821" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A821" t="s">
-        <v>760</v>
+        <v>853</v>
       </c>
       <c r="B821" s="1" t="s">
-        <v>523</v>
+        <v>854</v>
       </c>
     </row>
     <row r="822" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A822" t="s">
-        <v>1348</v>
+        <v>851</v>
       </c>
       <c r="B822" s="1" t="s">
-        <v>1349</v>
+        <v>855</v>
       </c>
     </row>
     <row r="823" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A823" t="s">
-        <v>703</v>
+        <v>852</v>
       </c>
       <c r="B823" s="1" t="s">
-        <v>524</v>
+        <v>856</v>
       </c>
     </row>
     <row r="824" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A824" t="s">
-        <v>704</v>
+        <v>776</v>
       </c>
       <c r="B824" s="1" t="s">
-        <v>525</v>
+        <v>774</v>
       </c>
     </row>
     <row r="825" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A825" t="s">
-        <v>761</v>
+        <v>207</v>
       </c>
       <c r="B825" s="1" t="s">
-        <v>763</v>
+        <v>208</v>
       </c>
     </row>
     <row r="826" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A826" t="s">
-        <v>762</v>
+        <v>209</v>
       </c>
       <c r="B826" s="1" t="s">
-        <v>764</v>
+        <v>210</v>
       </c>
     </row>
     <row r="827" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A827" t="s">
-        <v>1694</v>
+        <v>701</v>
       </c>
       <c r="B827" s="1" t="s">
-        <v>1699</v>
+        <v>664</v>
       </c>
     </row>
     <row r="828" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A828" t="s">
-        <v>1694</v>
+        <v>702</v>
       </c>
       <c r="B828" s="1" t="s">
-        <v>1692</v>
+        <v>540</v>
       </c>
     </row>
     <row r="829" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A829" t="s">
-        <v>1695</v>
+        <v>760</v>
       </c>
       <c r="B829" s="1" t="s">
-        <v>1698</v>
+        <v>523</v>
       </c>
     </row>
     <row r="830" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A830" t="s">
-        <v>1695</v>
+        <v>1348</v>
       </c>
       <c r="B830" s="1" t="s">
-        <v>1700</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="831" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A831" t="s">
-        <v>1655</v>
+        <v>703</v>
       </c>
       <c r="B831" s="1" t="s">
-        <v>1677</v>
+        <v>524</v>
       </c>
     </row>
     <row r="832" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A832" t="s">
-        <v>1656</v>
+        <v>704</v>
       </c>
       <c r="B832" s="1" t="s">
-        <v>1680</v>
+        <v>525</v>
       </c>
     </row>
     <row r="833" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A833" t="s">
-        <v>1653</v>
+        <v>761</v>
       </c>
       <c r="B833" s="1" t="s">
-        <v>1678</v>
+        <v>763</v>
       </c>
     </row>
     <row r="834" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A834" t="s">
-        <v>1654</v>
+        <v>762</v>
       </c>
       <c r="B834" s="1" t="s">
-        <v>1679</v>
+        <v>764</v>
       </c>
     </row>
     <row r="835" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A835" t="s">
-        <v>1352</v>
+        <v>1694</v>
       </c>
       <c r="B835" s="1" t="s">
-        <v>1360</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="836" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A836" t="s">
-        <v>1353</v>
+        <v>1694</v>
       </c>
       <c r="B836" s="1" t="s">
-        <v>1362</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="837" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A837" t="s">
-        <v>1354</v>
+        <v>1695</v>
       </c>
       <c r="B837" s="1" t="s">
-        <v>1361</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="838" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A838" t="s">
-        <v>693</v>
+        <v>1695</v>
       </c>
       <c r="B838" s="1" t="s">
-        <v>692</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="839" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A839" t="s">
-        <v>906</v>
+        <v>1655</v>
       </c>
       <c r="B839" s="1" t="s">
-        <v>665</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="840" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A840" t="s">
-        <v>819</v>
+        <v>1656</v>
       </c>
       <c r="B840" s="1" t="s">
-        <v>810</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="841" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A841" t="s">
-        <v>818</v>
+        <v>1653</v>
       </c>
       <c r="B841" s="1" t="s">
-        <v>811</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="842" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A842" t="s">
-        <v>1606</v>
+        <v>1654</v>
       </c>
       <c r="B842" s="1" t="s">
-        <v>1617</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="843" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A843" t="s">
-        <v>1605</v>
+        <v>1352</v>
       </c>
       <c r="B843" s="1" t="s">
-        <v>1621</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="844" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A844" t="s">
-        <v>1570</v>
+        <v>1353</v>
       </c>
       <c r="B844" s="1" t="s">
-        <v>1566</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="845" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A845" t="s">
-        <v>1569</v>
+        <v>1354</v>
       </c>
       <c r="B845" s="1" t="s">
-        <v>1565</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="846" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A846" t="s">
-        <v>1567</v>
+        <v>693</v>
       </c>
       <c r="B846" s="1" t="s">
-        <v>1563</v>
+        <v>692</v>
       </c>
     </row>
     <row r="847" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A847" t="s">
-        <v>1568</v>
+        <v>906</v>
       </c>
       <c r="B847" s="1" t="s">
-        <v>1564</v>
+        <v>665</v>
       </c>
     </row>
     <row r="848" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A848" t="s">
-        <v>1608</v>
+        <v>819</v>
       </c>
       <c r="B848" s="1" t="s">
-        <v>1618</v>
+        <v>810</v>
       </c>
     </row>
     <row r="849" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A849" t="s">
-        <v>1607</v>
+        <v>818</v>
       </c>
       <c r="B849" s="1" t="s">
-        <v>1622</v>
+        <v>811</v>
       </c>
     </row>
     <row r="850" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A850" t="s">
-        <v>1371</v>
+        <v>1606</v>
       </c>
       <c r="B850" s="1" t="s">
-        <v>1369</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="851" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A851" t="s">
-        <v>492</v>
+        <v>1605</v>
       </c>
       <c r="B851" s="1" t="s">
-        <v>494</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="852" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A852" t="s">
-        <v>823</v>
+        <v>1570</v>
       </c>
       <c r="B852" s="1" t="s">
-        <v>828</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="853" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A853" t="s">
-        <v>824</v>
+        <v>1569</v>
       </c>
       <c r="B853" s="1" t="s">
-        <v>827</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="854" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A854" t="s">
-        <v>825</v>
+        <v>1567</v>
       </c>
       <c r="B854" s="1" t="s">
-        <v>826</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="855" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A855" t="s">
-        <v>668</v>
+        <v>1568</v>
       </c>
       <c r="B855" s="1" t="s">
-        <v>658</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="856" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A856" t="s">
-        <v>666</v>
+        <v>1608</v>
       </c>
       <c r="B856" s="1" t="s">
-        <v>659</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="857" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A857" t="s">
-        <v>667</v>
+        <v>1607</v>
       </c>
       <c r="B857" s="1" t="s">
-        <v>660</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="858" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A858" t="s">
-        <v>1376</v>
+        <v>1371</v>
       </c>
       <c r="B858" s="1" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="859" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A859" t="s">
-        <v>1373</v>
+        <v>492</v>
       </c>
       <c r="B859" s="1" t="s">
-        <v>1375</v>
+        <v>494</v>
       </c>
     </row>
     <row r="860" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A860" t="s">
-        <v>1377</v>
+        <v>823</v>
       </c>
       <c r="B860" s="1" t="s">
-        <v>1379</v>
+        <v>828</v>
       </c>
     </row>
     <row r="861" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A861" t="s">
-        <v>1378</v>
+        <v>824</v>
       </c>
       <c r="B861" s="1" t="s">
-        <v>1380</v>
+        <v>827</v>
       </c>
     </row>
     <row r="862" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A862" t="s">
-        <v>977</v>
+        <v>825</v>
       </c>
       <c r="B862" s="1" t="s">
-        <v>979</v>
+        <v>826</v>
       </c>
     </row>
     <row r="863" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A863" t="s">
-        <v>978</v>
+        <v>668</v>
       </c>
       <c r="B863" s="1" t="s">
-        <v>980</v>
+        <v>658</v>
       </c>
     </row>
     <row r="864" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A864" t="s">
-        <v>362</v>
+        <v>666</v>
       </c>
       <c r="B864" s="1" t="s">
-        <v>363</v>
+        <v>659</v>
       </c>
     </row>
     <row r="865" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A865" t="s">
-        <v>367</v>
+        <v>667</v>
       </c>
       <c r="B865" s="1" t="s">
-        <v>365</v>
+        <v>660</v>
       </c>
     </row>
     <row r="866" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A866" t="s">
-        <v>368</v>
+        <v>1376</v>
       </c>
       <c r="B866" s="1" t="s">
-        <v>366</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="867" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A867" t="s">
-        <v>1050</v>
+        <v>1373</v>
       </c>
       <c r="B867" s="1" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C867" s="2" t="s">
-        <v>1052</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="868" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A868" t="s">
-        <v>211</v>
+        <v>1377</v>
       </c>
       <c r="B868" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C868" s="2" t="s">
-        <v>212</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="869" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A869" t="s">
-        <v>299</v>
+        <v>1378</v>
       </c>
       <c r="B869" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C869" s="2" t="s">
-        <v>300</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="870" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A870" t="s">
-        <v>213</v>
+        <v>977</v>
       </c>
       <c r="B870" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C870" s="2" t="s">
-        <v>251</v>
+        <v>979</v>
       </c>
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A871" t="s">
-        <v>439</v>
+        <v>978</v>
       </c>
       <c r="B871" s="1" t="s">
-        <v>447</v>
+        <v>980</v>
       </c>
     </row>
     <row r="872" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A872" t="s">
-        <v>1055</v>
+        <v>362</v>
       </c>
       <c r="B872" s="1" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C872" s="2" t="s">
-        <v>1048</v>
+        <v>363</v>
       </c>
     </row>
     <row r="873" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A873" t="s">
-        <v>215</v>
+        <v>367</v>
       </c>
       <c r="B873" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="C873" s="2" t="s">
-        <v>580</v>
+        <v>365</v>
       </c>
     </row>
     <row r="874" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A874" t="s">
-        <v>260</v>
+        <v>368</v>
       </c>
       <c r="B874" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C874" s="2" t="s">
-        <v>262</v>
+        <v>366</v>
       </c>
     </row>
     <row r="875" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A875" t="s">
-        <v>261</v>
+        <v>1050</v>
       </c>
       <c r="B875" s="1" t="s">
-        <v>264</v>
+        <v>1051</v>
       </c>
       <c r="C875" s="2" t="s">
-        <v>268</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="876" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A876" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B876" s="1" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C876" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="877" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A877" t="s">
-        <v>232</v>
+        <v>299</v>
       </c>
       <c r="B877" s="1" t="s">
-        <v>247</v>
+        <v>301</v>
       </c>
       <c r="C877" s="2" t="s">
-        <v>250</v>
+        <v>300</v>
       </c>
     </row>
     <row r="878" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A878" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="B878" s="1" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="C878" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="879" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A879" t="s">
-        <v>218</v>
+        <v>439</v>
       </c>
       <c r="B879" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C879" s="2" t="s">
-        <v>219</v>
+        <v>447</v>
       </c>
     </row>
     <row r="880" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A880" t="s">
-        <v>987</v>
+        <v>1055</v>
       </c>
       <c r="B880" s="1" t="s">
-        <v>995</v>
+        <v>1047</v>
+      </c>
+      <c r="C880" s="2" t="s">
+        <v>1048</v>
       </c>
     </row>
     <row r="881" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A881" t="s">
-        <v>1731</v>
+        <v>215</v>
       </c>
       <c r="B881" s="1" t="s">
-        <v>1730</v>
+        <v>579</v>
+      </c>
+      <c r="C881" s="2" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A882" t="s">
-        <v>1671</v>
+        <v>260</v>
       </c>
       <c r="B882" s="1" t="s">
-        <v>1672</v>
+        <v>265</v>
+      </c>
+      <c r="C882" s="2" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="883" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A883" t="s">
-        <v>1728</v>
+        <v>261</v>
       </c>
       <c r="B883" s="1" t="s">
-        <v>1729</v>
+        <v>264</v>
+      </c>
+      <c r="C883" s="2" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="884" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A884" t="s">
-        <v>281</v>
+        <v>216</v>
       </c>
       <c r="B884" s="1" t="s">
-        <v>282</v>
+        <v>217</v>
       </c>
       <c r="C884" s="2" t="s">
-        <v>283</v>
+        <v>217</v>
       </c>
     </row>
     <row r="885" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A885" t="s">
-        <v>986</v>
+        <v>232</v>
       </c>
       <c r="B885" s="1" t="s">
-        <v>994</v>
+        <v>247</v>
+      </c>
+      <c r="C885" s="2" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="886" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A886" t="s">
-        <v>799</v>
+        <v>236</v>
       </c>
       <c r="B886" s="1" t="s">
-        <v>802</v>
+        <v>246</v>
+      </c>
+      <c r="C886" s="2" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="887" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A887" t="s">
-        <v>258</v>
+        <v>218</v>
       </c>
       <c r="B887" s="1" t="s">
-        <v>266</v>
+        <v>219</v>
       </c>
       <c r="C887" s="2" t="s">
-        <v>263</v>
+        <v>219</v>
       </c>
     </row>
     <row r="888" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A888" t="s">
-        <v>259</v>
+        <v>987</v>
       </c>
       <c r="B888" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C888" s="2" t="s">
-        <v>269</v>
+        <v>995</v>
       </c>
     </row>
     <row r="889" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A889" t="s">
-        <v>297</v>
+        <v>1731</v>
       </c>
       <c r="B889" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C889" s="2" t="s">
-        <v>307</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="890" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A890" t="s">
-        <v>220</v>
+        <v>1671</v>
       </c>
       <c r="B890" s="1" t="s">
-        <v>1257</v>
-      </c>
-      <c r="C890" s="2" t="s">
-        <v>221</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="891" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A891" t="s">
-        <v>988</v>
+        <v>1756</v>
       </c>
       <c r="B891" s="1" t="s">
-        <v>1258</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="892" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A892" t="s">
-        <v>1732</v>
+        <v>1728</v>
       </c>
       <c r="B892" s="1" t="s">
-        <v>1733</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A893" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="B893" s="1" t="s">
-        <v>304</v>
+        <v>282</v>
       </c>
       <c r="C893" s="2" t="s">
-        <v>308</v>
+        <v>283</v>
       </c>
     </row>
     <row r="894" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A894" t="s">
-        <v>294</v>
+        <v>986</v>
       </c>
       <c r="B894" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C894" s="2" t="s">
-        <v>314</v>
+        <v>994</v>
       </c>
     </row>
     <row r="895" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A895" t="s">
-        <v>222</v>
+        <v>799</v>
       </c>
       <c r="B895" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C895" s="2" t="s">
-        <v>257</v>
+        <v>802</v>
       </c>
     </row>
     <row r="896" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A896" t="s">
-        <v>985</v>
+        <v>258</v>
       </c>
       <c r="B896" s="1" t="s">
-        <v>993</v>
+        <v>266</v>
+      </c>
+      <c r="C896" s="2" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="897" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A897" t="s">
-        <v>800</v>
+        <v>259</v>
       </c>
       <c r="B897" s="1" t="s">
-        <v>805</v>
+        <v>267</v>
+      </c>
+      <c r="C897" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="898" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A898" t="s">
-        <v>224</v>
+        <v>297</v>
       </c>
       <c r="B898" s="1" t="s">
-        <v>225</v>
+        <v>303</v>
       </c>
       <c r="C898" s="2" t="s">
-        <v>225</v>
+        <v>307</v>
       </c>
     </row>
     <row r="899" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A899" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="B899" s="1" t="s">
-        <v>240</v>
+        <v>1257</v>
       </c>
       <c r="C899" s="2" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
     </row>
     <row r="900" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A900" t="s">
-        <v>239</v>
+        <v>988</v>
       </c>
       <c r="B900" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C900" s="2" t="s">
-        <v>252</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="901" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A901" t="s">
-        <v>562</v>
+        <v>1732</v>
       </c>
       <c r="B901" s="1" t="s">
-        <v>563</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="902" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A902" t="s">
-        <v>989</v>
+        <v>298</v>
       </c>
       <c r="B902" s="1" t="s">
-        <v>992</v>
+        <v>304</v>
+      </c>
+      <c r="C902" s="2" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="903" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A903" t="s">
-        <v>564</v>
+        <v>294</v>
       </c>
       <c r="B903" s="1" t="s">
-        <v>565</v>
+        <v>306</v>
+      </c>
+      <c r="C903" s="2" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A904" t="s">
-        <v>797</v>
+        <v>222</v>
       </c>
       <c r="B904" s="1" t="s">
-        <v>803</v>
+        <v>223</v>
+      </c>
+      <c r="C904" s="2" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="905" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A905" t="s">
-        <v>798</v>
+        <v>985</v>
       </c>
       <c r="B905" s="1" t="s">
-        <v>804</v>
+        <v>993</v>
       </c>
     </row>
     <row r="906" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A906" t="s">
-        <v>330</v>
+        <v>800</v>
       </c>
       <c r="B906" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C906" s="2" t="s">
-        <v>336</v>
+        <v>805</v>
       </c>
     </row>
     <row r="907" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A907" t="s">
-        <v>983</v>
+        <v>224</v>
       </c>
       <c r="B907" s="1" t="s">
-        <v>990</v>
+        <v>225</v>
+      </c>
+      <c r="C907" s="2" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="908" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A908" t="s">
-        <v>1734</v>
+        <v>235</v>
       </c>
       <c r="B908" s="1" t="s">
-        <v>1735</v>
+        <v>240</v>
+      </c>
+      <c r="C908" s="2" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="909" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A909" t="s">
-        <v>801</v>
+        <v>239</v>
       </c>
       <c r="B909" s="1" t="s">
-        <v>806</v>
+        <v>245</v>
+      </c>
+      <c r="C909" s="2" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="910" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A910" t="s">
-        <v>296</v>
+        <v>562</v>
       </c>
       <c r="B910" s="1" t="s">
-        <v>302</v>
+        <v>563</v>
       </c>
     </row>
     <row r="911" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A911" t="s">
-        <v>226</v>
+        <v>989</v>
       </c>
       <c r="B911" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C911" s="2" t="s">
-        <v>292</v>
+        <v>992</v>
       </c>
     </row>
     <row r="912" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A912" t="s">
-        <v>984</v>
+        <v>564</v>
       </c>
       <c r="B912" s="1" t="s">
-        <v>991</v>
+        <v>565</v>
       </c>
     </row>
     <row r="913" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A913" t="s">
-        <v>1726</v>
+        <v>797</v>
       </c>
       <c r="B913" s="1" t="s">
-        <v>1727</v>
+        <v>803</v>
       </c>
     </row>
     <row r="914" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A914" t="s">
-        <v>228</v>
+        <v>798</v>
       </c>
       <c r="B914" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="C914" s="2" t="s">
-        <v>229</v>
+        <v>804</v>
       </c>
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A915" t="s">
-        <v>234</v>
+        <v>330</v>
       </c>
       <c r="B915" s="1" t="s">
-        <v>241</v>
+        <v>335</v>
       </c>
       <c r="C915" s="2" t="s">
-        <v>253</v>
+        <v>336</v>
       </c>
     </row>
     <row r="916" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A916" t="s">
-        <v>238</v>
+        <v>983</v>
       </c>
       <c r="B916" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C916" s="2" t="s">
-        <v>254</v>
+        <v>990</v>
       </c>
     </row>
     <row r="917" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A917" t="s">
-        <v>230</v>
+        <v>1734</v>
       </c>
       <c r="B917" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C917" s="2" t="s">
-        <v>231</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="918" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A918" t="s">
-        <v>1046</v>
+        <v>801</v>
       </c>
       <c r="B918" s="1" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C918" s="2" t="s">
-        <v>1053</v>
+        <v>806</v>
       </c>
     </row>
     <row r="919" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A919" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="B919" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C919" s="2" t="s">
-        <v>255</v>
+        <v>302</v>
       </c>
     </row>
     <row r="920" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A920" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="B920" s="1" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="C920" s="2" t="s">
-        <v>256</v>
+        <v>292</v>
       </c>
     </row>
     <row r="921" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A921" t="s">
+        <v>984</v>
+      </c>
+      <c r="B921" s="1" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="922" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A922" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B922" s="1" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="923" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A923" t="s">
+        <v>228</v>
+      </c>
+      <c r="B923" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C923" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="924" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A924" t="s">
+        <v>234</v>
+      </c>
+      <c r="B924" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C924" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A925" t="s">
+        <v>238</v>
+      </c>
+      <c r="B925" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C925" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A926" t="s">
+        <v>230</v>
+      </c>
+      <c r="B926" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C926" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A927" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B927" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C927" s="2" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="928" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A928" t="s">
+        <v>233</v>
+      </c>
+      <c r="B928" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C928" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="929" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A929" t="s">
+        <v>237</v>
+      </c>
+      <c r="B929" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C929" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="930" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A930" t="s">
         <v>295</v>
       </c>
-      <c r="B921" s="1" t="s">
+      <c r="B930" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C921" s="2" t="s">
+      <c r="C930" s="2" t="s">
         <v>313</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K921">
-    <sortState ref="A2:K921">
-      <sortCondition ref="A1:A921"/>
+  <autoFilter ref="A1:K930">
+    <sortState ref="A2:K930">
+      <sortCondition ref="A1:A930"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13647,7 +13770,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.7265625" customWidth="1"/>
@@ -13700,7 +13823,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>1498</v>
+        <v>1741</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1505</v>
@@ -13760,6 +13883,70 @@
       </c>
       <c r="B16" s="1" t="s">
         <v>1508</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>1749</v>
       </c>
     </row>
   </sheetData>
